--- a/research/traditional_assets/database/data/hungary/hungary_diversified.xlsx
+++ b/research/traditional_assets/database/data/hungary/hungary_diversified.xlsx
@@ -8,6 +8,8 @@
   </bookViews>
   <sheets>
     <sheet name="earnings_debt" sheetId="1" r:id="rId1"/>
+    <sheet name="cost_capital" sheetId="2" r:id="rId2"/>
+    <sheet name="buse_opus" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -588,34 +590,37 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.9490000000000001</v>
+        <v>0.642</v>
+      </c>
+      <c r="E2">
+        <v>0.393</v>
       </c>
       <c r="G2">
-        <v>0.08900976634936333</v>
+        <v>0.1365303244005642</v>
       </c>
       <c r="H2">
-        <v>0.08900976634936333</v>
+        <v>0.1365303244005642</v>
       </c>
       <c r="I2">
-        <v>-0.01940907405118061</v>
+        <v>0.0769158439116126</v>
       </c>
       <c r="J2">
-        <v>-0.009704537025590307</v>
+        <v>0.06275383075478867</v>
       </c>
       <c r="K2">
-        <v>6.36</v>
+        <v>45.3</v>
       </c>
       <c r="L2">
-        <v>0.007862529360860428</v>
+        <v>0.04259520451339915</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="N2">
-        <v>0</v>
+        <v>4.664179104477612e-05</v>
       </c>
       <c r="O2">
-        <v>0</v>
+        <v>0.0002207505518763797</v>
       </c>
       <c r="P2">
         <v>0</v>
@@ -627,76 +632,79 @@
         <v>0</v>
       </c>
       <c r="S2">
-        <v>0</v>
+        <v>0.01</v>
+      </c>
+      <c r="T2">
+        <v>1</v>
       </c>
       <c r="U2">
-        <v>477.6</v>
+        <v>261.8</v>
       </c>
       <c r="V2">
-        <v>1.10889250058045</v>
+        <v>1.221082089552239</v>
       </c>
       <c r="W2">
-        <v>0.009872710338404223</v>
+        <v>0.06462196861626247</v>
       </c>
       <c r="X2">
-        <v>0.1445554398417766</v>
+        <v>0.30735614037807</v>
       </c>
       <c r="Y2">
-        <v>-0.1346827295033723</v>
+        <v>-0.2427341717618075</v>
       </c>
       <c r="Z2">
-        <v>1.42763854571126</v>
+        <v>1.100931677018634</v>
       </c>
       <c r="AA2">
-        <v>-0.01385457112601482</v>
+        <v>0.06908768013221302</v>
       </c>
       <c r="AB2">
-        <v>0.0767889000218063</v>
+        <v>0.1215404733623177</v>
       </c>
       <c r="AC2">
-        <v>-0.09064347114782112</v>
+        <v>-0.05245279323010467</v>
       </c>
       <c r="AD2">
-        <v>797.4</v>
+        <v>695.3</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>797.4</v>
+        <v>695.3</v>
       </c>
       <c r="AG2">
-        <v>319.8</v>
+        <v>433.4999999999999</v>
       </c>
       <c r="AH2">
-        <v>0.6492956599625438</v>
+        <v>0.7643179070023085</v>
       </c>
       <c r="AI2">
-        <v>0.4778856526429342</v>
+        <v>0.4744132096069869</v>
       </c>
       <c r="AJ2">
-        <v>0.4261159227181878</v>
+        <v>0.6690847352986571</v>
       </c>
       <c r="AK2">
-        <v>0.2685138539042821</v>
+        <v>0.3601096527662402</v>
       </c>
       <c r="AL2">
-        <v>21.1</v>
+        <v>67.5</v>
       </c>
       <c r="AM2">
-        <v>-7.299999999999997</v>
+        <v>30</v>
       </c>
       <c r="AN2">
-        <v>14.82156133828996</v>
+        <v>4.114201183431953</v>
       </c>
       <c r="AO2">
-        <v>-0.7440758293838862</v>
+        <v>1.211851851851852</v>
       </c>
       <c r="AP2">
-        <v>5.944237918215613</v>
+        <v>2.565088757396449</v>
       </c>
       <c r="AQ2">
-        <v>2.15068493150685</v>
+        <v>2.726666666666667</v>
       </c>
     </row>
     <row r="3">
@@ -716,34 +724,37 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.9490000000000001</v>
+        <v>0.642</v>
+      </c>
+      <c r="E3">
+        <v>0.393</v>
       </c>
       <c r="G3">
-        <v>0.08900976634936333</v>
+        <v>0.1365303244005642</v>
       </c>
       <c r="H3">
-        <v>0.08900976634936333</v>
+        <v>0.1365303244005642</v>
       </c>
       <c r="I3">
-        <v>-0.01940907405118061</v>
+        <v>0.0769158439116126</v>
       </c>
       <c r="J3">
-        <v>-0.009704537025590307</v>
+        <v>0.06275383075478867</v>
       </c>
       <c r="K3">
-        <v>6.36</v>
+        <v>45.3</v>
       </c>
       <c r="L3">
-        <v>0.007862529360860428</v>
+        <v>0.04259520451339915</v>
       </c>
       <c r="M3">
-        <v>-0</v>
+        <v>0.01</v>
       </c>
       <c r="N3">
-        <v>-0</v>
+        <v>4.664179104477612e-05</v>
       </c>
       <c r="O3">
-        <v>-0</v>
+        <v>0.0002207505518763797</v>
       </c>
       <c r="P3">
         <v>-0</v>
@@ -755,76 +766,8791 @@
         <v>-0</v>
       </c>
       <c r="S3">
-        <v>0</v>
+        <v>0.01</v>
+      </c>
+      <c r="T3">
+        <v>1</v>
       </c>
       <c r="U3">
-        <v>477.6</v>
+        <v>261.8</v>
       </c>
       <c r="V3">
-        <v>1.10889250058045</v>
+        <v>1.221082089552239</v>
       </c>
       <c r="W3">
-        <v>0.009872710338404223</v>
+        <v>0.06462196861626247</v>
       </c>
       <c r="X3">
-        <v>0.1445554398417766</v>
+        <v>0.30735614037807</v>
       </c>
       <c r="Y3">
-        <v>-0.1346827295033723</v>
+        <v>-0.2427341717618075</v>
       </c>
       <c r="Z3">
-        <v>1.42763854571126</v>
+        <v>1.100931677018634</v>
       </c>
       <c r="AA3">
-        <v>-0.01385457112601482</v>
+        <v>0.06908768013221302</v>
       </c>
       <c r="AB3">
-        <v>0.0767889000218063</v>
+        <v>0.1215404733623177</v>
       </c>
       <c r="AC3">
-        <v>-0.09064347114782112</v>
+        <v>-0.05245279323010467</v>
       </c>
       <c r="AD3">
-        <v>797.4</v>
+        <v>695.3</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>797.4</v>
+        <v>695.3</v>
       </c>
       <c r="AG3">
-        <v>319.8</v>
+        <v>433.4999999999999</v>
       </c>
       <c r="AH3">
-        <v>0.6492956599625438</v>
+        <v>0.7643179070023085</v>
       </c>
       <c r="AI3">
-        <v>0.4778856526429342</v>
+        <v>0.4744132096069869</v>
       </c>
       <c r="AJ3">
-        <v>0.4261159227181878</v>
+        <v>0.6690847352986571</v>
       </c>
       <c r="AK3">
-        <v>0.2685138539042821</v>
+        <v>0.3601096527662402</v>
       </c>
       <c r="AL3">
-        <v>21.1</v>
+        <v>67.5</v>
       </c>
       <c r="AM3">
-        <v>-7.299999999999997</v>
+        <v>30</v>
       </c>
       <c r="AN3">
-        <v>14.82156133828996</v>
+        <v>4.114201183431953</v>
       </c>
       <c r="AO3">
-        <v>-0.7440758293838862</v>
+        <v>1.211851851851852</v>
       </c>
       <c r="AP3">
-        <v>5.944237918215613</v>
+        <v>2.565088757396449</v>
       </c>
       <c r="AQ3">
-        <v>2.15068493150685</v>
+        <v>2.726666666666667</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:AQ2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>company_name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>exchange_ticker</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>industry_group</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt_capital</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_capital</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>actual_equity_value</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_equity_value</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>actual_enterprise_value</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_enterprise_value</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_capital</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_capital</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt_rating</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_rating</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_equity</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_equity</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>actual_beta</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_beta</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_error</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>country_default_spread</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>risk_free</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>market_capitalization</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_risk_premium</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>marginal_tax_rate</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_max_percentage</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_method</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_ebitda</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_depreciation</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>reported_capital_spending</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_debt</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_mv_debt</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>reported_interest_expense</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>reported_bv_debt</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>reported_cash</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>flag_bankruptcy</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>flag_refinanced</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>rating_firm_type</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>OPUS GLOBAL Nyrt. (BUSE:OPUS)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>BUSE:OPUS</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Diversified</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Hungary</t>
+        </is>
+      </c>
+      <c r="E2">
+        <v>0.7643179070023089</v>
+      </c>
+      <c r="F2">
+        <v>0.14</v>
+      </c>
+      <c r="G2">
+        <v>214.4</v>
+      </c>
+      <c r="H2">
+        <v>928.59079841633</v>
+      </c>
+      <c r="I2">
+        <v>647.9</v>
+      </c>
+      <c r="J2">
+        <v>794.14879841633</v>
+      </c>
+      <c r="K2">
+        <v>695.3</v>
+      </c>
+      <c r="L2">
+        <v>127.358</v>
+      </c>
+      <c r="M2">
+        <v>0.121540473362318</v>
+      </c>
+      <c r="N2">
+        <v>0.106303159103619</v>
+      </c>
+      <c r="O2">
+        <v>0.06424307798165139</v>
+      </c>
+      <c r="P2">
+        <v>0.041587</v>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="S2">
+        <v>0.30735614037807</v>
+      </c>
+      <c r="T2">
+        <v>0.116838347794906</v>
+      </c>
+      <c r="U2">
+        <v>2.91891630622597</v>
+      </c>
+      <c r="V2">
+        <v>0.848192879033817</v>
+      </c>
+      <c r="W2">
+        <v>13.43582450586491</v>
+      </c>
+      <c r="X2">
+        <v>0</v>
+      </c>
+      <c r="Y2">
+        <v>0</v>
+      </c>
+      <c r="Z2">
+        <v>0.0388</v>
+      </c>
+      <c r="AA2">
+        <v>214.4</v>
+      </c>
+      <c r="AB2">
+        <v>0.09200542674185173</v>
+      </c>
+      <c r="AC2">
+        <v>0.07059678899082569</v>
+      </c>
+      <c r="AD2">
+        <v>0.08999999999999997</v>
+      </c>
+      <c r="AE2">
+        <v>0</v>
+      </c>
+      <c r="AF2">
+        <v>1</v>
+      </c>
+      <c r="AG2">
+        <v>169</v>
+      </c>
+      <c r="AH2">
+        <v>90.8</v>
+      </c>
+      <c r="AI2">
+        <v>273.2</v>
+      </c>
+      <c r="AJ2">
+        <v>695.3</v>
+      </c>
+      <c r="AK2">
+        <v>695.3</v>
+      </c>
+      <c r="AL2">
+        <v>67.5</v>
+      </c>
+      <c r="AM2">
+        <v>695.3</v>
+      </c>
+      <c r="AN2">
+        <v>261.8</v>
+      </c>
+      <c r="AO2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AP2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AQ2">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:Z101"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>debt_capital</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>cost_capital</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>equity_value</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>enterprise_value</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>debt_issued</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>debt</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>marketcap</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>drop_ebitda</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ebitda</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>depreciation</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>ebit</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>interest_expense</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>taxable_income</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>taxes</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>net_income</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>operating_cash_flow</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>debt_equity</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>cost_equity</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>beta</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>tax_rate</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>debt_rating</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_error</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2">
+        <v>0.1067693934612308</v>
+      </c>
+      <c r="C2">
+        <v>1050.501354559284</v>
+      </c>
+      <c r="D2">
+        <v>788.7013545592835</v>
+      </c>
+      <c r="E2">
+        <v>-695.3</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>261.8</v>
+      </c>
+      <c r="H2">
+        <v>214.4</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>169</v>
+      </c>
+      <c r="K2">
+        <v>90.8</v>
+      </c>
+      <c r="L2">
+        <v>78.2</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>78.2</v>
+      </c>
+      <c r="O2">
+        <v>7.037999999999998</v>
+      </c>
+      <c r="P2">
+        <v>71.16200000000001</v>
+      </c>
+      <c r="Q2">
+        <v>161.962</v>
+      </c>
+      <c r="R2">
+        <v>0</v>
+      </c>
+      <c r="S2">
+        <v>0.1067693934612308</v>
+      </c>
+      <c r="T2">
+        <v>0.7387541786196905</v>
+      </c>
+      <c r="U2">
+        <v>0.0457</v>
+      </c>
+      <c r="V2">
+        <v>0.08999999999999997</v>
+      </c>
+      <c r="W2">
+        <v>0.04158700000000001</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y2">
+        <v>10000000</v>
+      </c>
+      <c r="Z2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3">
+        <v>0.01</v>
+      </c>
+      <c r="B3">
+        <v>0.1067360910071157</v>
+      </c>
+      <c r="C3">
+        <v>1041.790978079733</v>
+      </c>
+      <c r="D3">
+        <v>789.0879780797326</v>
+      </c>
+      <c r="E3">
+        <v>-686.203</v>
+      </c>
+      <c r="F3">
+        <v>9.097</v>
+      </c>
+      <c r="G3">
+        <v>261.8</v>
+      </c>
+      <c r="H3">
+        <v>214.4</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>169</v>
+      </c>
+      <c r="K3">
+        <v>90.8</v>
+      </c>
+      <c r="L3">
+        <v>78.2</v>
+      </c>
+      <c r="M3">
+        <v>0.4157329</v>
+      </c>
+      <c r="N3">
+        <v>77.78426710000001</v>
+      </c>
+      <c r="O3">
+        <v>7.000584038999999</v>
+      </c>
+      <c r="P3">
+        <v>70.783683061</v>
+      </c>
+      <c r="Q3">
+        <v>161.583683061</v>
+      </c>
+      <c r="R3">
+        <v>0.0101010101010101</v>
+      </c>
+      <c r="S3">
+        <v>0.1073941626334502</v>
+      </c>
+      <c r="T3">
+        <v>0.7455447473322553</v>
+      </c>
+      <c r="U3">
+        <v>0.0457</v>
+      </c>
+      <c r="V3">
+        <v>0.08999999999999997</v>
+      </c>
+      <c r="W3">
+        <v>0.04158700000000001</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y3">
+        <v>188.1015430821087</v>
+      </c>
+      <c r="Z3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <v>0.02</v>
+      </c>
+      <c r="B4">
+        <v>0.1067027885530006</v>
+      </c>
+      <c r="C4">
+        <v>1033.080980833858</v>
+      </c>
+      <c r="D4">
+        <v>789.4749808338576</v>
+      </c>
+      <c r="E4">
+        <v>-677.106</v>
+      </c>
+      <c r="F4">
+        <v>18.194</v>
+      </c>
+      <c r="G4">
+        <v>261.8</v>
+      </c>
+      <c r="H4">
+        <v>214.4</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>169</v>
+      </c>
+      <c r="K4">
+        <v>90.8</v>
+      </c>
+      <c r="L4">
+        <v>78.2</v>
+      </c>
+      <c r="M4">
+        <v>0.8314658</v>
+      </c>
+      <c r="N4">
+        <v>77.3685342</v>
+      </c>
+      <c r="O4">
+        <v>6.963168077999997</v>
+      </c>
+      <c r="P4">
+        <v>70.405366122</v>
+      </c>
+      <c r="Q4">
+        <v>161.205366122</v>
+      </c>
+      <c r="R4">
+        <v>0.02040816326530612</v>
+      </c>
+      <c r="S4">
+        <v>0.1080316821969394</v>
+      </c>
+      <c r="T4">
+        <v>0.7524738990797706</v>
+      </c>
+      <c r="U4">
+        <v>0.0457</v>
+      </c>
+      <c r="V4">
+        <v>0.08999999999999997</v>
+      </c>
+      <c r="W4">
+        <v>0.04158700000000001</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y4">
+        <v>94.05077154105436</v>
+      </c>
+      <c r="Z4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5">
+        <v>0.03</v>
+      </c>
+      <c r="B5">
+        <v>0.1066694860988855</v>
+      </c>
+      <c r="C5">
+        <v>1024.37136337991</v>
+      </c>
+      <c r="D5">
+        <v>789.86236337991</v>
+      </c>
+      <c r="E5">
+        <v>-668.009</v>
+      </c>
+      <c r="F5">
+        <v>27.291</v>
+      </c>
+      <c r="G5">
+        <v>261.8</v>
+      </c>
+      <c r="H5">
+        <v>214.4</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>169</v>
+      </c>
+      <c r="K5">
+        <v>90.8</v>
+      </c>
+      <c r="L5">
+        <v>78.2</v>
+      </c>
+      <c r="M5">
+        <v>1.2471987</v>
+      </c>
+      <c r="N5">
+        <v>76.9528013</v>
+      </c>
+      <c r="O5">
+        <v>6.925752116999998</v>
+      </c>
+      <c r="P5">
+        <v>70.027049183</v>
+      </c>
+      <c r="Q5">
+        <v>160.827049183</v>
+      </c>
+      <c r="R5">
+        <v>0.03092783505154639</v>
+      </c>
+      <c r="S5">
+        <v>0.1086823464936964</v>
+      </c>
+      <c r="T5">
+        <v>0.7595459199354818</v>
+      </c>
+      <c r="U5">
+        <v>0.0457</v>
+      </c>
+      <c r="V5">
+        <v>0.08999999999999997</v>
+      </c>
+      <c r="W5">
+        <v>0.04158700000000001</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y5">
+        <v>62.70051436070291</v>
+      </c>
+      <c r="Z5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6">
+        <v>0.04</v>
+      </c>
+      <c r="B6">
+        <v>0.1066361836447704</v>
+      </c>
+      <c r="C6">
+        <v>1015.662126277237</v>
+      </c>
+      <c r="D6">
+        <v>790.2501262772371</v>
+      </c>
+      <c r="E6">
+        <v>-658.9119999999999</v>
+      </c>
+      <c r="F6">
+        <v>36.388</v>
+      </c>
+      <c r="G6">
+        <v>261.8</v>
+      </c>
+      <c r="H6">
+        <v>214.4</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>169</v>
+      </c>
+      <c r="K6">
+        <v>90.8</v>
+      </c>
+      <c r="L6">
+        <v>78.2</v>
+      </c>
+      <c r="M6">
+        <v>1.6629316</v>
+      </c>
+      <c r="N6">
+        <v>76.53706840000001</v>
+      </c>
+      <c r="O6">
+        <v>6.888336155999998</v>
+      </c>
+      <c r="P6">
+        <v>69.64873224400002</v>
+      </c>
+      <c r="Q6">
+        <v>160.448732244</v>
+      </c>
+      <c r="R6">
+        <v>0.04166666666666667</v>
+      </c>
+      <c r="S6">
+        <v>0.1093465662966358</v>
+      </c>
+      <c r="T6">
+        <v>0.7667652745590204</v>
+      </c>
+      <c r="U6">
+        <v>0.0457</v>
+      </c>
+      <c r="V6">
+        <v>0.08999999999999997</v>
+      </c>
+      <c r="W6">
+        <v>0.04158700000000001</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y6">
+        <v>47.02538577052719</v>
+      </c>
+      <c r="Z6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7">
+        <v>0.05</v>
+      </c>
+      <c r="B7">
+        <v>0.1066028811906552</v>
+      </c>
+      <c r="C7">
+        <v>1006.953270086286</v>
+      </c>
+      <c r="D7">
+        <v>790.6382700862857</v>
+      </c>
+      <c r="E7">
+        <v>-649.8149999999999</v>
+      </c>
+      <c r="F7">
+        <v>45.485</v>
+      </c>
+      <c r="G7">
+        <v>261.8</v>
+      </c>
+      <c r="H7">
+        <v>214.4</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>169</v>
+      </c>
+      <c r="K7">
+        <v>90.8</v>
+      </c>
+      <c r="L7">
+        <v>78.2</v>
+      </c>
+      <c r="M7">
+        <v>2.0786645</v>
+      </c>
+      <c r="N7">
+        <v>76.1213355</v>
+      </c>
+      <c r="O7">
+        <v>6.850920194999998</v>
+      </c>
+      <c r="P7">
+        <v>69.270415305</v>
+      </c>
+      <c r="Q7">
+        <v>160.070415305</v>
+      </c>
+      <c r="R7">
+        <v>0.05263157894736843</v>
+      </c>
+      <c r="S7">
+        <v>0.1100247696743739</v>
+      </c>
+      <c r="T7">
+        <v>0.7741366155956861</v>
+      </c>
+      <c r="U7">
+        <v>0.0457</v>
+      </c>
+      <c r="V7">
+        <v>0.08999999999999997</v>
+      </c>
+      <c r="W7">
+        <v>0.04158700000000001</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y7">
+        <v>37.62030861642174</v>
+      </c>
+      <c r="Z7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8">
+        <v>0.06</v>
+      </c>
+      <c r="B8">
+        <v>0.1065695787365401</v>
+      </c>
+      <c r="C8">
+        <v>998.2447953686036</v>
+      </c>
+      <c r="D8">
+        <v>791.0267953686036</v>
+      </c>
+      <c r="E8">
+        <v>-640.718</v>
+      </c>
+      <c r="F8">
+        <v>54.58199999999999</v>
+      </c>
+      <c r="G8">
+        <v>261.8</v>
+      </c>
+      <c r="H8">
+        <v>214.4</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>169</v>
+      </c>
+      <c r="K8">
+        <v>90.8</v>
+      </c>
+      <c r="L8">
+        <v>78.2</v>
+      </c>
+      <c r="M8">
+        <v>2.4943974</v>
+      </c>
+      <c r="N8">
+        <v>75.70560260000001</v>
+      </c>
+      <c r="O8">
+        <v>6.813504233999998</v>
+      </c>
+      <c r="P8">
+        <v>68.89209836600001</v>
+      </c>
+      <c r="Q8">
+        <v>159.692098366</v>
+      </c>
+      <c r="R8">
+        <v>0.06382978723404255</v>
+      </c>
+      <c r="S8">
+        <v>0.1107174029112129</v>
+      </c>
+      <c r="T8">
+        <v>0.7816647936756853</v>
+      </c>
+      <c r="U8">
+        <v>0.0457</v>
+      </c>
+      <c r="V8">
+        <v>0.08999999999999997</v>
+      </c>
+      <c r="W8">
+        <v>0.04158700000000001</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y8">
+        <v>31.35025718035146</v>
+      </c>
+      <c r="Z8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="B9">
+        <v>0.106536276282425</v>
+      </c>
+      <c r="C9">
+        <v>989.5367026868443</v>
+      </c>
+      <c r="D9">
+        <v>791.4157026868442</v>
+      </c>
+      <c r="E9">
+        <v>-631.621</v>
+      </c>
+      <c r="F9">
+        <v>63.679</v>
+      </c>
+      <c r="G9">
+        <v>261.8</v>
+      </c>
+      <c r="H9">
+        <v>214.4</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>169</v>
+      </c>
+      <c r="K9">
+        <v>90.8</v>
+      </c>
+      <c r="L9">
+        <v>78.2</v>
+      </c>
+      <c r="M9">
+        <v>2.910130300000001</v>
+      </c>
+      <c r="N9">
+        <v>75.2898697</v>
+      </c>
+      <c r="O9">
+        <v>6.776088272999997</v>
+      </c>
+      <c r="P9">
+        <v>68.513781427</v>
+      </c>
+      <c r="Q9">
+        <v>159.313781427</v>
+      </c>
+      <c r="R9">
+        <v>0.07526881720430109</v>
+      </c>
+      <c r="S9">
+        <v>0.1114249314864785</v>
+      </c>
+      <c r="T9">
+        <v>0.7893548680584801</v>
+      </c>
+      <c r="U9">
+        <v>0.0457</v>
+      </c>
+      <c r="V9">
+        <v>0.08999999999999997</v>
+      </c>
+      <c r="W9">
+        <v>0.04158700000000001</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y9">
+        <v>26.87164901172981</v>
+      </c>
+      <c r="Z9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10">
+        <v>0.08</v>
+      </c>
+      <c r="B10">
+        <v>0.1065029738283099</v>
+      </c>
+      <c r="C10">
+        <v>980.8289926047661</v>
+      </c>
+      <c r="D10">
+        <v>791.8049926047661</v>
+      </c>
+      <c r="E10">
+        <v>-622.524</v>
+      </c>
+      <c r="F10">
+        <v>72.776</v>
+      </c>
+      <c r="G10">
+        <v>261.8</v>
+      </c>
+      <c r="H10">
+        <v>214.4</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>169</v>
+      </c>
+      <c r="K10">
+        <v>90.8</v>
+      </c>
+      <c r="L10">
+        <v>78.2</v>
+      </c>
+      <c r="M10">
+        <v>3.3258632</v>
+      </c>
+      <c r="N10">
+        <v>74.8741368</v>
+      </c>
+      <c r="O10">
+        <v>6.738672311999998</v>
+      </c>
+      <c r="P10">
+        <v>68.13546448800001</v>
+      </c>
+      <c r="Q10">
+        <v>158.935464488</v>
+      </c>
+      <c r="R10">
+        <v>0.08695652173913043</v>
+      </c>
+      <c r="S10">
+        <v>0.1121478411177282</v>
+      </c>
+      <c r="T10">
+        <v>0.7972121179713356</v>
+      </c>
+      <c r="U10">
+        <v>0.0457</v>
+      </c>
+      <c r="V10">
+        <v>0.08999999999999997</v>
+      </c>
+      <c r="W10">
+        <v>0.04158700000000001</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y10">
+        <v>23.51269288526359</v>
+      </c>
+      <c r="Z10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
+        <v>0.09</v>
+      </c>
+      <c r="B11">
+        <v>0.1064696713741948</v>
+      </c>
+      <c r="C11">
+        <v>972.1216656872393</v>
+      </c>
+      <c r="D11">
+        <v>792.1946656872393</v>
+      </c>
+      <c r="E11">
+        <v>-613.4269999999999</v>
+      </c>
+      <c r="F11">
+        <v>81.87299999999999</v>
+      </c>
+      <c r="G11">
+        <v>261.8</v>
+      </c>
+      <c r="H11">
+        <v>214.4</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>169</v>
+      </c>
+      <c r="K11">
+        <v>90.8</v>
+      </c>
+      <c r="L11">
+        <v>78.2</v>
+      </c>
+      <c r="M11">
+        <v>3.7415961</v>
+      </c>
+      <c r="N11">
+        <v>74.45840390000001</v>
+      </c>
+      <c r="O11">
+        <v>6.701256350999999</v>
+      </c>
+      <c r="P11">
+        <v>67.75714754900001</v>
+      </c>
+      <c r="Q11">
+        <v>158.557147549</v>
+      </c>
+      <c r="R11">
+        <v>0.0989010989010989</v>
+      </c>
+      <c r="S11">
+        <v>0.1128866388727416</v>
+      </c>
+      <c r="T11">
+        <v>0.8052420546954627</v>
+      </c>
+      <c r="U11">
+        <v>0.0457</v>
+      </c>
+      <c r="V11">
+        <v>0.08999999999999997</v>
+      </c>
+      <c r="W11">
+        <v>0.04158700000000001</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y11">
+        <v>20.90017145356764</v>
+      </c>
+      <c r="Z11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
+        <v>0.1</v>
+      </c>
+      <c r="B12">
+        <v>0.1064363689200797</v>
+      </c>
+      <c r="C12">
+        <v>963.4147225002457</v>
+      </c>
+      <c r="D12">
+        <v>792.5847225002457</v>
+      </c>
+      <c r="E12">
+        <v>-604.3299999999999</v>
+      </c>
+      <c r="F12">
+        <v>90.97</v>
+      </c>
+      <c r="G12">
+        <v>261.8</v>
+      </c>
+      <c r="H12">
+        <v>214.4</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>169</v>
+      </c>
+      <c r="K12">
+        <v>90.8</v>
+      </c>
+      <c r="L12">
+        <v>78.2</v>
+      </c>
+      <c r="M12">
+        <v>4.157329000000001</v>
+      </c>
+      <c r="N12">
+        <v>74.042671</v>
+      </c>
+      <c r="O12">
+        <v>6.663840389999997</v>
+      </c>
+      <c r="P12">
+        <v>67.37883060999999</v>
+      </c>
+      <c r="Q12">
+        <v>158.17883061</v>
+      </c>
+      <c r="R12">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="S12">
+        <v>0.1136418543556441</v>
+      </c>
+      <c r="T12">
+        <v>0.8134504344579037</v>
+      </c>
+      <c r="U12">
+        <v>0.0457</v>
+      </c>
+      <c r="V12">
+        <v>0.08999999999999997</v>
+      </c>
+      <c r="W12">
+        <v>0.04158700000000001</v>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y12">
+        <v>18.81015430821087</v>
+      </c>
+      <c r="Z12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13">
+        <v>0.11</v>
+      </c>
+      <c r="B13">
+        <v>0.1064030664659646</v>
+      </c>
+      <c r="C13">
+        <v>954.7081636108821</v>
+      </c>
+      <c r="D13">
+        <v>792.9751636108821</v>
+      </c>
+      <c r="E13">
+        <v>-595.2329999999999</v>
+      </c>
+      <c r="F13">
+        <v>100.067</v>
+      </c>
+      <c r="G13">
+        <v>261.8</v>
+      </c>
+      <c r="H13">
+        <v>214.4</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>169</v>
+      </c>
+      <c r="K13">
+        <v>90.8</v>
+      </c>
+      <c r="L13">
+        <v>78.2</v>
+      </c>
+      <c r="M13">
+        <v>4.5730619</v>
+      </c>
+      <c r="N13">
+        <v>73.6269381</v>
+      </c>
+      <c r="O13">
+        <v>6.626424428999998</v>
+      </c>
+      <c r="P13">
+        <v>67.00051367100001</v>
+      </c>
+      <c r="Q13">
+        <v>157.800513671</v>
+      </c>
+      <c r="R13">
+        <v>0.1235955056179775</v>
+      </c>
+      <c r="S13">
+        <v>0.1144140409729939</v>
+      </c>
+      <c r="T13">
+        <v>0.8218432721925343</v>
+      </c>
+      <c r="U13">
+        <v>0.0457</v>
+      </c>
+      <c r="V13">
+        <v>0.08999999999999997</v>
+      </c>
+      <c r="W13">
+        <v>0.04158700000000001</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y13">
+        <v>17.1001402801917</v>
+      </c>
+      <c r="Z13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14">
+        <v>0.12</v>
+      </c>
+      <c r="B14">
+        <v>0.1063697640118495</v>
+      </c>
+      <c r="C14">
+        <v>946.0019895873641</v>
+      </c>
+      <c r="D14">
+        <v>793.365989587364</v>
+      </c>
+      <c r="E14">
+        <v>-586.136</v>
+      </c>
+      <c r="F14">
+        <v>109.164</v>
+      </c>
+      <c r="G14">
+        <v>261.8</v>
+      </c>
+      <c r="H14">
+        <v>214.4</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>169</v>
+      </c>
+      <c r="K14">
+        <v>90.8</v>
+      </c>
+      <c r="L14">
+        <v>78.2</v>
+      </c>
+      <c r="M14">
+        <v>4.9887948</v>
+      </c>
+      <c r="N14">
+        <v>73.21120520000001</v>
+      </c>
+      <c r="O14">
+        <v>6.589008467999999</v>
+      </c>
+      <c r="P14">
+        <v>66.62219673200001</v>
+      </c>
+      <c r="Q14">
+        <v>157.422196732</v>
+      </c>
+      <c r="R14">
+        <v>0.1363636363636364</v>
+      </c>
+      <c r="S14">
+        <v>0.1152037772861926</v>
+      </c>
+      <c r="T14">
+        <v>0.8304268562393157</v>
+      </c>
+      <c r="U14">
+        <v>0.0457</v>
+      </c>
+      <c r="V14">
+        <v>0.08999999999999997</v>
+      </c>
+      <c r="W14">
+        <v>0.04158700000000001</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y14">
+        <v>15.67512859017573</v>
+      </c>
+      <c r="Z14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15">
+        <v>0.13</v>
+      </c>
+      <c r="B15">
+        <v>0.1063364615577344</v>
+      </c>
+      <c r="C15">
+        <v>937.296200999027</v>
+      </c>
+      <c r="D15">
+        <v>793.7572009990268</v>
+      </c>
+      <c r="E15">
+        <v>-577.039</v>
+      </c>
+      <c r="F15">
+        <v>118.261</v>
+      </c>
+      <c r="G15">
+        <v>261.8</v>
+      </c>
+      <c r="H15">
+        <v>214.4</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>169</v>
+      </c>
+      <c r="K15">
+        <v>90.8</v>
+      </c>
+      <c r="L15">
+        <v>78.2</v>
+      </c>
+      <c r="M15">
+        <v>5.4045277</v>
+      </c>
+      <c r="N15">
+        <v>72.7954723</v>
+      </c>
+      <c r="O15">
+        <v>6.551592506999998</v>
+      </c>
+      <c r="P15">
+        <v>66.243879793</v>
+      </c>
+      <c r="Q15">
+        <v>157.043879793</v>
+      </c>
+      <c r="R15">
+        <v>0.1494252873563219</v>
+      </c>
+      <c r="S15">
+        <v>0.116011668457166</v>
+      </c>
+      <c r="T15">
+        <v>0.8392077640572875</v>
+      </c>
+      <c r="U15">
+        <v>0.0457</v>
+      </c>
+      <c r="V15">
+        <v>0.08999999999999997</v>
+      </c>
+      <c r="W15">
+        <v>0.04158700000000001</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y15">
+        <v>14.46934946785452</v>
+      </c>
+      <c r="Z15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16">
+        <v>0.14</v>
+      </c>
+      <c r="B16">
+        <v>0.1063031591036193</v>
+      </c>
+      <c r="C16">
+        <v>928.5907984163305</v>
+      </c>
+      <c r="D16">
+        <v>794.1487984163304</v>
+      </c>
+      <c r="E16">
+        <v>-567.942</v>
+      </c>
+      <c r="F16">
+        <v>127.358</v>
+      </c>
+      <c r="G16">
+        <v>261.8</v>
+      </c>
+      <c r="H16">
+        <v>214.4</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>169</v>
+      </c>
+      <c r="K16">
+        <v>90.8</v>
+      </c>
+      <c r="L16">
+        <v>78.2</v>
+      </c>
+      <c r="M16">
+        <v>5.820260600000001</v>
+      </c>
+      <c r="N16">
+        <v>72.37973940000001</v>
+      </c>
+      <c r="O16">
+        <v>6.514176545999998</v>
+      </c>
+      <c r="P16">
+        <v>65.865562854</v>
+      </c>
+      <c r="Q16">
+        <v>156.665562854</v>
+      </c>
+      <c r="R16">
+        <v>0.1627906976744186</v>
+      </c>
+      <c r="S16">
+        <v>0.1168383477949061</v>
+      </c>
+      <c r="T16">
+        <v>0.8481928790338167</v>
+      </c>
+      <c r="U16">
+        <v>0.0457</v>
+      </c>
+      <c r="V16">
+        <v>0.08999999999999997</v>
+      </c>
+      <c r="W16">
+        <v>0.04158700000000001</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y16">
+        <v>13.43582450586491</v>
+      </c>
+      <c r="Z16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17">
+        <v>0.15</v>
+      </c>
+      <c r="B17">
+        <v>0.1064882566495042</v>
+      </c>
+      <c r="C17">
+        <v>917.322151502517</v>
+      </c>
+      <c r="D17">
+        <v>791.977151502517</v>
+      </c>
+      <c r="E17">
+        <v>-558.845</v>
+      </c>
+      <c r="F17">
+        <v>136.455</v>
+      </c>
+      <c r="G17">
+        <v>261.8</v>
+      </c>
+      <c r="H17">
+        <v>214.4</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>169</v>
+      </c>
+      <c r="K17">
+        <v>90.8</v>
+      </c>
+      <c r="L17">
+        <v>78.2</v>
+      </c>
+      <c r="M17">
+        <v>6.4543215</v>
+      </c>
+      <c r="N17">
+        <v>71.7456785</v>
+      </c>
+      <c r="O17">
+        <v>6.457111064999998</v>
+      </c>
+      <c r="P17">
+        <v>65.288567435</v>
+      </c>
+      <c r="Q17">
+        <v>156.088567435</v>
+      </c>
+      <c r="R17">
+        <v>0.1764705882352941</v>
+      </c>
+      <c r="S17">
+        <v>0.1176844784111814</v>
+      </c>
+      <c r="T17">
+        <v>0.857389408480382</v>
+      </c>
+      <c r="U17">
+        <v>0.0473</v>
+      </c>
+      <c r="V17">
+        <v>0.08999999999999997</v>
+      </c>
+      <c r="W17">
+        <v>0.043043</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y17">
+        <v>12.11591334581025</v>
+      </c>
+      <c r="Z17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18">
+        <v>0.16</v>
+      </c>
+      <c r="B18">
+        <v>0.1064695141953891</v>
+      </c>
+      <c r="C18">
+        <v>908.4445057508627</v>
+      </c>
+      <c r="D18">
+        <v>792.1965057508628</v>
+      </c>
+      <c r="E18">
+        <v>-549.7479999999999</v>
+      </c>
+      <c r="F18">
+        <v>145.552</v>
+      </c>
+      <c r="G18">
+        <v>261.8</v>
+      </c>
+      <c r="H18">
+        <v>214.4</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>169</v>
+      </c>
+      <c r="K18">
+        <v>90.8</v>
+      </c>
+      <c r="L18">
+        <v>78.2</v>
+      </c>
+      <c r="M18">
+        <v>6.8846096</v>
+      </c>
+      <c r="N18">
+        <v>71.3153904</v>
+      </c>
+      <c r="O18">
+        <v>6.418385135999998</v>
+      </c>
+      <c r="P18">
+        <v>64.897005264</v>
+      </c>
+      <c r="Q18">
+        <v>155.697005264</v>
+      </c>
+      <c r="R18">
+        <v>0.1904761904761905</v>
+      </c>
+      <c r="S18">
+        <v>0.1185507549945108</v>
+      </c>
+      <c r="T18">
+        <v>0.8668049029137702</v>
+      </c>
+      <c r="U18">
+        <v>0.0473</v>
+      </c>
+      <c r="V18">
+        <v>0.08999999999999997</v>
+      </c>
+      <c r="W18">
+        <v>0.043043</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y18">
+        <v>11.35866876169711</v>
+      </c>
+      <c r="Z18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19">
+        <v>0.17</v>
+      </c>
+      <c r="B19">
+        <v>0.106450771741274</v>
+      </c>
+      <c r="C19">
+        <v>899.566981542151</v>
+      </c>
+      <c r="D19">
+        <v>792.415981542151</v>
+      </c>
+      <c r="E19">
+        <v>-540.651</v>
+      </c>
+      <c r="F19">
+        <v>154.649</v>
+      </c>
+      <c r="G19">
+        <v>261.8</v>
+      </c>
+      <c r="H19">
+        <v>214.4</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>169</v>
+      </c>
+      <c r="K19">
+        <v>90.8</v>
+      </c>
+      <c r="L19">
+        <v>78.2</v>
+      </c>
+      <c r="M19">
+        <v>7.3148977</v>
+      </c>
+      <c r="N19">
+        <v>70.8851023</v>
+      </c>
+      <c r="O19">
+        <v>6.379659206999998</v>
+      </c>
+      <c r="P19">
+        <v>64.505443093</v>
+      </c>
+      <c r="Q19">
+        <v>155.305443093</v>
+      </c>
+      <c r="R19">
+        <v>0.2048192771084338</v>
+      </c>
+      <c r="S19">
+        <v>0.1194379057123783</v>
+      </c>
+      <c r="T19">
+        <v>0.8764472767310955</v>
+      </c>
+      <c r="U19">
+        <v>0.0473</v>
+      </c>
+      <c r="V19">
+        <v>0.08999999999999997</v>
+      </c>
+      <c r="W19">
+        <v>0.043043</v>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y19">
+        <v>10.69051177571492</v>
+      </c>
+      <c r="Z19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20">
+        <v>0.18</v>
+      </c>
+      <c r="B20">
+        <v>0.1070544692871589</v>
+      </c>
+      <c r="C20">
+        <v>883.4612158397273</v>
+      </c>
+      <c r="D20">
+        <v>785.4072158397273</v>
+      </c>
+      <c r="E20">
+        <v>-531.554</v>
+      </c>
+      <c r="F20">
+        <v>163.746</v>
+      </c>
+      <c r="G20">
+        <v>261.8</v>
+      </c>
+      <c r="H20">
+        <v>214.4</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>169</v>
+      </c>
+      <c r="K20">
+        <v>90.8</v>
+      </c>
+      <c r="L20">
+        <v>78.2</v>
+      </c>
+      <c r="M20">
+        <v>8.367420599999999</v>
+      </c>
+      <c r="N20">
+        <v>69.8325794</v>
+      </c>
+      <c r="O20">
+        <v>6.284932145999998</v>
+      </c>
+      <c r="P20">
+        <v>63.547647254</v>
+      </c>
+      <c r="Q20">
+        <v>154.347647254</v>
+      </c>
+      <c r="R20">
+        <v>0.2195121951219512</v>
+      </c>
+      <c r="S20">
+        <v>0.1203466942526327</v>
+      </c>
+      <c r="T20">
+        <v>0.8863248303976238</v>
+      </c>
+      <c r="U20">
+        <v>0.0511</v>
+      </c>
+      <c r="V20">
+        <v>0.08999999999999997</v>
+      </c>
+      <c r="W20">
+        <v>0.046501</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y20">
+        <v>9.345771383836018</v>
+      </c>
+      <c r="Z20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21">
+        <v>0.19</v>
+      </c>
+      <c r="B21">
+        <v>0.1070703068330437</v>
+      </c>
+      <c r="C21">
+        <v>874.1820147717052</v>
+      </c>
+      <c r="D21">
+        <v>785.2250147717051</v>
+      </c>
+      <c r="E21">
+        <v>-522.457</v>
+      </c>
+      <c r="F21">
+        <v>172.843</v>
+      </c>
+      <c r="G21">
+        <v>261.8</v>
+      </c>
+      <c r="H21">
+        <v>214.4</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>169</v>
+      </c>
+      <c r="K21">
+        <v>90.8</v>
+      </c>
+      <c r="L21">
+        <v>78.2</v>
+      </c>
+      <c r="M21">
+        <v>8.832277299999999</v>
+      </c>
+      <c r="N21">
+        <v>69.3677227</v>
+      </c>
+      <c r="O21">
+        <v>6.243095042999998</v>
+      </c>
+      <c r="P21">
+        <v>63.124627657</v>
+      </c>
+      <c r="Q21">
+        <v>153.924627657</v>
+      </c>
+      <c r="R21">
+        <v>0.2345679012345679</v>
+      </c>
+      <c r="S21">
+        <v>0.1212779220161034</v>
+      </c>
+      <c r="T21">
+        <v>0.8964462742781405</v>
+      </c>
+      <c r="U21">
+        <v>0.0511</v>
+      </c>
+      <c r="V21">
+        <v>0.08999999999999997</v>
+      </c>
+      <c r="W21">
+        <v>0.046501</v>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y21">
+        <v>8.853888679423596</v>
+      </c>
+      <c r="Z21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22">
+        <v>0.2</v>
+      </c>
+      <c r="B22">
+        <v>0.1070861443789286</v>
+      </c>
+      <c r="C22">
+        <v>864.9028982191523</v>
+      </c>
+      <c r="D22">
+        <v>785.0428982191523</v>
+      </c>
+      <c r="E22">
+        <v>-513.3599999999999</v>
+      </c>
+      <c r="F22">
+        <v>181.94</v>
+      </c>
+      <c r="G22">
+        <v>261.8</v>
+      </c>
+      <c r="H22">
+        <v>214.4</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>169</v>
+      </c>
+      <c r="K22">
+        <v>90.8</v>
+      </c>
+      <c r="L22">
+        <v>78.2</v>
+      </c>
+      <c r="M22">
+        <v>9.297134</v>
+      </c>
+      <c r="N22">
+        <v>68.902866</v>
+      </c>
+      <c r="O22">
+        <v>6.201257939999998</v>
+      </c>
+      <c r="P22">
+        <v>62.70160806000001</v>
+      </c>
+      <c r="Q22">
+        <v>153.50160806</v>
+      </c>
+      <c r="R22">
+        <v>0.25</v>
+      </c>
+      <c r="S22">
+        <v>0.1222324304736608</v>
+      </c>
+      <c r="T22">
+        <v>0.9068207542556701</v>
+      </c>
+      <c r="U22">
+        <v>0.0511</v>
+      </c>
+      <c r="V22">
+        <v>0.08999999999999997</v>
+      </c>
+      <c r="W22">
+        <v>0.046501</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y22">
+        <v>8.411194245452418</v>
+      </c>
+      <c r="Z22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23">
+        <v>0.21</v>
+      </c>
+      <c r="B23">
+        <v>0.1071019819248135</v>
+      </c>
+      <c r="C23">
+        <v>855.6238661232778</v>
+      </c>
+      <c r="D23">
+        <v>784.8608661232779</v>
+      </c>
+      <c r="E23">
+        <v>-504.263</v>
+      </c>
+      <c r="F23">
+        <v>191.037</v>
+      </c>
+      <c r="G23">
+        <v>261.8</v>
+      </c>
+      <c r="H23">
+        <v>214.4</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>169</v>
+      </c>
+      <c r="K23">
+        <v>90.8</v>
+      </c>
+      <c r="L23">
+        <v>78.2</v>
+      </c>
+      <c r="M23">
+        <v>9.761990699999998</v>
+      </c>
+      <c r="N23">
+        <v>68.4380093</v>
+      </c>
+      <c r="O23">
+        <v>6.159420836999998</v>
+      </c>
+      <c r="P23">
+        <v>62.27858846300001</v>
+      </c>
+      <c r="Q23">
+        <v>153.078588463</v>
+      </c>
+      <c r="R23">
+        <v>0.2658227848101266</v>
+      </c>
+      <c r="S23">
+        <v>0.1232111037022956</v>
+      </c>
+      <c r="T23">
+        <v>0.9174578792959219</v>
+      </c>
+      <c r="U23">
+        <v>0.0511</v>
+      </c>
+      <c r="V23">
+        <v>0.08999999999999997</v>
+      </c>
+      <c r="W23">
+        <v>0.046501</v>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y23">
+        <v>8.01066118614516</v>
+      </c>
+      <c r="Z23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24">
+        <v>0.22</v>
+      </c>
+      <c r="B24">
+        <v>0.1074981994706984</v>
+      </c>
+      <c r="C24">
+        <v>842.000173304071</v>
+      </c>
+      <c r="D24">
+        <v>780.334173304071</v>
+      </c>
+      <c r="E24">
+        <v>-495.1659999999999</v>
+      </c>
+      <c r="F24">
+        <v>200.134</v>
+      </c>
+      <c r="G24">
+        <v>261.8</v>
+      </c>
+      <c r="H24">
+        <v>214.4</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>169</v>
+      </c>
+      <c r="K24">
+        <v>90.8</v>
+      </c>
+      <c r="L24">
+        <v>78.2</v>
+      </c>
+      <c r="M24">
+        <v>10.607102</v>
+      </c>
+      <c r="N24">
+        <v>67.59289800000001</v>
+      </c>
+      <c r="O24">
+        <v>6.083360819999998</v>
+      </c>
+      <c r="P24">
+        <v>61.50953718000001</v>
+      </c>
+      <c r="Q24">
+        <v>152.30953718</v>
+      </c>
+      <c r="R24">
+        <v>0.282051282051282</v>
+      </c>
+      <c r="S24">
+        <v>0.12421487111628</v>
+      </c>
+      <c r="T24">
+        <v>0.9283677511320777</v>
+      </c>
+      <c r="U24">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V24">
+        <v>0.08999999999999997</v>
+      </c>
+      <c r="W24">
+        <v>0.04823000000000001</v>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y24">
+        <v>7.372418969856234</v>
+      </c>
+      <c r="Z24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25">
+        <v>0.23</v>
+      </c>
+      <c r="B25">
+        <v>0.1075313270165833</v>
+      </c>
+      <c r="C25">
+        <v>832.5270630606963</v>
+      </c>
+      <c r="D25">
+        <v>779.9580630606962</v>
+      </c>
+      <c r="E25">
+        <v>-486.069</v>
+      </c>
+      <c r="F25">
+        <v>209.231</v>
+      </c>
+      <c r="G25">
+        <v>261.8</v>
+      </c>
+      <c r="H25">
+        <v>214.4</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>169</v>
+      </c>
+      <c r="K25">
+        <v>90.8</v>
+      </c>
+      <c r="L25">
+        <v>78.2</v>
+      </c>
+      <c r="M25">
+        <v>11.089243</v>
+      </c>
+      <c r="N25">
+        <v>67.11075700000001</v>
+      </c>
+      <c r="O25">
+        <v>6.039968129999998</v>
+      </c>
+      <c r="P25">
+        <v>61.07078887000001</v>
+      </c>
+      <c r="Q25">
+        <v>151.87078887</v>
+      </c>
+      <c r="R25">
+        <v>0.2987012987012987</v>
+      </c>
+      <c r="S25">
+        <v>0.1252447104111472</v>
+      </c>
+      <c r="T25">
+        <v>0.9395609962626791</v>
+      </c>
+      <c r="U25">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V25">
+        <v>0.08999999999999997</v>
+      </c>
+      <c r="W25">
+        <v>0.04823000000000001</v>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y25">
+        <v>7.051879014645094</v>
+      </c>
+      <c r="Z25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26">
+        <v>0.24</v>
+      </c>
+      <c r="B26">
+        <v>0.1075644545624682</v>
+      </c>
+      <c r="C26">
+        <v>823.0543152024934</v>
+      </c>
+      <c r="D26">
+        <v>779.5823152024934</v>
+      </c>
+      <c r="E26">
+        <v>-476.972</v>
+      </c>
+      <c r="F26">
+        <v>218.328</v>
+      </c>
+      <c r="G26">
+        <v>261.8</v>
+      </c>
+      <c r="H26">
+        <v>214.4</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <v>169</v>
+      </c>
+      <c r="K26">
+        <v>90.8</v>
+      </c>
+      <c r="L26">
+        <v>78.2</v>
+      </c>
+      <c r="M26">
+        <v>11.571384</v>
+      </c>
+      <c r="N26">
+        <v>66.62861600000001</v>
+      </c>
+      <c r="O26">
+        <v>5.996575439999999</v>
+      </c>
+      <c r="P26">
+        <v>60.63204056000001</v>
+      </c>
+      <c r="Q26">
+        <v>151.43204056</v>
+      </c>
+      <c r="R26">
+        <v>0.3157894736842105</v>
+      </c>
+      <c r="S26">
+        <v>0.1263016507400897</v>
+      </c>
+      <c r="T26">
+        <v>0.9510488004756646</v>
+      </c>
+      <c r="U26">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V26">
+        <v>0.08999999999999997</v>
+      </c>
+      <c r="W26">
+        <v>0.04823000000000001</v>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y26">
+        <v>6.758050722368215</v>
+      </c>
+      <c r="Z26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27">
+        <v>0.25</v>
+      </c>
+      <c r="B27">
+        <v>0.1075975821083531</v>
+      </c>
+      <c r="C27">
+        <v>813.5819292059734</v>
+      </c>
+      <c r="D27">
+        <v>779.2069292059734</v>
+      </c>
+      <c r="E27">
+        <v>-467.875</v>
+      </c>
+      <c r="F27">
+        <v>227.425</v>
+      </c>
+      <c r="G27">
+        <v>261.8</v>
+      </c>
+      <c r="H27">
+        <v>214.4</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <v>169</v>
+      </c>
+      <c r="K27">
+        <v>90.8</v>
+      </c>
+      <c r="L27">
+        <v>78.2</v>
+      </c>
+      <c r="M27">
+        <v>12.053525</v>
+      </c>
+      <c r="N27">
+        <v>66.14647500000001</v>
+      </c>
+      <c r="O27">
+        <v>5.953182749999999</v>
+      </c>
+      <c r="P27">
+        <v>60.19329225000001</v>
+      </c>
+      <c r="Q27">
+        <v>150.99329225</v>
+      </c>
+      <c r="R27">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="S27">
+        <v>0.1273867761444708</v>
+      </c>
+      <c r="T27">
+        <v>0.9628429461343299</v>
+      </c>
+      <c r="U27">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V27">
+        <v>0.08999999999999997</v>
+      </c>
+      <c r="W27">
+        <v>0.04823000000000001</v>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y27">
+        <v>6.487728693473486</v>
+      </c>
+      <c r="Z27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28">
+        <v>0.26</v>
+      </c>
+      <c r="B28">
+        <v>0.107630709654238</v>
+      </c>
+      <c r="C28">
+        <v>804.1099045486546</v>
+      </c>
+      <c r="D28">
+        <v>778.8319045486545</v>
+      </c>
+      <c r="E28">
+        <v>-458.778</v>
+      </c>
+      <c r="F28">
+        <v>236.522</v>
+      </c>
+      <c r="G28">
+        <v>261.8</v>
+      </c>
+      <c r="H28">
+        <v>214.4</v>
+      </c>
+      <c r="I28">
+        <v>0</v>
+      </c>
+      <c r="J28">
+        <v>169</v>
+      </c>
+      <c r="K28">
+        <v>90.8</v>
+      </c>
+      <c r="L28">
+        <v>78.2</v>
+      </c>
+      <c r="M28">
+        <v>12.535666</v>
+      </c>
+      <c r="N28">
+        <v>65.664334</v>
+      </c>
+      <c r="O28">
+        <v>5.909790059999998</v>
+      </c>
+      <c r="P28">
+        <v>59.75454394</v>
+      </c>
+      <c r="Q28">
+        <v>150.55454394</v>
+      </c>
+      <c r="R28">
+        <v>0.3513513513513514</v>
+      </c>
+      <c r="S28">
+        <v>0.1285012292624838</v>
+      </c>
+      <c r="T28">
+        <v>0.9749558524864727</v>
+      </c>
+      <c r="U28">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V28">
+        <v>0.08999999999999997</v>
+      </c>
+      <c r="W28">
+        <v>0.04823000000000001</v>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y28">
+        <v>6.238200666801428</v>
+      </c>
+      <c r="Z28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29">
+        <v>0.27</v>
+      </c>
+      <c r="B29">
+        <v>0.1081552372001229</v>
+      </c>
+      <c r="C29">
+        <v>789.1226675017969</v>
+      </c>
+      <c r="D29">
+        <v>772.9416675017968</v>
+      </c>
+      <c r="E29">
+        <v>-449.6809999999999</v>
+      </c>
+      <c r="F29">
+        <v>245.619</v>
+      </c>
+      <c r="G29">
+        <v>261.8</v>
+      </c>
+      <c r="H29">
+        <v>214.4</v>
+      </c>
+      <c r="I29">
+        <v>0</v>
+      </c>
+      <c r="J29">
+        <v>169</v>
+      </c>
+      <c r="K29">
+        <v>90.8</v>
+      </c>
+      <c r="L29">
+        <v>78.2</v>
+      </c>
+      <c r="M29">
+        <v>13.509045</v>
+      </c>
+      <c r="N29">
+        <v>64.690955</v>
+      </c>
+      <c r="O29">
+        <v>5.822185949999998</v>
+      </c>
+      <c r="P29">
+        <v>58.86876905</v>
+      </c>
+      <c r="Q29">
+        <v>149.66876905</v>
+      </c>
+      <c r="R29">
+        <v>0.3698630136986302</v>
+      </c>
+      <c r="S29">
+        <v>0.1296462153426341</v>
+      </c>
+      <c r="T29">
+        <v>0.9874006192866192</v>
+      </c>
+      <c r="U29">
+        <v>0.055</v>
+      </c>
+      <c r="V29">
+        <v>0.08999999999999997</v>
+      </c>
+      <c r="W29">
+        <v>0.05005</v>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y29">
+        <v>5.788714154109339</v>
+      </c>
+      <c r="Z29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30">
+        <v>0.28</v>
+      </c>
+      <c r="B30">
+        <v>0.1082065647460078</v>
+      </c>
+      <c r="C30">
+        <v>779.4540616450564</v>
+      </c>
+      <c r="D30">
+        <v>772.3700616450565</v>
+      </c>
+      <c r="E30">
+        <v>-440.5839999999999</v>
+      </c>
+      <c r="F30">
+        <v>254.716</v>
+      </c>
+      <c r="G30">
+        <v>261.8</v>
+      </c>
+      <c r="H30">
+        <v>214.4</v>
+      </c>
+      <c r="I30">
+        <v>0</v>
+      </c>
+      <c r="J30">
+        <v>169</v>
+      </c>
+      <c r="K30">
+        <v>90.8</v>
+      </c>
+      <c r="L30">
+        <v>78.2</v>
+      </c>
+      <c r="M30">
+        <v>14.00938</v>
+      </c>
+      <c r="N30">
+        <v>64.19062</v>
+      </c>
+      <c r="O30">
+        <v>5.777155799999997</v>
+      </c>
+      <c r="P30">
+        <v>58.4134642</v>
+      </c>
+      <c r="Q30">
+        <v>149.2134642</v>
+      </c>
+      <c r="R30">
+        <v>0.388888888888889</v>
+      </c>
+      <c r="S30">
+        <v>0.1308230065916774</v>
+      </c>
+      <c r="T30">
+        <v>1.000191074053437</v>
+      </c>
+      <c r="U30">
+        <v>0.055</v>
+      </c>
+      <c r="V30">
+        <v>0.08999999999999997</v>
+      </c>
+      <c r="W30">
+        <v>0.05005</v>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y30">
+        <v>5.581974362891148</v>
+      </c>
+      <c r="Z30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31">
+        <v>0.29</v>
+      </c>
+      <c r="B31">
+        <v>0.1082578922918926</v>
+      </c>
+      <c r="C31">
+        <v>769.7863005915452</v>
+      </c>
+      <c r="D31">
+        <v>771.7993005915451</v>
+      </c>
+      <c r="E31">
+        <v>-431.487</v>
+      </c>
+      <c r="F31">
+        <v>263.813</v>
+      </c>
+      <c r="G31">
+        <v>261.8</v>
+      </c>
+      <c r="H31">
+        <v>214.4</v>
+      </c>
+      <c r="I31">
+        <v>0</v>
+      </c>
+      <c r="J31">
+        <v>169</v>
+      </c>
+      <c r="K31">
+        <v>90.8</v>
+      </c>
+      <c r="L31">
+        <v>78.2</v>
+      </c>
+      <c r="M31">
+        <v>14.509715</v>
+      </c>
+      <c r="N31">
+        <v>63.690285</v>
+      </c>
+      <c r="O31">
+        <v>5.732125649999999</v>
+      </c>
+      <c r="P31">
+        <v>57.95815935</v>
+      </c>
+      <c r="Q31">
+        <v>148.75815935</v>
+      </c>
+      <c r="R31">
+        <v>0.4084507042253521</v>
+      </c>
+      <c r="S31">
+        <v>0.1320329468899896</v>
+      </c>
+      <c r="T31">
+        <v>1.013341823320727</v>
+      </c>
+      <c r="U31">
+        <v>0.055</v>
+      </c>
+      <c r="V31">
+        <v>0.08999999999999997</v>
+      </c>
+      <c r="W31">
+        <v>0.05005</v>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y31">
+        <v>5.389492488308695</v>
+      </c>
+      <c r="Z31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32">
+        <v>0.3</v>
+      </c>
+      <c r="B32">
+        <v>0.1083092198377776</v>
+      </c>
+      <c r="C32">
+        <v>760.1193824697835</v>
+      </c>
+      <c r="D32">
+        <v>771.2293824697834</v>
+      </c>
+      <c r="E32">
+        <v>-422.39</v>
+      </c>
+      <c r="F32">
+        <v>272.91</v>
+      </c>
+      <c r="G32">
+        <v>261.8</v>
+      </c>
+      <c r="H32">
+        <v>214.4</v>
+      </c>
+      <c r="I32">
+        <v>0</v>
+      </c>
+      <c r="J32">
+        <v>169</v>
+      </c>
+      <c r="K32">
+        <v>90.8</v>
+      </c>
+      <c r="L32">
+        <v>78.2</v>
+      </c>
+      <c r="M32">
+        <v>15.01005</v>
+      </c>
+      <c r="N32">
+        <v>63.18995</v>
+      </c>
+      <c r="O32">
+        <v>5.687095499999998</v>
+      </c>
+      <c r="P32">
+        <v>57.50285450000001</v>
+      </c>
+      <c r="Q32">
+        <v>148.3028545</v>
+      </c>
+      <c r="R32">
+        <v>0.4285714285714286</v>
+      </c>
+      <c r="S32">
+        <v>0.1332774569111108</v>
+      </c>
+      <c r="T32">
+        <v>1.02686830828137</v>
+      </c>
+      <c r="U32">
+        <v>0.055</v>
+      </c>
+      <c r="V32">
+        <v>0.08999999999999997</v>
+      </c>
+      <c r="W32">
+        <v>0.05005</v>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y32">
+        <v>5.209842738698407</v>
+      </c>
+      <c r="Z32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33">
+        <v>0.31</v>
+      </c>
+      <c r="B33">
+        <v>0.1083605473836624</v>
+      </c>
+      <c r="C33">
+        <v>750.4533054138176</v>
+      </c>
+      <c r="D33">
+        <v>770.6603054138177</v>
+      </c>
+      <c r="E33">
+        <v>-413.2929999999999</v>
+      </c>
+      <c r="F33">
+        <v>282.007</v>
+      </c>
+      <c r="G33">
+        <v>261.8</v>
+      </c>
+      <c r="H33">
+        <v>214.4</v>
+      </c>
+      <c r="I33">
+        <v>0</v>
+      </c>
+      <c r="J33">
+        <v>169</v>
+      </c>
+      <c r="K33">
+        <v>90.8</v>
+      </c>
+      <c r="L33">
+        <v>78.2</v>
+      </c>
+      <c r="M33">
+        <v>15.510385</v>
+      </c>
+      <c r="N33">
+        <v>62.689615</v>
+      </c>
+      <c r="O33">
+        <v>5.642065349999998</v>
+      </c>
+      <c r="P33">
+        <v>57.04754965000001</v>
+      </c>
+      <c r="Q33">
+        <v>147.84754965</v>
+      </c>
+      <c r="R33">
+        <v>0.4492753623188406</v>
+      </c>
+      <c r="S33">
+        <v>0.1345580396864673</v>
+      </c>
+      <c r="T33">
+        <v>1.040786865269857</v>
+      </c>
+      <c r="U33">
+        <v>0.055</v>
+      </c>
+      <c r="V33">
+        <v>0.08999999999999997</v>
+      </c>
+      <c r="W33">
+        <v>0.05005</v>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y33">
+        <v>5.041783295514586</v>
+      </c>
+      <c r="Z33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34">
+        <v>0.32</v>
+      </c>
+      <c r="B34">
+        <v>0.1084118749295473</v>
+      </c>
+      <c r="C34">
+        <v>740.7880675631945</v>
+      </c>
+      <c r="D34">
+        <v>770.0920675631946</v>
+      </c>
+      <c r="E34">
+        <v>-404.196</v>
+      </c>
+      <c r="F34">
+        <v>291.104</v>
+      </c>
+      <c r="G34">
+        <v>261.8</v>
+      </c>
+      <c r="H34">
+        <v>214.4</v>
+      </c>
+      <c r="I34">
+        <v>0</v>
+      </c>
+      <c r="J34">
+        <v>169</v>
+      </c>
+      <c r="K34">
+        <v>90.8</v>
+      </c>
+      <c r="L34">
+        <v>78.2</v>
+      </c>
+      <c r="M34">
+        <v>16.01072</v>
+      </c>
+      <c r="N34">
+        <v>62.18928</v>
+      </c>
+      <c r="O34">
+        <v>5.597035199999999</v>
+      </c>
+      <c r="P34">
+        <v>56.5922448</v>
+      </c>
+      <c r="Q34">
+        <v>147.3922448</v>
+      </c>
+      <c r="R34">
+        <v>0.4705882352941177</v>
+      </c>
+      <c r="S34">
+        <v>0.135876286661099</v>
+      </c>
+      <c r="T34">
+        <v>1.055114791581534</v>
+      </c>
+      <c r="U34">
+        <v>0.055</v>
+      </c>
+      <c r="V34">
+        <v>0.08999999999999997</v>
+      </c>
+      <c r="W34">
+        <v>0.05005</v>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y34">
+        <v>4.884227567529756</v>
+      </c>
+      <c r="Z34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35">
+        <v>0.33</v>
+      </c>
+      <c r="B35">
+        <v>0.1084632024754322</v>
+      </c>
+      <c r="C35">
+        <v>731.1236670629464</v>
+      </c>
+      <c r="D35">
+        <v>769.5246670629465</v>
+      </c>
+      <c r="E35">
+        <v>-395.099</v>
+      </c>
+      <c r="F35">
+        <v>300.201</v>
+      </c>
+      <c r="G35">
+        <v>261.8</v>
+      </c>
+      <c r="H35">
+        <v>214.4</v>
+      </c>
+      <c r="I35">
+        <v>0</v>
+      </c>
+      <c r="J35">
+        <v>169</v>
+      </c>
+      <c r="K35">
+        <v>90.8</v>
+      </c>
+      <c r="L35">
+        <v>78.2</v>
+      </c>
+      <c r="M35">
+        <v>16.511055</v>
+      </c>
+      <c r="N35">
+        <v>61.688945</v>
+      </c>
+      <c r="O35">
+        <v>5.552005049999998</v>
+      </c>
+      <c r="P35">
+        <v>56.13693995000001</v>
+      </c>
+      <c r="Q35">
+        <v>146.93693995</v>
+      </c>
+      <c r="R35">
+        <v>0.4925373134328359</v>
+      </c>
+      <c r="S35">
+        <v>0.1372338842916899</v>
+      </c>
+      <c r="T35">
+        <v>1.069870417186098</v>
+      </c>
+      <c r="U35">
+        <v>0.055</v>
+      </c>
+      <c r="V35">
+        <v>0.08999999999999997</v>
+      </c>
+      <c r="W35">
+        <v>0.05005</v>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y35">
+        <v>4.736220671544006</v>
+      </c>
+      <c r="Z35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36">
+        <v>0.34</v>
+      </c>
+      <c r="B36">
+        <v>0.1085145300213171</v>
+      </c>
+      <c r="C36">
+        <v>721.4601020635678</v>
+      </c>
+      <c r="D36">
+        <v>768.9581020635677</v>
+      </c>
+      <c r="E36">
+        <v>-386.002</v>
+      </c>
+      <c r="F36">
+        <v>309.298</v>
+      </c>
+      <c r="G36">
+        <v>261.8</v>
+      </c>
+      <c r="H36">
+        <v>214.4</v>
+      </c>
+      <c r="I36">
+        <v>0</v>
+      </c>
+      <c r="J36">
+        <v>169</v>
+      </c>
+      <c r="K36">
+        <v>90.8</v>
+      </c>
+      <c r="L36">
+        <v>78.2</v>
+      </c>
+      <c r="M36">
+        <v>17.01139</v>
+      </c>
+      <c r="N36">
+        <v>61.18861</v>
+      </c>
+      <c r="O36">
+        <v>5.506974899999999</v>
+      </c>
+      <c r="P36">
+        <v>55.68163510000001</v>
+      </c>
+      <c r="Q36">
+        <v>146.4816351</v>
+      </c>
+      <c r="R36">
+        <v>0.5151515151515152</v>
+      </c>
+      <c r="S36">
+        <v>0.1386326212444199</v>
+      </c>
+      <c r="T36">
+        <v>1.085073182960497</v>
+      </c>
+      <c r="U36">
+        <v>0.055</v>
+      </c>
+      <c r="V36">
+        <v>0.08999999999999997</v>
+      </c>
+      <c r="W36">
+        <v>0.05005</v>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y36">
+        <v>4.596920063557417</v>
+      </c>
+      <c r="Z36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37">
+        <v>0.35</v>
+      </c>
+      <c r="B37">
+        <v>0.109776157567202</v>
+      </c>
+      <c r="C37">
+        <v>698.6945863753774</v>
+      </c>
+      <c r="D37">
+        <v>755.2895863753773</v>
+      </c>
+      <c r="E37">
+        <v>-376.905</v>
+      </c>
+      <c r="F37">
+        <v>318.395</v>
+      </c>
+      <c r="G37">
+        <v>261.8</v>
+      </c>
+      <c r="H37">
+        <v>214.4</v>
+      </c>
+      <c r="I37">
+        <v>0</v>
+      </c>
+      <c r="J37">
+        <v>169</v>
+      </c>
+      <c r="K37">
+        <v>90.8</v>
+      </c>
+      <c r="L37">
+        <v>78.2</v>
+      </c>
+      <c r="M37">
+        <v>18.721626</v>
+      </c>
+      <c r="N37">
+        <v>59.478374</v>
+      </c>
+      <c r="O37">
+        <v>5.353053659999999</v>
+      </c>
+      <c r="P37">
+        <v>54.12532034</v>
+      </c>
+      <c r="Q37">
+        <v>144.92532034</v>
+      </c>
+      <c r="R37">
+        <v>0.5384615384615385</v>
+      </c>
+      <c r="S37">
+        <v>0.1400743962572339</v>
+      </c>
+      <c r="T37">
+        <v>1.100743726143339</v>
+      </c>
+      <c r="U37">
+        <v>0.05880000000000001</v>
+      </c>
+      <c r="V37">
+        <v>0.08999999999999997</v>
+      </c>
+      <c r="W37">
+        <v>0.05350800000000001</v>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>Baa2/BBB</t>
+        </is>
+      </c>
+      <c r="Y37">
+        <v>4.176987618489975</v>
+      </c>
+      <c r="Z37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38">
+        <v>0.36</v>
+      </c>
+      <c r="B38">
+        <v>0.1098620651130869</v>
+      </c>
+      <c r="C38">
+        <v>688.6845102538957</v>
+      </c>
+      <c r="D38">
+        <v>754.3765102538957</v>
+      </c>
+      <c r="E38">
+        <v>-367.808</v>
+      </c>
+      <c r="F38">
+        <v>327.492</v>
+      </c>
+      <c r="G38">
+        <v>261.8</v>
+      </c>
+      <c r="H38">
+        <v>214.4</v>
+      </c>
+      <c r="I38">
+        <v>0</v>
+      </c>
+      <c r="J38">
+        <v>169</v>
+      </c>
+      <c r="K38">
+        <v>90.8</v>
+      </c>
+      <c r="L38">
+        <v>78.2</v>
+      </c>
+      <c r="M38">
+        <v>19.2565296</v>
+      </c>
+      <c r="N38">
+        <v>58.9434704</v>
+      </c>
+      <c r="O38">
+        <v>5.304912335999998</v>
+      </c>
+      <c r="P38">
+        <v>53.638558064</v>
+      </c>
+      <c r="Q38">
+        <v>144.438558064</v>
+      </c>
+      <c r="R38">
+        <v>0.5625</v>
+      </c>
+      <c r="S38">
+        <v>0.1415612267391983</v>
+      </c>
+      <c r="T38">
+        <v>1.116903973800645</v>
+      </c>
+      <c r="U38">
+        <v>0.05880000000000001</v>
+      </c>
+      <c r="V38">
+        <v>0.08999999999999997</v>
+      </c>
+      <c r="W38">
+        <v>0.05350800000000001</v>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>Baa2/BBB</t>
+        </is>
+      </c>
+      <c r="Y38">
+        <v>4.060960184643031</v>
+      </c>
+      <c r="Z38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39">
+        <v>0.37</v>
+      </c>
+      <c r="B39">
+        <v>0.1113621126589718</v>
+      </c>
+      <c r="C39">
+        <v>663.9925862444768</v>
+      </c>
+      <c r="D39">
+        <v>738.7815862444767</v>
+      </c>
+      <c r="E39">
+        <v>-358.711</v>
+      </c>
+      <c r="F39">
+        <v>336.589</v>
+      </c>
+      <c r="G39">
+        <v>261.8</v>
+      </c>
+      <c r="H39">
+        <v>214.4</v>
+      </c>
+      <c r="I39">
+        <v>0</v>
+      </c>
+      <c r="J39">
+        <v>169</v>
+      </c>
+      <c r="K39">
+        <v>90.8</v>
+      </c>
+      <c r="L39">
+        <v>78.2</v>
+      </c>
+      <c r="M39">
+        <v>21.205107</v>
+      </c>
+      <c r="N39">
+        <v>56.994893</v>
+      </c>
+      <c r="O39">
+        <v>5.129540369999999</v>
+      </c>
+      <c r="P39">
+        <v>51.86535263</v>
+      </c>
+      <c r="Q39">
+        <v>142.66535263</v>
+      </c>
+      <c r="R39">
+        <v>0.5873015873015873</v>
+      </c>
+      <c r="S39">
+        <v>0.1430952581888441</v>
+      </c>
+      <c r="T39">
+        <v>1.133577245193103</v>
+      </c>
+      <c r="U39">
+        <v>0.063</v>
+      </c>
+      <c r="V39">
+        <v>0.08999999999999997</v>
+      </c>
+      <c r="W39">
+        <v>0.05733</v>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y39">
+        <v>3.687790870378536</v>
+      </c>
+      <c r="Z39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40">
+        <v>0.38</v>
+      </c>
+      <c r="B40">
+        <v>0.1114862402048567</v>
+      </c>
+      <c r="C40">
+        <v>653.6339561892282</v>
+      </c>
+      <c r="D40">
+        <v>737.5199561892282</v>
+      </c>
+      <c r="E40">
+        <v>-349.614</v>
+      </c>
+      <c r="F40">
+        <v>345.686</v>
+      </c>
+      <c r="G40">
+        <v>261.8</v>
+      </c>
+      <c r="H40">
+        <v>214.4</v>
+      </c>
+      <c r="I40">
+        <v>0</v>
+      </c>
+      <c r="J40">
+        <v>169</v>
+      </c>
+      <c r="K40">
+        <v>90.8</v>
+      </c>
+      <c r="L40">
+        <v>78.2</v>
+      </c>
+      <c r="M40">
+        <v>21.778218</v>
+      </c>
+      <c r="N40">
+        <v>56.42178200000001</v>
+      </c>
+      <c r="O40">
+        <v>5.077960379999999</v>
+      </c>
+      <c r="P40">
+        <v>51.34382162000001</v>
+      </c>
+      <c r="Q40">
+        <v>142.14382162</v>
+      </c>
+      <c r="R40">
+        <v>0.6129032258064516</v>
+      </c>
+      <c r="S40">
+        <v>0.1446787745239624</v>
+      </c>
+      <c r="T40">
+        <v>1.150788364049834</v>
+      </c>
+      <c r="U40">
+        <v>0.063</v>
+      </c>
+      <c r="V40">
+        <v>0.08999999999999997</v>
+      </c>
+      <c r="W40">
+        <v>0.05733</v>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y40">
+        <v>3.590743742210681</v>
+      </c>
+      <c r="Z40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41">
+        <v>0.39</v>
+      </c>
+      <c r="B41">
+        <v>0.1141301577507416</v>
+      </c>
+      <c r="C41">
+        <v>618.6516798161044</v>
+      </c>
+      <c r="D41">
+        <v>711.6346798161043</v>
+      </c>
+      <c r="E41">
+        <v>-340.517</v>
+      </c>
+      <c r="F41">
+        <v>354.783</v>
+      </c>
+      <c r="G41">
+        <v>261.8</v>
+      </c>
+      <c r="H41">
+        <v>214.4</v>
+      </c>
+      <c r="I41">
+        <v>0</v>
+      </c>
+      <c r="J41">
+        <v>169</v>
+      </c>
+      <c r="K41">
+        <v>90.8</v>
+      </c>
+      <c r="L41">
+        <v>78.2</v>
+      </c>
+      <c r="M41">
+        <v>24.8702883</v>
+      </c>
+      <c r="N41">
+        <v>53.3297117</v>
+      </c>
+      <c r="O41">
+        <v>4.799674052999999</v>
+      </c>
+      <c r="P41">
+        <v>48.53003764700001</v>
+      </c>
+      <c r="Q41">
+        <v>139.330037647</v>
+      </c>
+      <c r="R41">
+        <v>0.639344262295082</v>
+      </c>
+      <c r="S41">
+        <v>0.1463142094274452</v>
+      </c>
+      <c r="T41">
+        <v>1.168563781885474</v>
+      </c>
+      <c r="U41">
+        <v>0.0701</v>
+      </c>
+      <c r="V41">
+        <v>0.08999999999999997</v>
+      </c>
+      <c r="W41">
+        <v>0.063791</v>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>Ba2/BB</t>
+        </is>
+      </c>
+      <c r="Y41">
+        <v>3.144314173471001</v>
+      </c>
+      <c r="Z41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42">
+        <v>0.4</v>
+      </c>
+      <c r="B42">
+        <v>0.1143188952966265</v>
+      </c>
+      <c r="C42">
+        <v>607.7761556135519</v>
+      </c>
+      <c r="D42">
+        <v>709.8561556135519</v>
+      </c>
+      <c r="E42">
+        <v>-331.42</v>
+      </c>
+      <c r="F42">
+        <v>363.88</v>
+      </c>
+      <c r="G42">
+        <v>261.8</v>
+      </c>
+      <c r="H42">
+        <v>214.4</v>
+      </c>
+      <c r="I42">
+        <v>0</v>
+      </c>
+      <c r="J42">
+        <v>169</v>
+      </c>
+      <c r="K42">
+        <v>90.8</v>
+      </c>
+      <c r="L42">
+        <v>78.2</v>
+      </c>
+      <c r="M42">
+        <v>25.507988</v>
+      </c>
+      <c r="N42">
+        <v>52.69201200000001</v>
+      </c>
+      <c r="O42">
+        <v>4.742281079999999</v>
+      </c>
+      <c r="P42">
+        <v>47.94973092000001</v>
+      </c>
+      <c r="Q42">
+        <v>138.74973092</v>
+      </c>
+      <c r="R42">
+        <v>0.6666666666666667</v>
+      </c>
+      <c r="S42">
+        <v>0.1480041588277108</v>
+      </c>
+      <c r="T42">
+        <v>1.18693171364897</v>
+      </c>
+      <c r="U42">
+        <v>0.0701</v>
+      </c>
+      <c r="V42">
+        <v>0.08999999999999997</v>
+      </c>
+      <c r="W42">
+        <v>0.063791</v>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>Ba2/BB</t>
+        </is>
+      </c>
+      <c r="Y42">
+        <v>3.065706319134226</v>
+      </c>
+      <c r="Z42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43">
+        <v>0.41</v>
+      </c>
+      <c r="B43">
+        <v>0.1224546628425114</v>
+      </c>
+      <c r="C43">
+        <v>529.642661091306</v>
+      </c>
+      <c r="D43">
+        <v>640.819661091306</v>
+      </c>
+      <c r="E43">
+        <v>-322.323</v>
+      </c>
+      <c r="F43">
+        <v>372.977</v>
+      </c>
+      <c r="G43">
+        <v>261.8</v>
+      </c>
+      <c r="H43">
+        <v>214.4</v>
+      </c>
+      <c r="I43">
+        <v>0</v>
+      </c>
+      <c r="J43">
+        <v>169</v>
+      </c>
+      <c r="K43">
+        <v>90.8</v>
+      </c>
+      <c r="L43">
+        <v>78.2</v>
+      </c>
+      <c r="M43">
+        <v>34.0900978</v>
+      </c>
+      <c r="N43">
+        <v>44.1099022</v>
+      </c>
+      <c r="O43">
+        <v>3.969891197999999</v>
+      </c>
+      <c r="P43">
+        <v>40.140011002</v>
+      </c>
+      <c r="Q43">
+        <v>130.940011002</v>
+      </c>
+      <c r="R43">
+        <v>0.6949152542372882</v>
+      </c>
+      <c r="S43">
+        <v>0.1497513946483244</v>
+      </c>
+      <c r="T43">
+        <v>1.205922287167159</v>
+      </c>
+      <c r="U43">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V43">
+        <v>0.08999999999999997</v>
+      </c>
+      <c r="W43">
+        <v>0.08317400000000001</v>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y43">
+        <v>2.293921257098887</v>
+      </c>
+      <c r="Z43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44">
+        <v>0.42</v>
+      </c>
+      <c r="B44">
+        <v>0.1228372303883963</v>
+      </c>
+      <c r="C44">
+        <v>517.6284206733932</v>
+      </c>
+      <c r="D44">
+        <v>637.9024206733931</v>
+      </c>
+      <c r="E44">
+        <v>-313.226</v>
+      </c>
+      <c r="F44">
+        <v>382.074</v>
+      </c>
+      <c r="G44">
+        <v>261.8</v>
+      </c>
+      <c r="H44">
+        <v>214.4</v>
+      </c>
+      <c r="I44">
+        <v>0</v>
+      </c>
+      <c r="J44">
+        <v>169</v>
+      </c>
+      <c r="K44">
+        <v>90.8</v>
+      </c>
+      <c r="L44">
+        <v>78.2</v>
+      </c>
+      <c r="M44">
+        <v>34.9215636</v>
+      </c>
+      <c r="N44">
+        <v>43.2784364</v>
+      </c>
+      <c r="O44">
+        <v>3.895059275999999</v>
+      </c>
+      <c r="P44">
+        <v>39.38337712400001</v>
+      </c>
+      <c r="Q44">
+        <v>130.183377124</v>
+      </c>
+      <c r="R44">
+        <v>0.7241379310344827</v>
+      </c>
+      <c r="S44">
+        <v>0.1515588799799936</v>
+      </c>
+      <c r="T44">
+        <v>1.225567708048045</v>
+      </c>
+      <c r="U44">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V44">
+        <v>0.08999999999999997</v>
+      </c>
+      <c r="W44">
+        <v>0.08317400000000001</v>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y44">
+        <v>2.239304084310819</v>
+      </c>
+      <c r="Z44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45">
+        <v>0.43</v>
+      </c>
+      <c r="B45">
+        <v>0.1232197979342812</v>
+      </c>
+      <c r="C45">
+        <v>505.640620534532</v>
+      </c>
+      <c r="D45">
+        <v>635.0116205345321</v>
+      </c>
+      <c r="E45">
+        <v>-304.129</v>
+      </c>
+      <c r="F45">
+        <v>391.171</v>
+      </c>
+      <c r="G45">
+        <v>261.8</v>
+      </c>
+      <c r="H45">
+        <v>214.4</v>
+      </c>
+      <c r="I45">
+        <v>0</v>
+      </c>
+      <c r="J45">
+        <v>169</v>
+      </c>
+      <c r="K45">
+        <v>90.8</v>
+      </c>
+      <c r="L45">
+        <v>78.2</v>
+      </c>
+      <c r="M45">
+        <v>35.7530294</v>
+      </c>
+      <c r="N45">
+        <v>42.4469706</v>
+      </c>
+      <c r="O45">
+        <v>3.820227353999999</v>
+      </c>
+      <c r="P45">
+        <v>38.626743246</v>
+      </c>
+      <c r="Q45">
+        <v>129.426743246</v>
+      </c>
+      <c r="R45">
+        <v>0.7543859649122806</v>
+      </c>
+      <c r="S45">
+        <v>0.1534297858496161</v>
+      </c>
+      <c r="T45">
+        <v>1.245902441942295</v>
+      </c>
+      <c r="U45">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V45">
+        <v>0.08999999999999997</v>
+      </c>
+      <c r="W45">
+        <v>0.08317400000000001</v>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y45">
+        <v>2.187227245140799</v>
+      </c>
+      <c r="Z45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46">
+        <v>0.44</v>
+      </c>
+      <c r="B46">
+        <v>0.1236023654801661</v>
+      </c>
+      <c r="C46">
+        <v>493.678902835907</v>
+      </c>
+      <c r="D46">
+        <v>632.146902835907</v>
+      </c>
+      <c r="E46">
+        <v>-295.032</v>
+      </c>
+      <c r="F46">
+        <v>400.268</v>
+      </c>
+      <c r="G46">
+        <v>261.8</v>
+      </c>
+      <c r="H46">
+        <v>214.4</v>
+      </c>
+      <c r="I46">
+        <v>0</v>
+      </c>
+      <c r="J46">
+        <v>169</v>
+      </c>
+      <c r="K46">
+        <v>90.8</v>
+      </c>
+      <c r="L46">
+        <v>78.2</v>
+      </c>
+      <c r="M46">
+        <v>36.5844952</v>
+      </c>
+      <c r="N46">
+        <v>41.6155048</v>
+      </c>
+      <c r="O46">
+        <v>3.745395431999999</v>
+      </c>
+      <c r="P46">
+        <v>37.870109368</v>
+      </c>
+      <c r="Q46">
+        <v>128.670109368</v>
+      </c>
+      <c r="R46">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="S46">
+        <v>0.1553675097860108</v>
+      </c>
+      <c r="T46">
+        <v>1.266963416332769</v>
+      </c>
+      <c r="U46">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V46">
+        <v>0.08999999999999997</v>
+      </c>
+      <c r="W46">
+        <v>0.08317400000000001</v>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y46">
+        <v>2.137517535023963</v>
+      </c>
+      <c r="Z46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47">
+        <v>0.45</v>
+      </c>
+      <c r="B47">
+        <v>0.123984933026051</v>
+      </c>
+      <c r="C47">
+        <v>481.7429161669534</v>
+      </c>
+      <c r="D47">
+        <v>629.3079161669534</v>
+      </c>
+      <c r="E47">
+        <v>-285.935</v>
+      </c>
+      <c r="F47">
+        <v>409.365</v>
+      </c>
+      <c r="G47">
+        <v>261.8</v>
+      </c>
+      <c r="H47">
+        <v>214.4</v>
+      </c>
+      <c r="I47">
+        <v>0</v>
+      </c>
+      <c r="J47">
+        <v>169</v>
+      </c>
+      <c r="K47">
+        <v>90.8</v>
+      </c>
+      <c r="L47">
+        <v>78.2</v>
+      </c>
+      <c r="M47">
+        <v>37.415961</v>
+      </c>
+      <c r="N47">
+        <v>40.78403900000001</v>
+      </c>
+      <c r="O47">
+        <v>3.67056351</v>
+      </c>
+      <c r="P47">
+        <v>37.11347549000001</v>
+      </c>
+      <c r="Q47">
+        <v>127.91347549</v>
+      </c>
+      <c r="R47">
+        <v>0.8181818181818181</v>
+      </c>
+      <c r="S47">
+        <v>0.1573756964110017</v>
+      </c>
+      <c r="T47">
+        <v>1.288790244337442</v>
+      </c>
+      <c r="U47">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V47">
+        <v>0.08999999999999997</v>
+      </c>
+      <c r="W47">
+        <v>0.08317400000000001</v>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y47">
+        <v>2.090017145356764</v>
+      </c>
+      <c r="Z47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48">
+        <v>0.46</v>
+      </c>
+      <c r="B48">
+        <v>0.1243675005719359</v>
+      </c>
+      <c r="C48">
+        <v>469.8323154016543</v>
+      </c>
+      <c r="D48">
+        <v>626.4943154016544</v>
+      </c>
+      <c r="E48">
+        <v>-276.838</v>
+      </c>
+      <c r="F48">
+        <v>418.462</v>
+      </c>
+      <c r="G48">
+        <v>261.8</v>
+      </c>
+      <c r="H48">
+        <v>214.4</v>
+      </c>
+      <c r="I48">
+        <v>0</v>
+      </c>
+      <c r="J48">
+        <v>169</v>
+      </c>
+      <c r="K48">
+        <v>90.8</v>
+      </c>
+      <c r="L48">
+        <v>78.2</v>
+      </c>
+      <c r="M48">
+        <v>38.2474268</v>
+      </c>
+      <c r="N48">
+        <v>39.9525732</v>
+      </c>
+      <c r="O48">
+        <v>3.595731587999999</v>
+      </c>
+      <c r="P48">
+        <v>36.356841612</v>
+      </c>
+      <c r="Q48">
+        <v>127.156841612</v>
+      </c>
+      <c r="R48">
+        <v>0.8518518518518519</v>
+      </c>
+      <c r="S48">
+        <v>0.1594582603183997</v>
+      </c>
+      <c r="T48">
+        <v>1.311425473379325</v>
+      </c>
+      <c r="U48">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V48">
+        <v>0.08999999999999997</v>
+      </c>
+      <c r="W48">
+        <v>0.08317400000000001</v>
+      </c>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y48">
+        <v>2.044581990022921</v>
+      </c>
+      <c r="Z48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49">
+        <v>0.47</v>
+      </c>
+      <c r="B49">
+        <v>0.1247500681178207</v>
+      </c>
+      <c r="C49">
+        <v>457.9467615586777</v>
+      </c>
+      <c r="D49">
+        <v>623.7057615586778</v>
+      </c>
+      <c r="E49">
+        <v>-267.741</v>
+      </c>
+      <c r="F49">
+        <v>427.559</v>
+      </c>
+      <c r="G49">
+        <v>261.8</v>
+      </c>
+      <c r="H49">
+        <v>214.4</v>
+      </c>
+      <c r="I49">
+        <v>0</v>
+      </c>
+      <c r="J49">
+        <v>169</v>
+      </c>
+      <c r="K49">
+        <v>90.8</v>
+      </c>
+      <c r="L49">
+        <v>78.2</v>
+      </c>
+      <c r="M49">
+        <v>39.0788926</v>
+      </c>
+      <c r="N49">
+        <v>39.1211074</v>
+      </c>
+      <c r="O49">
+        <v>3.520899665999999</v>
+      </c>
+      <c r="P49">
+        <v>35.600207734</v>
+      </c>
+      <c r="Q49">
+        <v>126.400207734</v>
+      </c>
+      <c r="R49">
+        <v>0.8867924528301887</v>
+      </c>
+      <c r="S49">
+        <v>0.161619411543058</v>
+      </c>
+      <c r="T49">
+        <v>1.334914862007694</v>
+      </c>
+      <c r="U49">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V49">
+        <v>0.08999999999999997</v>
+      </c>
+      <c r="W49">
+        <v>0.08317400000000001</v>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y49">
+        <v>2.001080245554348</v>
+      </c>
+      <c r="Z49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50">
+        <v>0.48</v>
+      </c>
+      <c r="B50">
+        <v>0.1343491156637056</v>
+      </c>
+      <c r="C50">
+        <v>386.1910836812619</v>
+      </c>
+      <c r="D50">
+        <v>561.0470836812619</v>
+      </c>
+      <c r="E50">
+        <v>-258.644</v>
+      </c>
+      <c r="F50">
+        <v>436.6559999999999</v>
+      </c>
+      <c r="G50">
+        <v>261.8</v>
+      </c>
+      <c r="H50">
+        <v>214.4</v>
+      </c>
+      <c r="I50">
+        <v>0</v>
+      </c>
+      <c r="J50">
+        <v>169</v>
+      </c>
+      <c r="K50">
+        <v>90.8</v>
+      </c>
+      <c r="L50">
+        <v>78.2</v>
+      </c>
+      <c r="M50">
+        <v>49.1238</v>
+      </c>
+      <c r="N50">
+        <v>29.07620000000001</v>
+      </c>
+      <c r="O50">
+        <v>2.616858</v>
+      </c>
+      <c r="P50">
+        <v>26.45934200000001</v>
+      </c>
+      <c r="Q50">
+        <v>117.259342</v>
+      </c>
+      <c r="R50">
+        <v>0.923076923076923</v>
+      </c>
+      <c r="S50">
+        <v>0.1638636839686646</v>
+      </c>
+      <c r="T50">
+        <v>1.35930768866023</v>
+      </c>
+      <c r="U50">
+        <v>0.1125</v>
+      </c>
+      <c r="V50">
+        <v>0.08999999999999997</v>
+      </c>
+      <c r="W50">
+        <v>0.102375</v>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y50">
+        <v>1.591896392380069</v>
+      </c>
+      <c r="Z50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51">
+        <v>0.49</v>
+      </c>
+      <c r="B51">
+        <v>0.1349236932095905</v>
+      </c>
+      <c r="C51">
+        <v>373.7404354213624</v>
+      </c>
+      <c r="D51">
+        <v>557.6934354213623</v>
+      </c>
+      <c r="E51">
+        <v>-249.547</v>
+      </c>
+      <c r="F51">
+        <v>445.753</v>
+      </c>
+      <c r="G51">
+        <v>261.8</v>
+      </c>
+      <c r="H51">
+        <v>214.4</v>
+      </c>
+      <c r="I51">
+        <v>0</v>
+      </c>
+      <c r="J51">
+        <v>169</v>
+      </c>
+      <c r="K51">
+        <v>90.8</v>
+      </c>
+      <c r="L51">
+        <v>78.2</v>
+      </c>
+      <c r="M51">
+        <v>50.1472125</v>
+      </c>
+      <c r="N51">
+        <v>28.0527875</v>
+      </c>
+      <c r="O51">
+        <v>2.524750874999999</v>
+      </c>
+      <c r="P51">
+        <v>25.528036625</v>
+      </c>
+      <c r="Q51">
+        <v>116.328036625</v>
+      </c>
+      <c r="R51">
+        <v>0.9607843137254901</v>
+      </c>
+      <c r="S51">
+        <v>0.1661959670776285</v>
+      </c>
+      <c r="T51">
+        <v>1.384657096750122</v>
+      </c>
+      <c r="U51">
+        <v>0.1125</v>
+      </c>
+      <c r="V51">
+        <v>0.08999999999999997</v>
+      </c>
+      <c r="W51">
+        <v>0.102375</v>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y51">
+        <v>1.559408710902924</v>
+      </c>
+      <c r="Z51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52">
+        <v>0.5</v>
+      </c>
+      <c r="B52">
+        <v>0.1354982707554754</v>
+      </c>
+      <c r="C52">
+        <v>361.3296416691368</v>
+      </c>
+      <c r="D52">
+        <v>554.3796416691367</v>
+      </c>
+      <c r="E52">
+        <v>-240.45</v>
+      </c>
+      <c r="F52">
+        <v>454.85</v>
+      </c>
+      <c r="G52">
+        <v>261.8</v>
+      </c>
+      <c r="H52">
+        <v>214.4</v>
+      </c>
+      <c r="I52">
+        <v>0</v>
+      </c>
+      <c r="J52">
+        <v>169</v>
+      </c>
+      <c r="K52">
+        <v>90.8</v>
+      </c>
+      <c r="L52">
+        <v>78.2</v>
+      </c>
+      <c r="M52">
+        <v>51.17062499999999</v>
+      </c>
+      <c r="N52">
+        <v>27.02937500000001</v>
+      </c>
+      <c r="O52">
+        <v>2.43264375</v>
+      </c>
+      <c r="P52">
+        <v>24.59673125000001</v>
+      </c>
+      <c r="Q52">
+        <v>115.39673125</v>
+      </c>
+      <c r="R52">
+        <v>1</v>
+      </c>
+      <c r="S52">
+        <v>0.1686215415109508</v>
+      </c>
+      <c r="T52">
+        <v>1.411020481163609</v>
+      </c>
+      <c r="U52">
+        <v>0.1125</v>
+      </c>
+      <c r="V52">
+        <v>0.08999999999999997</v>
+      </c>
+      <c r="W52">
+        <v>0.102375</v>
+      </c>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y52">
+        <v>1.528220536684866</v>
+      </c>
+      <c r="Z52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53">
+        <v>0.51</v>
+      </c>
+      <c r="B53">
+        <v>0.1768360408360647</v>
+      </c>
+      <c r="C53">
+        <v>186.2121007591373</v>
+      </c>
+      <c r="D53">
+        <v>388.3591007591372</v>
+      </c>
+      <c r="E53">
+        <v>-231.353</v>
+      </c>
+      <c r="F53">
+        <v>463.9469999999999</v>
+      </c>
+      <c r="G53">
+        <v>261.8</v>
+      </c>
+      <c r="H53">
+        <v>214.4</v>
+      </c>
+      <c r="I53">
+        <v>0</v>
+      </c>
+      <c r="J53">
+        <v>169</v>
+      </c>
+      <c r="K53">
+        <v>90.8</v>
+      </c>
+      <c r="L53">
+        <v>78.2</v>
+      </c>
+      <c r="M53">
+        <v>91.21198019999999</v>
+      </c>
+      <c r="N53">
+        <v>-13.01198019999998</v>
+      </c>
+      <c r="O53">
+        <v>-1.171078217999998</v>
+      </c>
+      <c r="P53">
+        <v>-11.84090198199998</v>
+      </c>
+      <c r="Q53">
+        <v>78.95909801800002</v>
+      </c>
+      <c r="R53">
+        <v>1.040816326530612</v>
+      </c>
+      <c r="S53">
+        <v>0.1720544026592485</v>
+      </c>
+      <c r="T53">
+        <v>1.448331988428606</v>
+      </c>
+      <c r="U53">
+        <v>0.1966</v>
+      </c>
+      <c r="V53">
+        <v>0.07716091663143169</v>
+      </c>
+      <c r="W53">
+        <v>0.1814301637902605</v>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y53">
+        <v>0.8573435181270193</v>
+      </c>
+      <c r="Z53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54">
+        <v>0.52</v>
+      </c>
+      <c r="B54">
+        <v>0.1784140408360647</v>
+      </c>
+      <c r="C54">
+        <v>172.7256377987642</v>
+      </c>
+      <c r="D54">
+        <v>383.9696377987642</v>
+      </c>
+      <c r="E54">
+        <v>-222.256</v>
+      </c>
+      <c r="F54">
+        <v>473.044</v>
+      </c>
+      <c r="G54">
+        <v>261.8</v>
+      </c>
+      <c r="H54">
+        <v>214.4</v>
+      </c>
+      <c r="I54">
+        <v>0</v>
+      </c>
+      <c r="J54">
+        <v>169</v>
+      </c>
+      <c r="K54">
+        <v>90.8</v>
+      </c>
+      <c r="L54">
+        <v>78.2</v>
+      </c>
+      <c r="M54">
+        <v>93.00045039999999</v>
+      </c>
+      <c r="N54">
+        <v>-14.80045039999999</v>
+      </c>
+      <c r="O54">
+        <v>-1.332040535999998</v>
+      </c>
+      <c r="P54">
+        <v>-13.46840986399999</v>
+      </c>
+      <c r="Q54">
+        <v>77.331590136</v>
+      </c>
+      <c r="R54">
+        <v>1.083333333333333</v>
+      </c>
+      <c r="S54">
+        <v>0.1748305360479829</v>
+      </c>
+      <c r="T54">
+        <v>1.478505571520868</v>
+      </c>
+      <c r="U54">
+        <v>0.1966</v>
+      </c>
+      <c r="V54">
+        <v>0.075677052850058</v>
+      </c>
+      <c r="W54">
+        <v>0.1817218914096786</v>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y54">
+        <v>0.8408561427784226</v>
+      </c>
+      <c r="Z54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55">
+        <v>0.53</v>
+      </c>
+      <c r="B55">
+        <v>0.1799920408360647</v>
+      </c>
+      <c r="C55">
+        <v>159.3372904617712</v>
+      </c>
+      <c r="D55">
+        <v>379.6782904617712</v>
+      </c>
+      <c r="E55">
+        <v>-213.159</v>
+      </c>
+      <c r="F55">
+        <v>482.141</v>
+      </c>
+      <c r="G55">
+        <v>261.8</v>
+      </c>
+      <c r="H55">
+        <v>214.4</v>
+      </c>
+      <c r="I55">
+        <v>0</v>
+      </c>
+      <c r="J55">
+        <v>169</v>
+      </c>
+      <c r="K55">
+        <v>90.8</v>
+      </c>
+      <c r="L55">
+        <v>78.2</v>
+      </c>
+      <c r="M55">
+        <v>94.7889206</v>
+      </c>
+      <c r="N55">
+        <v>-16.58892059999999</v>
+      </c>
+      <c r="O55">
+        <v>-1.493002853999999</v>
+      </c>
+      <c r="P55">
+        <v>-15.095917746</v>
+      </c>
+      <c r="Q55">
+        <v>75.704082254</v>
+      </c>
+      <c r="R55">
+        <v>1.127659574468085</v>
+      </c>
+      <c r="S55">
+        <v>0.177724802772408</v>
+      </c>
+      <c r="T55">
+        <v>1.509963136872376</v>
+      </c>
+      <c r="U55">
+        <v>0.1966</v>
+      </c>
+      <c r="V55">
+        <v>0.0742491839283588</v>
+      </c>
+      <c r="W55">
+        <v>0.1820026104396847</v>
+      </c>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y55">
+        <v>0.8249909325373203</v>
+      </c>
+      <c r="Z55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56">
+        <v>0.54</v>
+      </c>
+      <c r="B56">
+        <v>0.1815700408360647</v>
+      </c>
+      <c r="C56">
+        <v>146.0438054090238</v>
+      </c>
+      <c r="D56">
+        <v>375.4818054090238</v>
+      </c>
+      <c r="E56">
+        <v>-204.062</v>
+      </c>
+      <c r="F56">
+        <v>491.238</v>
+      </c>
+      <c r="G56">
+        <v>261.8</v>
+      </c>
+      <c r="H56">
+        <v>214.4</v>
+      </c>
+      <c r="I56">
+        <v>0</v>
+      </c>
+      <c r="J56">
+        <v>169</v>
+      </c>
+      <c r="K56">
+        <v>90.8</v>
+      </c>
+      <c r="L56">
+        <v>78.2</v>
+      </c>
+      <c r="M56">
+        <v>96.5773908</v>
+      </c>
+      <c r="N56">
+        <v>-18.3773908</v>
+      </c>
+      <c r="O56">
+        <v>-1.653965171999999</v>
+      </c>
+      <c r="P56">
+        <v>-16.723425628</v>
+      </c>
+      <c r="Q56">
+        <v>74.076574372</v>
+      </c>
+      <c r="R56">
+        <v>1.173913043478261</v>
+      </c>
+      <c r="S56">
+        <v>0.1807449071805039</v>
+      </c>
+      <c r="T56">
+        <v>1.542788422456558</v>
+      </c>
+      <c r="U56">
+        <v>0.1966</v>
+      </c>
+      <c r="V56">
+        <v>0.07287419904079659</v>
+      </c>
+      <c r="W56">
+        <v>0.1822729324685794</v>
+      </c>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y56">
+        <v>0.809713322675518</v>
+      </c>
+      <c r="Z56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57">
+        <v>0.55</v>
+      </c>
+      <c r="B57">
+        <v>0.1928232207327953</v>
+      </c>
+      <c r="C57">
+        <v>109.513511363399</v>
+      </c>
+      <c r="D57">
+        <v>348.0485113633989</v>
+      </c>
+      <c r="E57">
+        <v>-194.965</v>
+      </c>
+      <c r="F57">
+        <v>500.335</v>
+      </c>
+      <c r="G57">
+        <v>261.8</v>
+      </c>
+      <c r="H57">
+        <v>214.4</v>
+      </c>
+      <c r="I57">
+        <v>0</v>
+      </c>
+      <c r="J57">
+        <v>169</v>
+      </c>
+      <c r="K57">
+        <v>90.8</v>
+      </c>
+      <c r="L57">
+        <v>78.2</v>
+      </c>
+      <c r="M57">
+        <v>106.971623</v>
+      </c>
+      <c r="N57">
+        <v>-28.77162299999999</v>
+      </c>
+      <c r="O57">
+        <v>-2.589446069999998</v>
+      </c>
+      <c r="P57">
+        <v>-26.18217692999999</v>
+      </c>
+      <c r="Q57">
+        <v>64.61782307</v>
+      </c>
+      <c r="R57">
+        <v>1.222222222222223</v>
+      </c>
+      <c r="S57">
+        <v>0.1843774159994722</v>
+      </c>
+      <c r="T57">
+        <v>1.582269885100717</v>
+      </c>
+      <c r="U57">
+        <v>0.2138</v>
+      </c>
+      <c r="V57">
+        <v>0.0657931496467993</v>
+      </c>
+      <c r="W57">
+        <v>0.1997334246055143</v>
+      </c>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y57">
+        <v>0.731034996075548</v>
+      </c>
+      <c r="Z57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="B58">
+        <v>0.1945732207327953</v>
+      </c>
+      <c r="C58">
+        <v>96.50643688448235</v>
+      </c>
+      <c r="D58">
+        <v>344.1384368844823</v>
+      </c>
+      <c r="E58">
+        <v>-185.8679999999999</v>
+      </c>
+      <c r="F58">
+        <v>509.432</v>
+      </c>
+      <c r="G58">
+        <v>261.8</v>
+      </c>
+      <c r="H58">
+        <v>214.4</v>
+      </c>
+      <c r="I58">
+        <v>0</v>
+      </c>
+      <c r="J58">
+        <v>169</v>
+      </c>
+      <c r="K58">
+        <v>90.8</v>
+      </c>
+      <c r="L58">
+        <v>78.2</v>
+      </c>
+      <c r="M58">
+        <v>108.9165616</v>
+      </c>
+      <c r="N58">
+        <v>-30.71656159999999</v>
+      </c>
+      <c r="O58">
+        <v>-2.764490543999998</v>
+      </c>
+      <c r="P58">
+        <v>-27.95207105599999</v>
+      </c>
+      <c r="Q58">
+        <v>62.847928944</v>
+      </c>
+      <c r="R58">
+        <v>1.272727272727273</v>
+      </c>
+      <c r="S58">
+        <v>0.1876859936358238</v>
+      </c>
+      <c r="T58">
+        <v>1.618230564307551</v>
+      </c>
+      <c r="U58">
+        <v>0.2138</v>
+      </c>
+      <c r="V58">
+        <v>0.06461827197453503</v>
+      </c>
+      <c r="W58">
+        <v>0.1999846134518444</v>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y58">
+        <v>0.7179807997170562</v>
+      </c>
+      <c r="Z58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59">
+        <v>0.5700000000000001</v>
+      </c>
+      <c r="B59">
+        <v>0.1963232207327953</v>
+      </c>
+      <c r="C59">
+        <v>83.58624014087695</v>
+      </c>
+      <c r="D59">
+        <v>340.3152401408769</v>
+      </c>
+      <c r="E59">
+        <v>-176.771</v>
+      </c>
+      <c r="F59">
+        <v>518.529</v>
+      </c>
+      <c r="G59">
+        <v>261.8</v>
+      </c>
+      <c r="H59">
+        <v>214.4</v>
+      </c>
+      <c r="I59">
+        <v>0</v>
+      </c>
+      <c r="J59">
+        <v>169</v>
+      </c>
+      <c r="K59">
+        <v>90.8</v>
+      </c>
+      <c r="L59">
+        <v>78.2</v>
+      </c>
+      <c r="M59">
+        <v>110.8615002</v>
+      </c>
+      <c r="N59">
+        <v>-32.66150019999999</v>
+      </c>
+      <c r="O59">
+        <v>-2.939535017999998</v>
+      </c>
+      <c r="P59">
+        <v>-29.72196518199999</v>
+      </c>
+      <c r="Q59">
+        <v>61.07803481800001</v>
+      </c>
+      <c r="R59">
+        <v>1.325581395348838</v>
+      </c>
+      <c r="S59">
+        <v>0.1911484586040988</v>
+      </c>
+      <c r="T59">
+        <v>1.655863833244936</v>
+      </c>
+      <c r="U59">
+        <v>0.2138</v>
+      </c>
+      <c r="V59">
+        <v>0.06348461808024494</v>
+      </c>
+      <c r="W59">
+        <v>0.2002269886544436</v>
+      </c>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y59">
+        <v>0.7053846453360552</v>
+      </c>
+      <c r="Z59">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60">
+        <v>0.58</v>
+      </c>
+      <c r="B60">
+        <v>0.1980732207327953</v>
+      </c>
+      <c r="C60">
+        <v>70.75005744898147</v>
+      </c>
+      <c r="D60">
+        <v>336.5760574489814</v>
+      </c>
+      <c r="E60">
+        <v>-167.674</v>
+      </c>
+      <c r="F60">
+        <v>527.626</v>
+      </c>
+      <c r="G60">
+        <v>261.8</v>
+      </c>
+      <c r="H60">
+        <v>214.4</v>
+      </c>
+      <c r="I60">
+        <v>0</v>
+      </c>
+      <c r="J60">
+        <v>169</v>
+      </c>
+      <c r="K60">
+        <v>90.8</v>
+      </c>
+      <c r="L60">
+        <v>78.2</v>
+      </c>
+      <c r="M60">
+        <v>112.8064388</v>
+      </c>
+      <c r="N60">
+        <v>-34.60643879999999</v>
+      </c>
+      <c r="O60">
+        <v>-3.114579491999998</v>
+      </c>
+      <c r="P60">
+        <v>-31.491859308</v>
+      </c>
+      <c r="Q60">
+        <v>59.308140692</v>
+      </c>
+      <c r="R60">
+        <v>1.380952380952381</v>
+      </c>
+      <c r="S60">
+        <v>0.1947758028565773</v>
+      </c>
+      <c r="T60">
+        <v>1.695289162607911</v>
+      </c>
+      <c r="U60">
+        <v>0.2138</v>
+      </c>
+      <c r="V60">
+        <v>0.06239005569955107</v>
+      </c>
+      <c r="W60">
+        <v>0.200461006091436</v>
+      </c>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y60">
+        <v>0.6932228411061232</v>
+      </c>
+      <c r="Z60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61">
+        <v>0.59</v>
+      </c>
+      <c r="B61">
+        <v>0.1998232207327953</v>
+      </c>
+      <c r="C61">
+        <v>57.99514961522186</v>
+      </c>
+      <c r="D61">
+        <v>332.9181496152218</v>
+      </c>
+      <c r="E61">
+        <v>-158.577</v>
+      </c>
+      <c r="F61">
+        <v>536.723</v>
+      </c>
+      <c r="G61">
+        <v>261.8</v>
+      </c>
+      <c r="H61">
+        <v>214.4</v>
+      </c>
+      <c r="I61">
+        <v>0</v>
+      </c>
+      <c r="J61">
+        <v>169</v>
+      </c>
+      <c r="K61">
+        <v>90.8</v>
+      </c>
+      <c r="L61">
+        <v>78.2</v>
+      </c>
+      <c r="M61">
+        <v>114.7513774</v>
+      </c>
+      <c r="N61">
+        <v>-36.55137739999998</v>
+      </c>
+      <c r="O61">
+        <v>-3.289623965999997</v>
+      </c>
+      <c r="P61">
+        <v>-33.26175343399998</v>
+      </c>
+      <c r="Q61">
+        <v>57.53824656600001</v>
+      </c>
+      <c r="R61">
+        <v>1.439024390243902</v>
+      </c>
+      <c r="S61">
+        <v>0.198580090731128</v>
+      </c>
+      <c r="T61">
+        <v>1.736637678769079</v>
+      </c>
+      <c r="U61">
+        <v>0.2138</v>
+      </c>
+      <c r="V61">
+        <v>0.06133259712837224</v>
+      </c>
+      <c r="W61">
+        <v>0.200687090733954</v>
+      </c>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y61">
+        <v>0.6814733014263584</v>
+      </c>
+      <c r="Z61">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62">
+        <v>0.6</v>
+      </c>
+      <c r="B62">
+        <v>0.2015732207327953</v>
+      </c>
+      <c r="C62">
+        <v>45.31889524399423</v>
+      </c>
+      <c r="D62">
+        <v>329.3388952439942</v>
+      </c>
+      <c r="E62">
+        <v>-149.48</v>
+      </c>
+      <c r="F62">
+        <v>545.8199999999999</v>
+      </c>
+      <c r="G62">
+        <v>261.8</v>
+      </c>
+      <c r="H62">
+        <v>214.4</v>
+      </c>
+      <c r="I62">
+        <v>0</v>
+      </c>
+      <c r="J62">
+        <v>169</v>
+      </c>
+      <c r="K62">
+        <v>90.8</v>
+      </c>
+      <c r="L62">
+        <v>78.2</v>
+      </c>
+      <c r="M62">
+        <v>116.696316</v>
+      </c>
+      <c r="N62">
+        <v>-38.49631599999998</v>
+      </c>
+      <c r="O62">
+        <v>-3.464668439999997</v>
+      </c>
+      <c r="P62">
+        <v>-35.03164755999998</v>
+      </c>
+      <c r="Q62">
+        <v>55.76835244000002</v>
+      </c>
+      <c r="R62">
+        <v>1.5</v>
+      </c>
+      <c r="S62">
+        <v>0.2025745929994061</v>
+      </c>
+      <c r="T62">
+        <v>1.780053620738306</v>
+      </c>
+      <c r="U62">
+        <v>0.2138</v>
+      </c>
+      <c r="V62">
+        <v>0.0603103871762327</v>
+      </c>
+      <c r="W62">
+        <v>0.2009056392217214</v>
+      </c>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y62">
+        <v>0.6701154130692525</v>
+      </c>
+      <c r="Z62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63">
+        <v>0.61</v>
+      </c>
+      <c r="B63">
+        <v>0.2033232207327953</v>
+      </c>
+      <c r="C63">
+        <v>32.71878447270046</v>
+      </c>
+      <c r="D63">
+        <v>325.8357844727004</v>
+      </c>
+      <c r="E63">
+        <v>-140.383</v>
+      </c>
+      <c r="F63">
+        <v>554.9169999999999</v>
+      </c>
+      <c r="G63">
+        <v>261.8</v>
+      </c>
+      <c r="H63">
+        <v>214.4</v>
+      </c>
+      <c r="I63">
+        <v>0</v>
+      </c>
+      <c r="J63">
+        <v>169</v>
+      </c>
+      <c r="K63">
+        <v>90.8</v>
+      </c>
+      <c r="L63">
+        <v>78.2</v>
+      </c>
+      <c r="M63">
+        <v>118.6412546</v>
+      </c>
+      <c r="N63">
+        <v>-40.44125459999998</v>
+      </c>
+      <c r="O63">
+        <v>-3.639712913999997</v>
+      </c>
+      <c r="P63">
+        <v>-36.80154168599998</v>
+      </c>
+      <c r="Q63">
+        <v>53.99845831400002</v>
+      </c>
+      <c r="R63">
+        <v>1.564102564102564</v>
+      </c>
+      <c r="S63">
+        <v>0.2067739415378525</v>
+      </c>
+      <c r="T63">
+        <v>1.825696021270058</v>
+      </c>
+      <c r="U63">
+        <v>0.2138</v>
+      </c>
+      <c r="V63">
+        <v>0.05932169230449118</v>
+      </c>
+      <c r="W63">
+        <v>0.2011170221852998</v>
+      </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y63">
+        <v>0.6591299144943467</v>
+      </c>
+      <c r="Z63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64">
+        <v>0.62</v>
+      </c>
+      <c r="B64">
+        <v>0.2050732207327953</v>
+      </c>
+      <c r="C64">
+        <v>20.19241310240875</v>
+      </c>
+      <c r="D64">
+        <v>322.4064131024088</v>
+      </c>
+      <c r="E64">
+        <v>-131.2859999999999</v>
+      </c>
+      <c r="F64">
+        <v>564.014</v>
+      </c>
+      <c r="G64">
+        <v>261.8</v>
+      </c>
+      <c r="H64">
+        <v>214.4</v>
+      </c>
+      <c r="I64">
+        <v>0</v>
+      </c>
+      <c r="J64">
+        <v>169</v>
+      </c>
+      <c r="K64">
+        <v>90.8</v>
+      </c>
+      <c r="L64">
+        <v>78.2</v>
+      </c>
+      <c r="M64">
+        <v>120.5861932</v>
+      </c>
+      <c r="N64">
+        <v>-42.38619319999999</v>
+      </c>
+      <c r="O64">
+        <v>-3.814757387999998</v>
+      </c>
+      <c r="P64">
+        <v>-38.571435812</v>
+      </c>
+      <c r="Q64">
+        <v>52.228564188</v>
+      </c>
+      <c r="R64">
+        <v>1.631578947368421</v>
+      </c>
+      <c r="S64">
+        <v>0.2111943084204276</v>
+      </c>
+      <c r="T64">
+        <v>1.873740653408744</v>
+      </c>
+      <c r="U64">
+        <v>0.2138</v>
+      </c>
+      <c r="V64">
+        <v>0.05836489081570906</v>
+      </c>
+      <c r="W64">
+        <v>0.2013215863436014</v>
+      </c>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y64">
+        <v>0.648498786841212</v>
+      </c>
+      <c r="Z64">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65">
+        <v>0.63</v>
+      </c>
+      <c r="B65">
+        <v>0.2068232207327954</v>
+      </c>
+      <c r="C65">
+        <v>7.737477095298914</v>
+      </c>
+      <c r="D65">
+        <v>319.0484770952989</v>
+      </c>
+      <c r="E65">
+        <v>-122.189</v>
+      </c>
+      <c r="F65">
+        <v>573.111</v>
+      </c>
+      <c r="G65">
+        <v>261.8</v>
+      </c>
+      <c r="H65">
+        <v>214.4</v>
+      </c>
+      <c r="I65">
+        <v>0</v>
+      </c>
+      <c r="J65">
+        <v>169</v>
+      </c>
+      <c r="K65">
+        <v>90.8</v>
+      </c>
+      <c r="L65">
+        <v>78.2</v>
+      </c>
+      <c r="M65">
+        <v>122.5311318</v>
+      </c>
+      <c r="N65">
+        <v>-44.33113179999999</v>
+      </c>
+      <c r="O65">
+        <v>-3.989801861999998</v>
+      </c>
+      <c r="P65">
+        <v>-40.34132993799999</v>
+      </c>
+      <c r="Q65">
+        <v>50.458670062</v>
+      </c>
+      <c r="R65">
+        <v>1.702702702702703</v>
+      </c>
+      <c r="S65">
+        <v>0.2158536140534121</v>
+      </c>
+      <c r="T65">
+        <v>1.924382292690061</v>
+      </c>
+      <c r="U65">
+        <v>0.2138</v>
+      </c>
+      <c r="V65">
+        <v>0.05743846397736447</v>
+      </c>
+      <c r="W65">
+        <v>0.2015196564016395</v>
+      </c>
+      <c r="X65" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y65">
+        <v>0.6382051553040499</v>
+      </c>
+      <c r="Z65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66">
+        <v>0.64</v>
+      </c>
+      <c r="B66">
+        <v>0.2085732207327954</v>
+      </c>
+      <c r="C66">
+        <v>-4.648232587575762</v>
+      </c>
+      <c r="D66">
+        <v>315.7597674124242</v>
+      </c>
+      <c r="E66">
+        <v>-113.092</v>
+      </c>
+      <c r="F66">
+        <v>582.208</v>
+      </c>
+      <c r="G66">
+        <v>261.8</v>
+      </c>
+      <c r="H66">
+        <v>214.4</v>
+      </c>
+      <c r="I66">
+        <v>0</v>
+      </c>
+      <c r="J66">
+        <v>169</v>
+      </c>
+      <c r="K66">
+        <v>90.8</v>
+      </c>
+      <c r="L66">
+        <v>78.2</v>
+      </c>
+      <c r="M66">
+        <v>124.4760704</v>
+      </c>
+      <c r="N66">
+        <v>-46.27607039999998</v>
+      </c>
+      <c r="O66">
+        <v>-4.164846335999997</v>
+      </c>
+      <c r="P66">
+        <v>-42.11122406399998</v>
+      </c>
+      <c r="Q66">
+        <v>48.68877593600001</v>
+      </c>
+      <c r="R66">
+        <v>1.777777777777778</v>
+      </c>
+      <c r="S66">
+        <v>0.2207717699993402</v>
+      </c>
+      <c r="T66">
+        <v>1.977837356375896</v>
+      </c>
+      <c r="U66">
+        <v>0.2138</v>
+      </c>
+      <c r="V66">
+        <v>0.05654098797771816</v>
+      </c>
+      <c r="W66">
+        <v>0.2017115367703639</v>
+      </c>
+      <c r="X66" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y66">
+        <v>0.6282331997524242</v>
+      </c>
+      <c r="Z66">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67">
+        <v>0.65</v>
+      </c>
+      <c r="B67">
+        <v>0.2103232207327953</v>
+      </c>
+      <c r="C67">
+        <v>-16.96683483251343</v>
+      </c>
+      <c r="D67">
+        <v>312.5381651674865</v>
+      </c>
+      <c r="E67">
+        <v>-103.995</v>
+      </c>
+      <c r="F67">
+        <v>591.3049999999999</v>
+      </c>
+      <c r="G67">
+        <v>261.8</v>
+      </c>
+      <c r="H67">
+        <v>214.4</v>
+      </c>
+      <c r="I67">
+        <v>0</v>
+      </c>
+      <c r="J67">
+        <v>169</v>
+      </c>
+      <c r="K67">
+        <v>90.8</v>
+      </c>
+      <c r="L67">
+        <v>78.2</v>
+      </c>
+      <c r="M67">
+        <v>126.421009</v>
+      </c>
+      <c r="N67">
+        <v>-48.22100899999998</v>
+      </c>
+      <c r="O67">
+        <v>-4.339890809999996</v>
+      </c>
+      <c r="P67">
+        <v>-43.88111818999998</v>
+      </c>
+      <c r="Q67">
+        <v>46.91888181000002</v>
+      </c>
+      <c r="R67">
+        <v>1.857142857142857</v>
+      </c>
+      <c r="S67">
+        <v>0.2259709634278927</v>
+      </c>
+      <c r="T67">
+        <v>2.034346995129493</v>
+      </c>
+      <c r="U67">
+        <v>0.2138</v>
+      </c>
+      <c r="V67">
+        <v>0.0556711266242148</v>
+      </c>
+      <c r="W67">
+        <v>0.2018975131277429</v>
+      </c>
+      <c r="X67" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y67">
+        <v>0.6185680736023869</v>
+      </c>
+      <c r="Z67">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68">
+        <v>0.66</v>
+      </c>
+      <c r="B68">
+        <v>0.2120732207327953</v>
+      </c>
+      <c r="C68">
+        <v>-29.22036292571806</v>
+      </c>
+      <c r="D68">
+        <v>309.3816370742819</v>
+      </c>
+      <c r="E68">
+        <v>-94.89800000000002</v>
+      </c>
+      <c r="F68">
+        <v>600.4019999999999</v>
+      </c>
+      <c r="G68">
+        <v>261.8</v>
+      </c>
+      <c r="H68">
+        <v>214.4</v>
+      </c>
+      <c r="I68">
+        <v>0</v>
+      </c>
+      <c r="J68">
+        <v>169</v>
+      </c>
+      <c r="K68">
+        <v>90.8</v>
+      </c>
+      <c r="L68">
+        <v>78.2</v>
+      </c>
+      <c r="M68">
+        <v>128.3659476</v>
+      </c>
+      <c r="N68">
+        <v>-50.16594759999997</v>
+      </c>
+      <c r="O68">
+        <v>-4.514935283999995</v>
+      </c>
+      <c r="P68">
+        <v>-45.65101231599997</v>
+      </c>
+      <c r="Q68">
+        <v>45.14898768400003</v>
+      </c>
+      <c r="R68">
+        <v>1.941176470588236</v>
+      </c>
+      <c r="S68">
+        <v>0.2314759917640073</v>
+      </c>
+      <c r="T68">
+        <v>2.094180730280361</v>
+      </c>
+      <c r="U68">
+        <v>0.2138</v>
+      </c>
+      <c r="V68">
+        <v>0.0548276247056661</v>
+      </c>
+      <c r="W68">
+        <v>0.2020778538379286</v>
+      </c>
+      <c r="X68" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y68">
+        <v>0.6091958300629569</v>
+      </c>
+      <c r="Z68">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69">
+        <v>0.67</v>
+      </c>
+      <c r="B69">
+        <v>0.2138232207327954</v>
+      </c>
+      <c r="C69">
+        <v>-41.41076883273536</v>
+      </c>
+      <c r="D69">
+        <v>306.2882311672647</v>
+      </c>
+      <c r="E69">
+        <v>-85.80099999999993</v>
+      </c>
+      <c r="F69">
+        <v>609.499</v>
+      </c>
+      <c r="G69">
+        <v>261.8</v>
+      </c>
+      <c r="H69">
+        <v>214.4</v>
+      </c>
+      <c r="I69">
+        <v>0</v>
+      </c>
+      <c r="J69">
+        <v>169</v>
+      </c>
+      <c r="K69">
+        <v>90.8</v>
+      </c>
+      <c r="L69">
+        <v>78.2</v>
+      </c>
+      <c r="M69">
+        <v>130.3108862</v>
+      </c>
+      <c r="N69">
+        <v>-52.1108862</v>
+      </c>
+      <c r="O69">
+        <v>-4.689979757999998</v>
+      </c>
+      <c r="P69">
+        <v>-47.420906442</v>
+      </c>
+      <c r="Q69">
+        <v>43.379093558</v>
+      </c>
+      <c r="R69">
+        <v>2.030303030303031</v>
+      </c>
+      <c r="S69">
+        <v>0.2373146581810984</v>
+      </c>
+      <c r="T69">
+        <v>2.157640752410069</v>
+      </c>
+      <c r="U69">
+        <v>0.2138</v>
+      </c>
+      <c r="V69">
+        <v>0.0540093019488651</v>
+      </c>
+      <c r="W69">
+        <v>0.2022528112433326</v>
+      </c>
+      <c r="X69" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y69">
+        <v>0.6001033549873902</v>
+      </c>
+      <c r="Z69">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70">
+        <v>0.68</v>
+      </c>
+      <c r="B70">
+        <v>0.2155732207327953</v>
+      </c>
+      <c r="C70">
+        <v>-53.53992722369946</v>
+      </c>
+      <c r="D70">
+        <v>303.2560727763005</v>
+      </c>
+      <c r="E70">
+        <v>-76.70399999999995</v>
+      </c>
+      <c r="F70">
+        <v>618.596</v>
+      </c>
+      <c r="G70">
+        <v>261.8</v>
+      </c>
+      <c r="H70">
+        <v>214.4</v>
+      </c>
+      <c r="I70">
+        <v>0</v>
+      </c>
+      <c r="J70">
+        <v>169</v>
+      </c>
+      <c r="K70">
+        <v>90.8</v>
+      </c>
+      <c r="L70">
+        <v>78.2</v>
+      </c>
+      <c r="M70">
+        <v>132.2558248</v>
+      </c>
+      <c r="N70">
+        <v>-54.0558248</v>
+      </c>
+      <c r="O70">
+        <v>-4.865024231999998</v>
+      </c>
+      <c r="P70">
+        <v>-49.190800568</v>
+      </c>
+      <c r="Q70">
+        <v>41.609199432</v>
+      </c>
+      <c r="R70">
+        <v>2.125</v>
+      </c>
+      <c r="S70">
+        <v>0.2435182412492577</v>
+      </c>
+      <c r="T70">
+        <v>2.225067025922883</v>
+      </c>
+      <c r="U70">
+        <v>0.2138</v>
+      </c>
+      <c r="V70">
+        <v>0.05321504750844062</v>
+      </c>
+      <c r="W70">
+        <v>0.2024226228426954</v>
+      </c>
+      <c r="X70" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y70">
+        <v>0.5912783056493403</v>
+      </c>
+      <c r="Z70">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71">
+        <v>0.6900000000000001</v>
+      </c>
+      <c r="B71">
+        <v>0.2173232207327954</v>
+      </c>
+      <c r="C71">
+        <v>-65.60963926183183</v>
+      </c>
+      <c r="D71">
+        <v>300.2833607381681</v>
+      </c>
+      <c r="E71">
+        <v>-67.60699999999997</v>
+      </c>
+      <c r="F71">
+        <v>627.693</v>
+      </c>
+      <c r="G71">
+        <v>261.8</v>
+      </c>
+      <c r="H71">
+        <v>214.4</v>
+      </c>
+      <c r="I71">
+        <v>0</v>
+      </c>
+      <c r="J71">
+        <v>169</v>
+      </c>
+      <c r="K71">
+        <v>90.8</v>
+      </c>
+      <c r="L71">
+        <v>78.2</v>
+      </c>
+      <c r="M71">
+        <v>134.2007634</v>
+      </c>
+      <c r="N71">
+        <v>-56.0007634</v>
+      </c>
+      <c r="O71">
+        <v>-5.040068705999998</v>
+      </c>
+      <c r="P71">
+        <v>-50.960694694</v>
+      </c>
+      <c r="Q71">
+        <v>39.839305306</v>
+      </c>
+      <c r="R71">
+        <v>2.225806451612904</v>
+      </c>
+      <c r="S71">
+        <v>0.2501220554831048</v>
+      </c>
+      <c r="T71">
+        <v>2.296843381597815</v>
+      </c>
+      <c r="U71">
+        <v>0.2138</v>
+      </c>
+      <c r="V71">
+        <v>0.05244381493585451</v>
+      </c>
+      <c r="W71">
+        <v>0.2025875123667143</v>
+      </c>
+      <c r="X71" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y71">
+        <v>0.5827090548428282</v>
+      </c>
+      <c r="Z71">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72">
+        <v>0.7000000000000001</v>
+      </c>
+      <c r="B72">
+        <v>0.2190732207327953</v>
+      </c>
+      <c r="C72">
+        <v>-77.6216361712768</v>
+      </c>
+      <c r="D72">
+        <v>297.3683638287232</v>
+      </c>
+      <c r="E72">
+        <v>-58.50999999999999</v>
+      </c>
+      <c r="F72">
+        <v>636.79</v>
+      </c>
+      <c r="G72">
+        <v>261.8</v>
+      </c>
+      <c r="H72">
+        <v>214.4</v>
+      </c>
+      <c r="I72">
+        <v>0</v>
+      </c>
+      <c r="J72">
+        <v>169</v>
+      </c>
+      <c r="K72">
+        <v>90.8</v>
+      </c>
+      <c r="L72">
+        <v>78.2</v>
+      </c>
+      <c r="M72">
+        <v>136.145702</v>
+      </c>
+      <c r="N72">
+        <v>-57.945702</v>
+      </c>
+      <c r="O72">
+        <v>-5.215113179999998</v>
+      </c>
+      <c r="P72">
+        <v>-52.73058882</v>
+      </c>
+      <c r="Q72">
+        <v>38.06941118</v>
+      </c>
+      <c r="R72">
+        <v>2.333333333333334</v>
+      </c>
+      <c r="S72">
+        <v>0.2571661239992082</v>
+      </c>
+      <c r="T72">
+        <v>2.373404827651076</v>
+      </c>
+      <c r="U72">
+        <v>0.2138</v>
+      </c>
+      <c r="V72">
+        <v>0.05169461757962802</v>
+      </c>
+      <c r="W72">
+        <v>0.2027476907614755</v>
+      </c>
+      <c r="X72" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y72">
+        <v>0.574384639773645</v>
+      </c>
+      <c r="Z72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73">
+        <v>0.71</v>
+      </c>
+      <c r="B73">
+        <v>0.2208232207327953</v>
+      </c>
+      <c r="C73">
+        <v>-89.5775825991293</v>
+      </c>
+      <c r="D73">
+        <v>294.5094174008706</v>
+      </c>
+      <c r="E73">
+        <v>-49.41300000000001</v>
+      </c>
+      <c r="F73">
+        <v>645.8869999999999</v>
+      </c>
+      <c r="G73">
+        <v>261.8</v>
+      </c>
+      <c r="H73">
+        <v>214.4</v>
+      </c>
+      <c r="I73">
+        <v>0</v>
+      </c>
+      <c r="J73">
+        <v>169</v>
+      </c>
+      <c r="K73">
+        <v>90.8</v>
+      </c>
+      <c r="L73">
+        <v>78.2</v>
+      </c>
+      <c r="M73">
+        <v>138.0906406</v>
+      </c>
+      <c r="N73">
+        <v>-59.89064059999997</v>
+      </c>
+      <c r="O73">
+        <v>-5.390157653999996</v>
+      </c>
+      <c r="P73">
+        <v>-54.50048294599998</v>
+      </c>
+      <c r="Q73">
+        <v>36.29951705400002</v>
+      </c>
+      <c r="R73">
+        <v>2.448275862068965</v>
+      </c>
+      <c r="S73">
+        <v>0.2646959903440085</v>
+      </c>
+      <c r="T73">
+        <v>2.455246373432146</v>
+      </c>
+      <c r="U73">
+        <v>0.2138</v>
+      </c>
+      <c r="V73">
+        <v>0.05096652437428115</v>
+      </c>
+      <c r="W73">
+        <v>0.2029033570887787</v>
+      </c>
+      <c r="X73" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y73">
+        <v>0.5662947152697908</v>
+      </c>
+      <c r="Z73">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74">
+        <v>0.72</v>
+      </c>
+      <c r="B74">
+        <v>0.2225732207327953</v>
+      </c>
+      <c r="C74">
+        <v>-101.47907978537</v>
+      </c>
+      <c r="D74">
+        <v>291.7049202146299</v>
+      </c>
+      <c r="E74">
+        <v>-40.31600000000003</v>
+      </c>
+      <c r="F74">
+        <v>654.9839999999999</v>
+      </c>
+      <c r="G74">
+        <v>261.8</v>
+      </c>
+      <c r="H74">
+        <v>214.4</v>
+      </c>
+      <c r="I74">
+        <v>0</v>
+      </c>
+      <c r="J74">
+        <v>169</v>
+      </c>
+      <c r="K74">
+        <v>90.8</v>
+      </c>
+      <c r="L74">
+        <v>78.2</v>
+      </c>
+      <c r="M74">
+        <v>140.0355792</v>
+      </c>
+      <c r="N74">
+        <v>-61.83557919999997</v>
+      </c>
+      <c r="O74">
+        <v>-5.565202127999996</v>
+      </c>
+      <c r="P74">
+        <v>-56.27037707199997</v>
+      </c>
+      <c r="Q74">
+        <v>34.52962292800002</v>
+      </c>
+      <c r="R74">
+        <v>2.571428571428571</v>
+      </c>
+      <c r="S74">
+        <v>0.2727637042848659</v>
+      </c>
+      <c r="T74">
+        <v>2.542933743911866</v>
+      </c>
+      <c r="U74">
+        <v>0.2138</v>
+      </c>
+      <c r="V74">
+        <v>0.05025865598019392</v>
+      </c>
+      <c r="W74">
+        <v>0.2030546993514345</v>
+      </c>
+      <c r="X74" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y74">
+        <v>0.5584295108910438</v>
+      </c>
+      <c r="Z74">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75">
+        <v>0.73</v>
+      </c>
+      <c r="B75">
+        <v>0.2243232207327953</v>
+      </c>
+      <c r="C75">
+        <v>-113.327668553392</v>
+      </c>
+      <c r="D75">
+        <v>288.953331446608</v>
+      </c>
+      <c r="E75">
+        <v>-31.21900000000005</v>
+      </c>
+      <c r="F75">
+        <v>664.0809999999999</v>
+      </c>
+      <c r="G75">
+        <v>261.8</v>
+      </c>
+      <c r="H75">
+        <v>214.4</v>
+      </c>
+      <c r="I75">
+        <v>0</v>
+      </c>
+      <c r="J75">
+        <v>169</v>
+      </c>
+      <c r="K75">
+        <v>90.8</v>
+      </c>
+      <c r="L75">
+        <v>78.2</v>
+      </c>
+      <c r="M75">
+        <v>141.9805178</v>
+      </c>
+      <c r="N75">
+        <v>-63.78051779999997</v>
+      </c>
+      <c r="O75">
+        <v>-5.740246601999996</v>
+      </c>
+      <c r="P75">
+        <v>-58.04027119799997</v>
+      </c>
+      <c r="Q75">
+        <v>32.75972880200003</v>
+      </c>
+      <c r="R75">
+        <v>2.703703703703703</v>
+      </c>
+      <c r="S75">
+        <v>0.2814290266657869</v>
+      </c>
+      <c r="T75">
+        <v>2.637116475167861</v>
+      </c>
+      <c r="U75">
+        <v>0.2138</v>
+      </c>
+      <c r="V75">
+        <v>0.04957018124073921</v>
+      </c>
+      <c r="W75">
+        <v>0.20320189525073</v>
+      </c>
+      <c r="X75" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y75">
+        <v>0.5507797915637691</v>
+      </c>
+      <c r="Z75">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76">
+        <v>0.74</v>
+      </c>
+      <c r="B76">
+        <v>0.2260732207327953</v>
+      </c>
+      <c r="C76">
+        <v>-125.1248321328557</v>
+      </c>
+      <c r="D76">
+        <v>286.2531678671443</v>
+      </c>
+      <c r="E76">
+        <v>-22.12199999999996</v>
+      </c>
+      <c r="F76">
+        <v>673.178</v>
+      </c>
+      <c r="G76">
+        <v>261.8</v>
+      </c>
+      <c r="H76">
+        <v>214.4</v>
+      </c>
+      <c r="I76">
+        <v>0</v>
+      </c>
+      <c r="J76">
+        <v>169</v>
+      </c>
+      <c r="K76">
+        <v>90.8</v>
+      </c>
+      <c r="L76">
+        <v>78.2</v>
+      </c>
+      <c r="M76">
+        <v>143.9254564</v>
+      </c>
+      <c r="N76">
+        <v>-65.7254564</v>
+      </c>
+      <c r="O76">
+        <v>-5.915291075999998</v>
+      </c>
+      <c r="P76">
+        <v>-59.810165324</v>
+      </c>
+      <c r="Q76">
+        <v>30.98983467599999</v>
+      </c>
+      <c r="R76">
+        <v>2.846153846153846</v>
+      </c>
+      <c r="S76">
+        <v>0.2907609123067787</v>
+      </c>
+      <c r="T76">
+        <v>2.738544031905086</v>
+      </c>
+      <c r="U76">
+        <v>0.2138</v>
+      </c>
+      <c r="V76">
+        <v>0.04890031392667516</v>
+      </c>
+      <c r="W76">
+        <v>0.2033451128824768</v>
+      </c>
+      <c r="X76" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y76">
+        <v>0.5433368214075018</v>
+      </c>
+      <c r="Z76">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77">
+        <v>0.75</v>
+      </c>
+      <c r="B77">
+        <v>0.2278232207327954</v>
+      </c>
+      <c r="C77">
+        <v>-136.8719988257386</v>
+      </c>
+      <c r="D77">
+        <v>283.6030011742613</v>
+      </c>
+      <c r="E77">
+        <v>-13.02499999999998</v>
+      </c>
+      <c r="F77">
+        <v>682.275</v>
+      </c>
+      <c r="G77">
+        <v>261.8</v>
+      </c>
+      <c r="H77">
+        <v>214.4</v>
+      </c>
+      <c r="I77">
+        <v>0</v>
+      </c>
+      <c r="J77">
+        <v>169</v>
+      </c>
+      <c r="K77">
+        <v>90.8</v>
+      </c>
+      <c r="L77">
+        <v>78.2</v>
+      </c>
+      <c r="M77">
+        <v>145.870395</v>
+      </c>
+      <c r="N77">
+        <v>-67.670395</v>
+      </c>
+      <c r="O77">
+        <v>-6.090335549999998</v>
+      </c>
+      <c r="P77">
+        <v>-61.58005945</v>
+      </c>
+      <c r="Q77">
+        <v>29.21994055</v>
+      </c>
+      <c r="R77">
+        <v>3</v>
+      </c>
+      <c r="S77">
+        <v>0.3008393487990499</v>
+      </c>
+      <c r="T77">
+        <v>2.84808579318129</v>
+      </c>
+      <c r="U77">
+        <v>0.2138</v>
+      </c>
+      <c r="V77">
+        <v>0.04824830974098615</v>
+      </c>
+      <c r="W77">
+        <v>0.2034845113773772</v>
+      </c>
+      <c r="X77" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y77">
+        <v>0.5360923304554019</v>
+      </c>
+      <c r="Z77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78">
+        <v>0.76</v>
+      </c>
+      <c r="B78">
+        <v>0.2295732207327953</v>
+      </c>
+      <c r="C78">
+        <v>-148.5705445256464</v>
+      </c>
+      <c r="D78">
+        <v>281.0014554743536</v>
+      </c>
+      <c r="E78">
+        <v>-3.927999999999997</v>
+      </c>
+      <c r="F78">
+        <v>691.372</v>
+      </c>
+      <c r="G78">
+        <v>261.8</v>
+      </c>
+      <c r="H78">
+        <v>214.4</v>
+      </c>
+      <c r="I78">
+        <v>0</v>
+      </c>
+      <c r="J78">
+        <v>169</v>
+      </c>
+      <c r="K78">
+        <v>90.8</v>
+      </c>
+      <c r="L78">
+        <v>78.2</v>
+      </c>
+      <c r="M78">
+        <v>147.8153336</v>
+      </c>
+      <c r="N78">
+        <v>-69.61533359999997</v>
+      </c>
+      <c r="O78">
+        <v>-6.265380023999995</v>
+      </c>
+      <c r="P78">
+        <v>-63.34995357599998</v>
+      </c>
+      <c r="Q78">
+        <v>27.45004642400002</v>
+      </c>
+      <c r="R78">
+        <v>3.166666666666667</v>
+      </c>
+      <c r="S78">
+        <v>0.3117576549990103</v>
+      </c>
+      <c r="T78">
+        <v>2.966756034563844</v>
+      </c>
+      <c r="U78">
+        <v>0.2138</v>
+      </c>
+      <c r="V78">
+        <v>0.04761346356018371</v>
+      </c>
+      <c r="W78">
+        <v>0.2036202414908327</v>
+      </c>
+      <c r="X78" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y78">
+        <v>0.5290384840020415</v>
+      </c>
+      <c r="Z78">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79">
+        <v>0.77</v>
+      </c>
+      <c r="B79">
+        <v>0.2313232207327953</v>
+      </c>
+      <c r="C79">
+        <v>-160.2217950997245</v>
+      </c>
+      <c r="D79">
+        <v>278.4472049002754</v>
+      </c>
+      <c r="E79">
+        <v>5.168999999999983</v>
+      </c>
+      <c r="F79">
+        <v>700.4689999999999</v>
+      </c>
+      <c r="G79">
+        <v>261.8</v>
+      </c>
+      <c r="H79">
+        <v>214.4</v>
+      </c>
+      <c r="I79">
+        <v>0</v>
+      </c>
+      <c r="J79">
+        <v>169</v>
+      </c>
+      <c r="K79">
+        <v>90.8</v>
+      </c>
+      <c r="L79">
+        <v>78.2</v>
+      </c>
+      <c r="M79">
+        <v>149.7602722</v>
+      </c>
+      <c r="N79">
+        <v>-71.56027219999997</v>
+      </c>
+      <c r="O79">
+        <v>-6.440424497999995</v>
+      </c>
+      <c r="P79">
+        <v>-65.11984770199997</v>
+      </c>
+      <c r="Q79">
+        <v>25.68015229800002</v>
+      </c>
+      <c r="R79">
+        <v>3.347826086956522</v>
+      </c>
+      <c r="S79">
+        <v>0.323625379129402</v>
+      </c>
+      <c r="T79">
+        <v>3.095745427370967</v>
+      </c>
+      <c r="U79">
+        <v>0.2138</v>
+      </c>
+      <c r="V79">
+        <v>0.04699510689057094</v>
+      </c>
+      <c r="W79">
+        <v>0.2037524461467959</v>
+      </c>
+      <c r="X79" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y79">
+        <v>0.5221678543396773</v>
+      </c>
+      <c r="Z79">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80">
+        <v>0.78</v>
+      </c>
+      <c r="B80">
+        <v>0.2330732207327953</v>
+      </c>
+      <c r="C80">
+        <v>-171.8270286418332</v>
+      </c>
+      <c r="D80">
+        <v>275.9389713581668</v>
+      </c>
+      <c r="E80">
+        <v>14.26599999999996</v>
+      </c>
+      <c r="F80">
+        <v>709.5659999999999</v>
+      </c>
+      <c r="G80">
+        <v>261.8</v>
+      </c>
+      <c r="H80">
+        <v>214.4</v>
+      </c>
+      <c r="I80">
+        <v>0</v>
+      </c>
+      <c r="J80">
+        <v>169</v>
+      </c>
+      <c r="K80">
+        <v>90.8</v>
+      </c>
+      <c r="L80">
+        <v>78.2</v>
+      </c>
+      <c r="M80">
+        <v>151.7052108</v>
+      </c>
+      <c r="N80">
+        <v>-73.50521079999997</v>
+      </c>
+      <c r="O80">
+        <v>-6.615468971999995</v>
+      </c>
+      <c r="P80">
+        <v>-66.88974182799998</v>
+      </c>
+      <c r="Q80">
+        <v>23.91025817200001</v>
+      </c>
+      <c r="R80">
+        <v>3.545454545454546</v>
+      </c>
+      <c r="S80">
+        <v>0.3365719872716476</v>
+      </c>
+      <c r="T80">
+        <v>3.236461128615103</v>
+      </c>
+      <c r="U80">
+        <v>0.2138</v>
+      </c>
+      <c r="V80">
+        <v>0.046392605520179</v>
+      </c>
+      <c r="W80">
+        <v>0.2038812609397857</v>
+      </c>
+      <c r="X80" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y80">
+        <v>0.5154733946686558</v>
+      </c>
+      <c r="Z80">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81">
+        <v>0.79</v>
+      </c>
+      <c r="B81">
+        <v>0.2348232207327954</v>
+      </c>
+      <c r="C81">
+        <v>-183.3874776050307</v>
+      </c>
+      <c r="D81">
+        <v>273.4755223949694</v>
+      </c>
+      <c r="E81">
+        <v>23.36300000000006</v>
+      </c>
+      <c r="F81">
+        <v>718.663</v>
+      </c>
+      <c r="G81">
+        <v>261.8</v>
+      </c>
+      <c r="H81">
+        <v>214.4</v>
+      </c>
+      <c r="I81">
+        <v>0</v>
+      </c>
+      <c r="J81">
+        <v>169</v>
+      </c>
+      <c r="K81">
+        <v>90.8</v>
+      </c>
+      <c r="L81">
+        <v>78.2</v>
+      </c>
+      <c r="M81">
+        <v>153.6501494</v>
+      </c>
+      <c r="N81">
+        <v>-75.4501494</v>
+      </c>
+      <c r="O81">
+        <v>-6.790513445999998</v>
+      </c>
+      <c r="P81">
+        <v>-68.65963595400001</v>
+      </c>
+      <c r="Q81">
+        <v>22.14036404599999</v>
+      </c>
+      <c r="R81">
+        <v>3.761904761904763</v>
+      </c>
+      <c r="S81">
+        <v>0.3507516057131547</v>
+      </c>
+      <c r="T81">
+        <v>3.390578325215822</v>
+      </c>
+      <c r="U81">
+        <v>0.2138</v>
+      </c>
+      <c r="V81">
+        <v>0.04580535734903748</v>
+      </c>
+      <c r="W81">
+        <v>0.2040068145987758</v>
+      </c>
+      <c r="X81" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y81">
+        <v>0.5089484149893055</v>
+      </c>
+      <c r="Z81">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82">
+        <v>0.8</v>
+      </c>
+      <c r="B82">
+        <v>0.2365732207327953</v>
+      </c>
+      <c r="C82">
+        <v>-194.9043308208397</v>
+      </c>
+      <c r="D82">
+        <v>271.0556691791603</v>
+      </c>
+      <c r="E82">
+        <v>32.46000000000004</v>
+      </c>
+      <c r="F82">
+        <v>727.76</v>
+      </c>
+      <c r="G82">
+        <v>261.8</v>
+      </c>
+      <c r="H82">
+        <v>214.4</v>
+      </c>
+      <c r="I82">
+        <v>0</v>
+      </c>
+      <c r="J82">
+        <v>169</v>
+      </c>
+      <c r="K82">
+        <v>90.8</v>
+      </c>
+      <c r="L82">
+        <v>78.2</v>
+      </c>
+      <c r="M82">
+        <v>155.595088</v>
+      </c>
+      <c r="N82">
+        <v>-77.395088</v>
+      </c>
+      <c r="O82">
+        <v>-6.965557919999998</v>
+      </c>
+      <c r="P82">
+        <v>-70.42953008000001</v>
+      </c>
+      <c r="Q82">
+        <v>20.37046991999999</v>
+      </c>
+      <c r="R82">
+        <v>4.000000000000001</v>
+      </c>
+      <c r="S82">
+        <v>0.3663491859988124</v>
+      </c>
+      <c r="T82">
+        <v>3.560107241476613</v>
+      </c>
+      <c r="U82">
+        <v>0.2138</v>
+      </c>
+      <c r="V82">
+        <v>0.04523279038217452</v>
+      </c>
+      <c r="W82">
+        <v>0.2041292294162911</v>
+      </c>
+      <c r="X82" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y82">
+        <v>0.5025865598019392</v>
+      </c>
+      <c r="Z82">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="B83">
+        <v>0.2588307119661987</v>
+      </c>
+      <c r="C83">
+        <v>-231.4203175914057</v>
+      </c>
+      <c r="D83">
+        <v>243.6366824085942</v>
+      </c>
+      <c r="E83">
+        <v>41.55700000000002</v>
+      </c>
+      <c r="F83">
+        <v>736.857</v>
+      </c>
+      <c r="G83">
+        <v>261.8</v>
+      </c>
+      <c r="H83">
+        <v>214.4</v>
+      </c>
+      <c r="I83">
+        <v>0</v>
+      </c>
+      <c r="J83">
+        <v>169</v>
+      </c>
+      <c r="K83">
+        <v>90.8</v>
+      </c>
+      <c r="L83">
+        <v>78.2</v>
+      </c>
+      <c r="M83">
+        <v>175.9614516</v>
+      </c>
+      <c r="N83">
+        <v>-97.7614516</v>
+      </c>
+      <c r="O83">
+        <v>-8.798530643999998</v>
+      </c>
+      <c r="P83">
+        <v>-88.962920956</v>
+      </c>
+      <c r="Q83">
+        <v>1.837079043999992</v>
+      </c>
+      <c r="R83">
+        <v>4.263157894736843</v>
+      </c>
+      <c r="S83">
+        <v>0.3849438338587673</v>
+      </c>
+      <c r="T83">
+        <v>3.762211057723536</v>
+      </c>
+      <c r="U83">
+        <v>0.2388</v>
+      </c>
+      <c r="V83">
+        <v>0.03999739679346904</v>
+      </c>
+      <c r="W83">
+        <v>0.2292486216457196</v>
+      </c>
+      <c r="X83" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y83">
+        <v>0.4444155199274339</v>
+      </c>
+      <c r="Z83">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84">
+        <v>0.8200000000000001</v>
+      </c>
+      <c r="B84">
+        <v>0.2608307119661987</v>
+      </c>
+      <c r="C84">
+        <v>-242.7119390494109</v>
+      </c>
+      <c r="D84">
+        <v>241.4420609505891</v>
+      </c>
+      <c r="E84">
+        <v>50.654</v>
+      </c>
+      <c r="F84">
+        <v>745.954</v>
+      </c>
+      <c r="G84">
+        <v>261.8</v>
+      </c>
+      <c r="H84">
+        <v>214.4</v>
+      </c>
+      <c r="I84">
+        <v>0</v>
+      </c>
+      <c r="J84">
+        <v>169</v>
+      </c>
+      <c r="K84">
+        <v>90.8</v>
+      </c>
+      <c r="L84">
+        <v>78.2</v>
+      </c>
+      <c r="M84">
+        <v>178.1338152</v>
+      </c>
+      <c r="N84">
+        <v>-99.93381519999998</v>
+      </c>
+      <c r="O84">
+        <v>-8.994043367999996</v>
+      </c>
+      <c r="P84">
+        <v>-90.93977183199999</v>
+      </c>
+      <c r="Q84">
+        <v>-0.1397718319999939</v>
+      </c>
+      <c r="R84">
+        <v>4.555555555555557</v>
+      </c>
+      <c r="S84">
+        <v>0.4041740468509211</v>
+      </c>
+      <c r="T84">
+        <v>3.971222783152621</v>
+      </c>
+      <c r="U84">
+        <v>0.2388</v>
+      </c>
+      <c r="V84">
+        <v>0.03950962366184137</v>
+      </c>
+      <c r="W84">
+        <v>0.2293651018695523</v>
+      </c>
+      <c r="X84" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y84">
+        <v>0.4389958184649043</v>
+      </c>
+      <c r="Z84">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85">
+        <v>0.8300000000000001</v>
+      </c>
+      <c r="B85">
+        <v>0.2628307119661987</v>
+      </c>
+      <c r="C85">
+        <v>-253.9643762109643</v>
+      </c>
+      <c r="D85">
+        <v>239.2866237890357</v>
+      </c>
+      <c r="E85">
+        <v>59.75100000000009</v>
+      </c>
+      <c r="F85">
+        <v>755.051</v>
+      </c>
+      <c r="G85">
+        <v>261.8</v>
+      </c>
+      <c r="H85">
+        <v>214.4</v>
+      </c>
+      <c r="I85">
+        <v>0</v>
+      </c>
+      <c r="J85">
+        <v>169</v>
+      </c>
+      <c r="K85">
+        <v>90.8</v>
+      </c>
+      <c r="L85">
+        <v>78.2</v>
+      </c>
+      <c r="M85">
+        <v>180.3061788</v>
+      </c>
+      <c r="N85">
+        <v>-102.1061788</v>
+      </c>
+      <c r="O85">
+        <v>-9.189556091999998</v>
+      </c>
+      <c r="P85">
+        <v>-92.91662270800002</v>
+      </c>
+      <c r="Q85">
+        <v>-2.116622708000023</v>
+      </c>
+      <c r="R85">
+        <v>4.882352941176473</v>
+      </c>
+      <c r="S85">
+        <v>0.4256666378421518</v>
+      </c>
+      <c r="T85">
+        <v>4.20482412333807</v>
+      </c>
+      <c r="U85">
+        <v>0.2388</v>
+      </c>
+      <c r="V85">
+        <v>0.0390336040996505</v>
+      </c>
+      <c r="W85">
+        <v>0.2294787753410035</v>
+      </c>
+      <c r="X85" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y85">
+        <v>0.4337067122183391</v>
+      </c>
+      <c r="Z85">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86">
+        <v>0.84</v>
+      </c>
+      <c r="B86">
+        <v>0.2648307119661987</v>
+      </c>
+      <c r="C86">
+        <v>-265.178669225772</v>
+      </c>
+      <c r="D86">
+        <v>237.1693307742279</v>
+      </c>
+      <c r="E86">
+        <v>68.84799999999996</v>
+      </c>
+      <c r="F86">
+        <v>764.1479999999999</v>
+      </c>
+      <c r="G86">
+        <v>261.8</v>
+      </c>
+      <c r="H86">
+        <v>214.4</v>
+      </c>
+      <c r="I86">
+        <v>0</v>
+      </c>
+      <c r="J86">
+        <v>169</v>
+      </c>
+      <c r="K86">
+        <v>90.8</v>
+      </c>
+      <c r="L86">
+        <v>78.2</v>
+      </c>
+      <c r="M86">
+        <v>182.4785424</v>
+      </c>
+      <c r="N86">
+        <v>-104.2785424</v>
+      </c>
+      <c r="O86">
+        <v>-9.385068815999995</v>
+      </c>
+      <c r="P86">
+        <v>-94.89347358399998</v>
+      </c>
+      <c r="Q86">
+        <v>-4.09347358399998</v>
+      </c>
+      <c r="R86">
+        <v>5.249999999999999</v>
+      </c>
+      <c r="S86">
+        <v>0.4498458027072861</v>
+      </c>
+      <c r="T86">
+        <v>4.467625631046698</v>
+      </c>
+      <c r="U86">
+        <v>0.2388</v>
+      </c>
+      <c r="V86">
+        <v>0.03856891833655944</v>
+      </c>
+      <c r="W86">
+        <v>0.2295897423012296</v>
+      </c>
+      <c r="X86" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y86">
+        <v>0.4285435370728827</v>
+      </c>
+      <c r="Z86">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87">
+        <v>0.85</v>
+      </c>
+      <c r="B87">
+        <v>0.2668307119661987</v>
+      </c>
+      <c r="C87">
+        <v>-276.3558217519753</v>
+      </c>
+      <c r="D87">
+        <v>235.0891782480245</v>
+      </c>
+      <c r="E87">
+        <v>77.94499999999994</v>
+      </c>
+      <c r="F87">
+        <v>773.2449999999999</v>
+      </c>
+      <c r="G87">
+        <v>261.8</v>
+      </c>
+      <c r="H87">
+        <v>214.4</v>
+      </c>
+      <c r="I87">
+        <v>0</v>
+      </c>
+      <c r="J87">
+        <v>169</v>
+      </c>
+      <c r="K87">
+        <v>90.8</v>
+      </c>
+      <c r="L87">
+        <v>78.2</v>
+      </c>
+      <c r="M87">
+        <v>184.650906</v>
+      </c>
+      <c r="N87">
+        <v>-106.450906</v>
+      </c>
+      <c r="O87">
+        <v>-9.580581539999995</v>
+      </c>
+      <c r="P87">
+        <v>-96.87032445999999</v>
+      </c>
+      <c r="Q87">
+        <v>-6.070324459999995</v>
+      </c>
+      <c r="R87">
+        <v>5.666666666666666</v>
+      </c>
+      <c r="S87">
+        <v>0.4772488562211051</v>
+      </c>
+      <c r="T87">
+        <v>4.765467339783144</v>
+      </c>
+      <c r="U87">
+        <v>0.2388</v>
+      </c>
+      <c r="V87">
+        <v>0.03811516635612932</v>
+      </c>
+      <c r="W87">
+        <v>0.2296980982741563</v>
+      </c>
+      <c r="X87" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y87">
+        <v>0.4235018484014371</v>
+      </c>
+      <c r="Z87">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88">
+        <v>0.86</v>
+      </c>
+      <c r="B88">
+        <v>0.2688307119661987</v>
+      </c>
+      <c r="C88">
+        <v>-287.496802542528</v>
+      </c>
+      <c r="D88">
+        <v>233.0451974574719</v>
+      </c>
+      <c r="E88">
+        <v>87.04200000000003</v>
+      </c>
+      <c r="F88">
+        <v>782.342</v>
+      </c>
+      <c r="G88">
+        <v>261.8</v>
+      </c>
+      <c r="H88">
+        <v>214.4</v>
+      </c>
+      <c r="I88">
+        <v>0</v>
+      </c>
+      <c r="J88">
+        <v>169</v>
+      </c>
+      <c r="K88">
+        <v>90.8</v>
+      </c>
+      <c r="L88">
+        <v>78.2</v>
+      </c>
+      <c r="M88">
+        <v>186.8232696</v>
+      </c>
+      <c r="N88">
+        <v>-108.6232696</v>
+      </c>
+      <c r="O88">
+        <v>-9.776094263999997</v>
+      </c>
+      <c r="P88">
+        <v>-98.84717533600001</v>
+      </c>
+      <c r="Q88">
+        <v>-8.047175336000009</v>
+      </c>
+      <c r="R88">
+        <v>6.142857142857142</v>
+      </c>
+      <c r="S88">
+        <v>0.5085666316654698</v>
+      </c>
+      <c r="T88">
+        <v>5.105857864053369</v>
+      </c>
+      <c r="U88">
+        <v>0.2388</v>
+      </c>
+      <c r="V88">
+        <v>0.03767196674733712</v>
+      </c>
+      <c r="W88">
+        <v>0.2298039343407359</v>
+      </c>
+      <c r="X88" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y88">
+        <v>0.4185774083037459</v>
+      </c>
+      <c r="Z88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89">
+        <v>0.87</v>
+      </c>
+      <c r="B89">
+        <v>0.2708307119661987</v>
+      </c>
+      <c r="C89">
+        <v>-298.6025469495307</v>
+      </c>
+      <c r="D89">
+        <v>231.0364530504693</v>
+      </c>
+      <c r="E89">
+        <v>96.13900000000001</v>
+      </c>
+      <c r="F89">
+        <v>791.439</v>
+      </c>
+      <c r="G89">
+        <v>261.8</v>
+      </c>
+      <c r="H89">
+        <v>214.4</v>
+      </c>
+      <c r="I89">
+        <v>0</v>
+      </c>
+      <c r="J89">
+        <v>169</v>
+      </c>
+      <c r="K89">
+        <v>90.8</v>
+      </c>
+      <c r="L89">
+        <v>78.2</v>
+      </c>
+      <c r="M89">
+        <v>188.9956332</v>
+      </c>
+      <c r="N89">
+        <v>-110.7956332</v>
+      </c>
+      <c r="O89">
+        <v>-9.971606987999998</v>
+      </c>
+      <c r="P89">
+        <v>-100.824026212</v>
+      </c>
+      <c r="Q89">
+        <v>-10.02402621200001</v>
+      </c>
+      <c r="R89">
+        <v>6.692307692307692</v>
+      </c>
+      <c r="S89">
+        <v>0.5447025264089673</v>
+      </c>
+      <c r="T89">
+        <v>5.498616161288242</v>
+      </c>
+      <c r="U89">
+        <v>0.2388</v>
+      </c>
+      <c r="V89">
+        <v>0.03723895563529876</v>
+      </c>
+      <c r="W89">
+        <v>0.2299073373942907</v>
+      </c>
+      <c r="X89" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y89">
+        <v>0.4137661737255419</v>
+      </c>
+      <c r="Z89">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90">
+        <v>0.88</v>
+      </c>
+      <c r="B90">
+        <v>0.2728307119661986</v>
+      </c>
+      <c r="C90">
+        <v>-309.6739583514311</v>
+      </c>
+      <c r="D90">
+        <v>229.0620416485689</v>
+      </c>
+      <c r="E90">
+        <v>105.236</v>
+      </c>
+      <c r="F90">
+        <v>800.5359999999999</v>
+      </c>
+      <c r="G90">
+        <v>261.8</v>
+      </c>
+      <c r="H90">
+        <v>214.4</v>
+      </c>
+      <c r="I90">
+        <v>0</v>
+      </c>
+      <c r="J90">
+        <v>169</v>
+      </c>
+      <c r="K90">
+        <v>90.8</v>
+      </c>
+      <c r="L90">
+        <v>78.2</v>
+      </c>
+      <c r="M90">
+        <v>191.1679968</v>
+      </c>
+      <c r="N90">
+        <v>-112.9679968</v>
+      </c>
+      <c r="O90">
+        <v>-10.167119712</v>
+      </c>
+      <c r="P90">
+        <v>-102.800877088</v>
+      </c>
+      <c r="Q90">
+        <v>-12.000877088</v>
+      </c>
+      <c r="R90">
+        <v>7.333333333333334</v>
+      </c>
+      <c r="S90">
+        <v>0.5868610702763815</v>
+      </c>
+      <c r="T90">
+        <v>5.956834174728932</v>
+      </c>
+      <c r="U90">
+        <v>0.2388</v>
+      </c>
+      <c r="V90">
+        <v>0.03681578568489764</v>
+      </c>
+      <c r="W90">
+        <v>0.2300083903784464</v>
+      </c>
+      <c r="X90" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y90">
+        <v>0.4090642853877517</v>
+      </c>
+      <c r="Z90">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91">
+        <v>0.89</v>
+      </c>
+      <c r="B91">
+        <v>0.2748307119661987</v>
+      </c>
+      <c r="C91">
+        <v>-320.7119095076634</v>
+      </c>
+      <c r="D91">
+        <v>227.1210904923365</v>
+      </c>
+      <c r="E91">
+        <v>114.333</v>
+      </c>
+      <c r="F91">
+        <v>809.6329999999999</v>
+      </c>
+      <c r="G91">
+        <v>261.8</v>
+      </c>
+      <c r="H91">
+        <v>214.4</v>
+      </c>
+      <c r="I91">
+        <v>0</v>
+      </c>
+      <c r="J91">
+        <v>169</v>
+      </c>
+      <c r="K91">
+        <v>90.8</v>
+      </c>
+      <c r="L91">
+        <v>78.2</v>
+      </c>
+      <c r="M91">
+        <v>193.3403604</v>
+      </c>
+      <c r="N91">
+        <v>-115.1403604</v>
+      </c>
+      <c r="O91">
+        <v>-10.36263243599999</v>
+      </c>
+      <c r="P91">
+        <v>-104.777727964</v>
+      </c>
+      <c r="Q91">
+        <v>-13.97772796399998</v>
+      </c>
+      <c r="R91">
+        <v>8.090909090909092</v>
+      </c>
+      <c r="S91">
+        <v>0.6366848039378707</v>
+      </c>
+      <c r="T91">
+        <v>6.498364554249743</v>
+      </c>
+      <c r="U91">
+        <v>0.2388</v>
+      </c>
+      <c r="V91">
+        <v>0.03640212517158418</v>
+      </c>
+      <c r="W91">
+        <v>0.2301071725090257</v>
+      </c>
+      <c r="X91" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y91">
+        <v>0.4044680574620466</v>
+      </c>
+      <c r="Z91">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92">
+        <v>0.9</v>
+      </c>
+      <c r="B92">
+        <v>0.2768307119661986</v>
+      </c>
+      <c r="C92">
+        <v>-331.7172438449953</v>
+      </c>
+      <c r="D92">
+        <v>225.2127561550046</v>
+      </c>
+      <c r="E92">
+        <v>123.4299999999999</v>
+      </c>
+      <c r="F92">
+        <v>818.7299999999999</v>
+      </c>
+      <c r="G92">
+        <v>261.8</v>
+      </c>
+      <c r="H92">
+        <v>214.4</v>
+      </c>
+      <c r="I92">
+        <v>0</v>
+      </c>
+      <c r="J92">
+        <v>169</v>
+      </c>
+      <c r="K92">
+        <v>90.8</v>
+      </c>
+      <c r="L92">
+        <v>78.2</v>
+      </c>
+      <c r="M92">
+        <v>195.512724</v>
+      </c>
+      <c r="N92">
+        <v>-117.312724</v>
+      </c>
+      <c r="O92">
+        <v>-10.55814516</v>
+      </c>
+      <c r="P92">
+        <v>-106.75457884</v>
+      </c>
+      <c r="Q92">
+        <v>-15.95457884</v>
+      </c>
+      <c r="R92">
+        <v>9.000000000000002</v>
+      </c>
+      <c r="S92">
+        <v>0.6964732843316579</v>
+      </c>
+      <c r="T92">
+        <v>7.148201009674717</v>
+      </c>
+      <c r="U92">
+        <v>0.2388</v>
+      </c>
+      <c r="V92">
+        <v>0.03599765711412214</v>
+      </c>
+      <c r="W92">
+        <v>0.2302037594811476</v>
+      </c>
+      <c r="X92" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y92">
+        <v>0.3999739679346905</v>
+      </c>
+      <c r="Z92">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93">
+        <v>0.91</v>
+      </c>
+      <c r="B93">
+        <v>0.2788307119661987</v>
+      </c>
+      <c r="C93">
+        <v>-342.6907766795664</v>
+      </c>
+      <c r="D93">
+        <v>223.3362233204336</v>
+      </c>
+      <c r="E93">
+        <v>132.527</v>
+      </c>
+      <c r="F93">
+        <v>827.827</v>
+      </c>
+      <c r="G93">
+        <v>261.8</v>
+      </c>
+      <c r="H93">
+        <v>214.4</v>
+      </c>
+      <c r="I93">
+        <v>0</v>
+      </c>
+      <c r="J93">
+        <v>169</v>
+      </c>
+      <c r="K93">
+        <v>90.8</v>
+      </c>
+      <c r="L93">
+        <v>78.2</v>
+      </c>
+      <c r="M93">
+        <v>197.6850876</v>
+      </c>
+      <c r="N93">
+        <v>-119.4850876</v>
+      </c>
+      <c r="O93">
+        <v>-10.753657884</v>
+      </c>
+      <c r="P93">
+        <v>-108.731429716</v>
+      </c>
+      <c r="Q93">
+        <v>-17.93142971600001</v>
+      </c>
+      <c r="R93">
+        <v>10.11111111111111</v>
+      </c>
+      <c r="S93">
+        <v>0.7695480937018422</v>
+      </c>
+      <c r="T93">
+        <v>7.942445566305243</v>
+      </c>
+      <c r="U93">
+        <v>0.2388</v>
+      </c>
+      <c r="V93">
+        <v>0.0356020784645164</v>
+      </c>
+      <c r="W93">
+        <v>0.2302982236626735</v>
+      </c>
+      <c r="X93" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y93">
+        <v>0.3955786496057379</v>
+      </c>
+      <c r="Z93">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94">
+        <v>0.92</v>
+      </c>
+      <c r="B94">
+        <v>0.2808307119661987</v>
+      </c>
+      <c r="C94">
+        <v>-353.633296378336</v>
+      </c>
+      <c r="D94">
+        <v>221.4907036216639</v>
+      </c>
+      <c r="E94">
+        <v>141.624</v>
+      </c>
+      <c r="F94">
+        <v>836.924</v>
+      </c>
+      <c r="G94">
+        <v>261.8</v>
+      </c>
+      <c r="H94">
+        <v>214.4</v>
+      </c>
+      <c r="I94">
+        <v>0</v>
+      </c>
+      <c r="J94">
+        <v>169</v>
+      </c>
+      <c r="K94">
+        <v>90.8</v>
+      </c>
+      <c r="L94">
+        <v>78.2</v>
+      </c>
+      <c r="M94">
+        <v>199.8574512</v>
+      </c>
+      <c r="N94">
+        <v>-121.6574512</v>
+      </c>
+      <c r="O94">
+        <v>-10.949170608</v>
+      </c>
+      <c r="P94">
+        <v>-110.708280592</v>
+      </c>
+      <c r="Q94">
+        <v>-19.90828059200001</v>
+      </c>
+      <c r="R94">
+        <v>11.50000000000001</v>
+      </c>
+      <c r="S94">
+        <v>0.8608916054145725</v>
+      </c>
+      <c r="T94">
+        <v>8.9352512620934</v>
+      </c>
+      <c r="U94">
+        <v>0.2388</v>
+      </c>
+      <c r="V94">
+        <v>0.03521509935077165</v>
+      </c>
+      <c r="W94">
+        <v>0.2303906342750358</v>
+      </c>
+      <c r="X94" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y94">
+        <v>0.3912788816752407</v>
+      </c>
+      <c r="Z94">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95">
+        <v>0.93</v>
+      </c>
+      <c r="B95">
+        <v>0.2828307119661987</v>
+      </c>
+      <c r="C95">
+        <v>-364.5455654634203</v>
+      </c>
+      <c r="D95">
+        <v>219.6754345365797</v>
+      </c>
+      <c r="E95">
+        <v>150.721</v>
+      </c>
+      <c r="F95">
+        <v>846.021</v>
+      </c>
+      <c r="G95">
+        <v>261.8</v>
+      </c>
+      <c r="H95">
+        <v>214.4</v>
+      </c>
+      <c r="I95">
+        <v>0</v>
+      </c>
+      <c r="J95">
+        <v>169</v>
+      </c>
+      <c r="K95">
+        <v>90.8</v>
+      </c>
+      <c r="L95">
+        <v>78.2</v>
+      </c>
+      <c r="M95">
+        <v>202.0298148</v>
+      </c>
+      <c r="N95">
+        <v>-123.8298148</v>
+      </c>
+      <c r="O95">
+        <v>-11.144683332</v>
+      </c>
+      <c r="P95">
+        <v>-112.685131468</v>
+      </c>
+      <c r="Q95">
+        <v>-21.885131468</v>
+      </c>
+      <c r="R95">
+        <v>13.2857142857143</v>
+      </c>
+      <c r="S95">
+        <v>0.9783332633309403</v>
+      </c>
+      <c r="T95">
+        <v>10.21171572810674</v>
+      </c>
+      <c r="U95">
+        <v>0.2388</v>
+      </c>
+      <c r="V95">
+        <v>0.0348364423685053</v>
+      </c>
+      <c r="W95">
+        <v>0.2304810575624009</v>
+      </c>
+      <c r="X95" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y95">
+        <v>0.3870715818722812</v>
+      </c>
+      <c r="Z95">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96">
+        <v>0.9400000000000001</v>
+      </c>
+      <c r="B96">
+        <v>0.2848307119661987</v>
+      </c>
+      <c r="C96">
+        <v>-375.428321662563</v>
+      </c>
+      <c r="D96">
+        <v>217.8896783374369</v>
+      </c>
+      <c r="E96">
+        <v>159.818</v>
+      </c>
+      <c r="F96">
+        <v>855.1179999999999</v>
+      </c>
+      <c r="G96">
+        <v>261.8</v>
+      </c>
+      <c r="H96">
+        <v>214.4</v>
+      </c>
+      <c r="I96">
+        <v>0</v>
+      </c>
+      <c r="J96">
+        <v>169</v>
+      </c>
+      <c r="K96">
+        <v>90.8</v>
+      </c>
+      <c r="L96">
+        <v>78.2</v>
+      </c>
+      <c r="M96">
+        <v>204.2021784</v>
+      </c>
+      <c r="N96">
+        <v>-126.0021784</v>
+      </c>
+      <c r="O96">
+        <v>-11.340196056</v>
+      </c>
+      <c r="P96">
+        <v>-114.661982344</v>
+      </c>
+      <c r="Q96">
+        <v>-23.86198234400001</v>
+      </c>
+      <c r="R96">
+        <v>15.66666666666668</v>
+      </c>
+      <c r="S96">
+        <v>1.134922140552764</v>
+      </c>
+      <c r="T96">
+        <v>11.91366834945787</v>
+      </c>
+      <c r="U96">
+        <v>0.2388</v>
+      </c>
+      <c r="V96">
+        <v>0.03446584191777651</v>
+      </c>
+      <c r="W96">
+        <v>0.230569556950035</v>
+      </c>
+      <c r="X96" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y96">
+        <v>0.3829537990864058</v>
+      </c>
+      <c r="Z96">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97">
+        <v>0.9500000000000001</v>
+      </c>
+      <c r="B97">
+        <v>0.2868307119661987</v>
+      </c>
+      <c r="C97">
+        <v>-386.2822789087862</v>
+      </c>
+      <c r="D97">
+        <v>216.1327210912139</v>
+      </c>
+      <c r="E97">
+        <v>168.9150000000001</v>
+      </c>
+      <c r="F97">
+        <v>864.215</v>
+      </c>
+      <c r="G97">
+        <v>261.8</v>
+      </c>
+      <c r="H97">
+        <v>214.4</v>
+      </c>
+      <c r="I97">
+        <v>0</v>
+      </c>
+      <c r="J97">
+        <v>169</v>
+      </c>
+      <c r="K97">
+        <v>90.8</v>
+      </c>
+      <c r="L97">
+        <v>78.2</v>
+      </c>
+      <c r="M97">
+        <v>206.374542</v>
+      </c>
+      <c r="N97">
+        <v>-128.174542</v>
+      </c>
+      <c r="O97">
+        <v>-11.53570878</v>
+      </c>
+      <c r="P97">
+        <v>-116.63883322</v>
+      </c>
+      <c r="Q97">
+        <v>-25.83883322000004</v>
+      </c>
+      <c r="R97">
+        <v>19.00000000000003</v>
+      </c>
+      <c r="S97">
+        <v>1.354146568663317</v>
+      </c>
+      <c r="T97">
+        <v>14.29640201934945</v>
+      </c>
+      <c r="U97">
+        <v>0.2388</v>
+      </c>
+      <c r="V97">
+        <v>0.03410304358179991</v>
+      </c>
+      <c r="W97">
+        <v>0.2306561931926662</v>
+      </c>
+      <c r="X97" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y97">
+        <v>0.3789227064644436</v>
+      </c>
+      <c r="Z97">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98">
+        <v>0.96</v>
+      </c>
+      <c r="B98">
+        <v>0.2888307119661986</v>
+      </c>
+      <c r="C98">
+        <v>-397.1081282920604</v>
+      </c>
+      <c r="D98">
+        <v>214.4038717079395</v>
+      </c>
+      <c r="E98">
+        <v>178.0119999999999</v>
+      </c>
+      <c r="F98">
+        <v>873.3119999999999</v>
+      </c>
+      <c r="G98">
+        <v>261.8</v>
+      </c>
+      <c r="H98">
+        <v>214.4</v>
+      </c>
+      <c r="I98">
+        <v>0</v>
+      </c>
+      <c r="J98">
+        <v>169</v>
+      </c>
+      <c r="K98">
+        <v>90.8</v>
+      </c>
+      <c r="L98">
+        <v>78.2</v>
+      </c>
+      <c r="M98">
+        <v>208.5469056</v>
+      </c>
+      <c r="N98">
+        <v>-130.3469056</v>
+      </c>
+      <c r="O98">
+        <v>-11.73122150399999</v>
+      </c>
+      <c r="P98">
+        <v>-118.615684096</v>
+      </c>
+      <c r="Q98">
+        <v>-27.81568409599997</v>
+      </c>
+      <c r="R98">
+        <v>23.99999999999998</v>
+      </c>
+      <c r="S98">
+        <v>1.682983210829143</v>
+      </c>
+      <c r="T98">
+        <v>17.87050252418678</v>
+      </c>
+      <c r="U98">
+        <v>0.2388</v>
+      </c>
+      <c r="V98">
+        <v>0.03374780354448951</v>
+      </c>
+      <c r="W98">
+        <v>0.2307410245135759</v>
+      </c>
+      <c r="X98" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y98">
+        <v>0.3749755949387725</v>
+      </c>
+      <c r="Z98">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99">
+        <v>0.97</v>
+      </c>
+      <c r="B99">
+        <v>0.2908307119661987</v>
+      </c>
+      <c r="C99">
+        <v>-407.9065389656668</v>
+      </c>
+      <c r="D99">
+        <v>212.7024610343331</v>
+      </c>
+      <c r="E99">
+        <v>187.1089999999999</v>
+      </c>
+      <c r="F99">
+        <v>882.4089999999999</v>
+      </c>
+      <c r="G99">
+        <v>261.8</v>
+      </c>
+      <c r="H99">
+        <v>214.4</v>
+      </c>
+      <c r="I99">
+        <v>0</v>
+      </c>
+      <c r="J99">
+        <v>169</v>
+      </c>
+      <c r="K99">
+        <v>90.8</v>
+      </c>
+      <c r="L99">
+        <v>78.2</v>
+      </c>
+      <c r="M99">
+        <v>210.7192692</v>
+      </c>
+      <c r="N99">
+        <v>-132.5192692</v>
+      </c>
+      <c r="O99">
+        <v>-11.926734228</v>
+      </c>
+      <c r="P99">
+        <v>-120.592534972</v>
+      </c>
+      <c r="Q99">
+        <v>-29.792534972</v>
+      </c>
+      <c r="R99">
+        <v>32.33333333333331</v>
+      </c>
+      <c r="S99">
+        <v>2.231044281105524</v>
+      </c>
+      <c r="T99">
+        <v>23.8273366989157</v>
+      </c>
+      <c r="U99">
+        <v>0.2388</v>
+      </c>
+      <c r="V99">
+        <v>0.03339988804403085</v>
+      </c>
+      <c r="W99">
+        <v>0.2308241067350854</v>
+      </c>
+      <c r="X99" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y99">
+        <v>0.3711098671558984</v>
+      </c>
+      <c r="Z99">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100">
+        <v>0.98</v>
+      </c>
+      <c r="B100">
+        <v>0.2928307119661986</v>
+      </c>
+      <c r="C100">
+        <v>-418.6781590097395</v>
+      </c>
+      <c r="D100">
+        <v>211.0278409902604</v>
+      </c>
+      <c r="E100">
+        <v>196.206</v>
+      </c>
+      <c r="F100">
+        <v>891.506</v>
+      </c>
+      <c r="G100">
+        <v>261.8</v>
+      </c>
+      <c r="H100">
+        <v>214.4</v>
+      </c>
+      <c r="I100">
+        <v>0</v>
+      </c>
+      <c r="J100">
+        <v>169</v>
+      </c>
+      <c r="K100">
+        <v>90.8</v>
+      </c>
+      <c r="L100">
+        <v>78.2</v>
+      </c>
+      <c r="M100">
+        <v>212.8916328</v>
+      </c>
+      <c r="N100">
+        <v>-134.6916328</v>
+      </c>
+      <c r="O100">
+        <v>-12.12224695199999</v>
+      </c>
+      <c r="P100">
+        <v>-122.569385848</v>
+      </c>
+      <c r="Q100">
+        <v>-31.76938584799998</v>
+      </c>
+      <c r="R100">
+        <v>48.99999999999996</v>
+      </c>
+      <c r="S100">
+        <v>3.327166421658286</v>
+      </c>
+      <c r="T100">
+        <v>35.74100504837355</v>
+      </c>
+      <c r="U100">
+        <v>0.2388</v>
+      </c>
+      <c r="V100">
+        <v>0.03305907285990808</v>
+      </c>
+      <c r="W100">
+        <v>0.230905493401054</v>
+      </c>
+      <c r="X100" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y100">
+        <v>0.3673230317767567</v>
+      </c>
+      <c r="Z100">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101">
+        <v>0.99</v>
+      </c>
+      <c r="B101">
+        <v>0.2948307119661986</v>
+      </c>
+      <c r="C101">
+        <v>-429.4236162543385</v>
+      </c>
+      <c r="D101">
+        <v>209.3793837456614</v>
+      </c>
+      <c r="E101">
+        <v>205.303</v>
+      </c>
+      <c r="F101">
+        <v>900.603</v>
+      </c>
+      <c r="G101">
+        <v>261.8</v>
+      </c>
+      <c r="H101">
+        <v>214.4</v>
+      </c>
+      <c r="I101">
+        <v>0</v>
+      </c>
+      <c r="J101">
+        <v>169</v>
+      </c>
+      <c r="K101">
+        <v>90.8</v>
+      </c>
+      <c r="L101">
+        <v>78.2</v>
+      </c>
+      <c r="M101">
+        <v>215.0639964</v>
+      </c>
+      <c r="N101">
+        <v>-136.8639964</v>
+      </c>
+      <c r="O101">
+        <v>-12.317759676</v>
+      </c>
+      <c r="P101">
+        <v>-124.546236724</v>
+      </c>
+      <c r="Q101">
+        <v>-33.74623672400003</v>
+      </c>
+      <c r="R101">
+        <v>98.99999999999991</v>
+      </c>
+      <c r="S101">
+        <v>6.615532843316572</v>
+      </c>
+      <c r="T101">
+        <v>71.4820100967471</v>
+      </c>
+      <c r="U101">
+        <v>0.2388</v>
+      </c>
+      <c r="V101">
+        <v>0.03272514283102013</v>
+      </c>
+      <c r="W101">
+        <v>0.2309852358919524</v>
+      </c>
+      <c r="X101" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y101">
+        <v>0.3636126981224459</v>
+      </c>
+      <c r="Z101">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/hungary/hungary_diversified.xlsx
+++ b/research/traditional_assets/database/data/hungary/hungary_diversified.xlsx
@@ -1266,7 +1266,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1403,22 +1403,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.09584444979624925</v>
+        <v>0.09579913979143263</v>
       </c>
       <c r="C2">
-        <v>1558.965298044015</v>
+        <v>1545.984559156157</v>
       </c>
       <c r="D2">
-        <v>1036.465298044015</v>
+        <v>1037.404559156157</v>
       </c>
       <c r="E2">
-        <v>-687.6</v>
+        <v>-673.6800000000001</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>13.92</v>
       </c>
       <c r="G2">
         <v>522.5</v>
@@ -1439,28 +1439,28 @@
         <v>108.3</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.7001759999999999</v>
       </c>
       <c r="N2">
-        <v>108.3</v>
+        <v>107.599824</v>
       </c>
       <c r="O2">
-        <v>9.747</v>
+        <v>9.683984160000001</v>
       </c>
       <c r="P2">
-        <v>98.55300000000001</v>
+        <v>97.91583984000002</v>
       </c>
       <c r="Q2">
-        <v>233.753</v>
+        <v>233.11583984</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.09584444979624925</v>
+        <v>0.09630445433478044</v>
       </c>
       <c r="T2">
-        <v>0.7282077218429369</v>
+        <v>0.7349013483770488</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1477,7 +1477,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>154.6753959004594</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1485,22 +1485,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.09579913979143263</v>
+        <v>0.09575382978661599</v>
       </c>
       <c r="C3">
-        <v>1545.984559156157</v>
+        <v>1533.005524158699</v>
       </c>
       <c r="D3">
-        <v>1037.404559156157</v>
+        <v>1038.345524158699</v>
       </c>
       <c r="E3">
-        <v>-673.6800000000001</v>
+        <v>-659.76</v>
       </c>
       <c r="F3">
-        <v>13.92</v>
+        <v>27.84</v>
       </c>
       <c r="G3">
         <v>522.5</v>
@@ -1521,28 +1521,28 @@
         <v>108.3</v>
       </c>
       <c r="M3">
-        <v>0.7001759999999999</v>
+        <v>1.400352</v>
       </c>
       <c r="N3">
-        <v>107.599824</v>
+        <v>106.899648</v>
       </c>
       <c r="O3">
-        <v>9.683984160000001</v>
+        <v>9.620968320000001</v>
       </c>
       <c r="P3">
-        <v>97.91583984000002</v>
+        <v>97.27867968000001</v>
       </c>
       <c r="Q3">
-        <v>233.11583984</v>
+        <v>232.47867968</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.09630445433478044</v>
+        <v>0.09677384672103673</v>
       </c>
       <c r="T3">
-        <v>0.7349013483770488</v>
+        <v>0.7417315795343058</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1559,7 +1559,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>154.6753959004594</v>
+        <v>77.33769795022968</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1567,22 +1567,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.09575382978661599</v>
+        <v>0.09570851978179937</v>
       </c>
       <c r="C4">
-        <v>1533.005524158699</v>
+        <v>1520.028197692329</v>
       </c>
       <c r="D4">
-        <v>1038.345524158699</v>
+        <v>1039.288197692329</v>
       </c>
       <c r="E4">
-        <v>-659.76</v>
+        <v>-645.84</v>
       </c>
       <c r="F4">
-        <v>27.84</v>
+        <v>41.76</v>
       </c>
       <c r="G4">
         <v>522.5</v>
@@ -1603,28 +1603,28 @@
         <v>108.3</v>
       </c>
       <c r="M4">
-        <v>1.400352</v>
+        <v>2.100528</v>
       </c>
       <c r="N4">
-        <v>106.899648</v>
+        <v>106.199472</v>
       </c>
       <c r="O4">
-        <v>9.620968320000001</v>
+        <v>9.557952480000001</v>
       </c>
       <c r="P4">
-        <v>97.27867968000001</v>
+        <v>96.64151952000002</v>
       </c>
       <c r="Q4">
-        <v>232.47867968</v>
+        <v>231.84151952</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.09677384672103673</v>
+        <v>0.0972529173008241</v>
       </c>
       <c r="T4">
-        <v>0.7417315795343058</v>
+        <v>0.7487026401999598</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1641,7 +1641,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>77.33769795022968</v>
+        <v>51.55846530015312</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1649,22 +1649,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.09570851978179937</v>
+        <v>0.09566320977698273</v>
       </c>
       <c r="C5">
-        <v>1520.028197692329</v>
+        <v>1507.052584414603</v>
       </c>
       <c r="D5">
-        <v>1039.288197692329</v>
+        <v>1040.232584414603</v>
       </c>
       <c r="E5">
-        <v>-645.84</v>
+        <v>-631.9200000000001</v>
       </c>
       <c r="F5">
-        <v>41.76</v>
+        <v>55.68</v>
       </c>
       <c r="G5">
         <v>522.5</v>
@@ -1685,28 +1685,28 @@
         <v>108.3</v>
       </c>
       <c r="M5">
-        <v>2.100528</v>
+        <v>2.800704</v>
       </c>
       <c r="N5">
-        <v>106.199472</v>
+        <v>105.499296</v>
       </c>
       <c r="O5">
-        <v>9.557952480000001</v>
+        <v>9.494936640000001</v>
       </c>
       <c r="P5">
-        <v>96.64151952000002</v>
+        <v>96.00435936000001</v>
       </c>
       <c r="Q5">
-        <v>231.84151952</v>
+        <v>231.20435936</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.0972529173008241</v>
+        <v>0.09774196851769035</v>
       </c>
       <c r="T5">
-        <v>0.7487026401999598</v>
+        <v>0.7558189312961482</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1723,7 +1723,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>51.55846530015312</v>
+        <v>38.66884897511484</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1731,22 +1731,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.09566320977698273</v>
+        <v>0.09561789977216612</v>
       </c>
       <c r="C6">
-        <v>1507.052584414603</v>
+        <v>1494.078689000018</v>
       </c>
       <c r="D6">
-        <v>1040.232584414603</v>
+        <v>1041.178689000018</v>
       </c>
       <c r="E6">
-        <v>-631.9200000000001</v>
+        <v>-618</v>
       </c>
       <c r="F6">
-        <v>55.68</v>
+        <v>69.60000000000001</v>
       </c>
       <c r="G6">
         <v>522.5</v>
@@ -1767,28 +1767,28 @@
         <v>108.3</v>
       </c>
       <c r="M6">
-        <v>2.800704</v>
+        <v>3.50088</v>
       </c>
       <c r="N6">
-        <v>105.499296</v>
+        <v>104.79912</v>
       </c>
       <c r="O6">
-        <v>9.494936640000001</v>
+        <v>9.4319208</v>
       </c>
       <c r="P6">
-        <v>96.00435936000001</v>
+        <v>95.36719920000002</v>
       </c>
       <c r="Q6">
-        <v>231.20435936</v>
+        <v>230.5671992</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.09774196851769035</v>
+        <v>0.09824131554964854</v>
       </c>
       <c r="T6">
-        <v>0.7558189312961482</v>
+        <v>0.7630850390469933</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1805,7 +1805,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>38.66884897511484</v>
+        <v>30.93507918009186</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1813,22 +1813,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.09561789977216612</v>
+        <v>0.09557258976734952</v>
       </c>
       <c r="C7">
-        <v>1494.078689000018</v>
+        <v>1481.106516140098</v>
       </c>
       <c r="D7">
-        <v>1041.178689000018</v>
+        <v>1042.126516140098</v>
       </c>
       <c r="E7">
-        <v>-618</v>
+        <v>-604.08</v>
       </c>
       <c r="F7">
-        <v>69.60000000000001</v>
+        <v>83.52000000000001</v>
       </c>
       <c r="G7">
         <v>522.5</v>
@@ -1849,28 +1849,28 @@
         <v>108.3</v>
       </c>
       <c r="M7">
-        <v>3.50088</v>
+        <v>4.201056</v>
       </c>
       <c r="N7">
-        <v>104.79912</v>
+        <v>104.098944</v>
       </c>
       <c r="O7">
-        <v>9.4319208</v>
+        <v>9.368904960000002</v>
       </c>
       <c r="P7">
-        <v>95.36719920000002</v>
+        <v>94.73003904000001</v>
       </c>
       <c r="Q7">
-        <v>230.5671992</v>
+        <v>229.93003904</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.09824131554964854</v>
+        <v>0.09875128698654204</v>
       </c>
       <c r="T7">
-        <v>0.7630850390469933</v>
+        <v>0.7705057448350906</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1887,7 +1887,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>30.93507918009186</v>
+        <v>25.77923265007655</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1895,22 +1895,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.09557258976734952</v>
+        <v>0.09552727976253288</v>
       </c>
       <c r="C8">
-        <v>1481.106516140098</v>
+        <v>1468.136070543462</v>
       </c>
       <c r="D8">
-        <v>1042.126516140098</v>
+        <v>1043.076070543462</v>
       </c>
       <c r="E8">
-        <v>-604.08</v>
+        <v>-590.1600000000001</v>
       </c>
       <c r="F8">
-        <v>83.52</v>
+        <v>97.43999999999998</v>
       </c>
       <c r="G8">
         <v>522.5</v>
@@ -1931,28 +1931,28 @@
         <v>108.3</v>
       </c>
       <c r="M8">
-        <v>4.201055999999999</v>
+        <v>4.901231999999999</v>
       </c>
       <c r="N8">
-        <v>104.098944</v>
+        <v>103.398768</v>
       </c>
       <c r="O8">
-        <v>9.368904960000002</v>
+        <v>9.305889120000002</v>
       </c>
       <c r="P8">
-        <v>94.73003904000001</v>
+        <v>94.09287888000001</v>
       </c>
       <c r="Q8">
-        <v>229.93003904</v>
+        <v>229.29287888</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.09875128698654204</v>
+        <v>0.09927222555111062</v>
       </c>
       <c r="T8">
-        <v>0.7705057448350906</v>
+        <v>0.7780860356938993</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1969,7 +1969,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>25.77923265007656</v>
+        <v>22.09648512863705</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1977,22 +1977,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.09552727976253286</v>
+        <v>0.09548196975771625</v>
       </c>
       <c r="C9">
-        <v>1468.136070543462</v>
+        <v>1455.167356935908</v>
       </c>
       <c r="D9">
-        <v>1043.076070543462</v>
+        <v>1044.027356935908</v>
       </c>
       <c r="E9">
-        <v>-590.16</v>
+        <v>-576.24</v>
       </c>
       <c r="F9">
-        <v>97.44000000000001</v>
+        <v>111.36</v>
       </c>
       <c r="G9">
         <v>522.5</v>
@@ -2013,28 +2013,28 @@
         <v>108.3</v>
       </c>
       <c r="M9">
-        <v>4.901232</v>
+        <v>5.601407999999999</v>
       </c>
       <c r="N9">
-        <v>103.398768</v>
+        <v>102.698592</v>
       </c>
       <c r="O9">
-        <v>9.305889120000002</v>
+        <v>9.242873280000001</v>
       </c>
       <c r="P9">
-        <v>94.09287888000001</v>
+        <v>93.45571872000002</v>
       </c>
       <c r="Q9">
-        <v>229.29287888</v>
+        <v>228.65571872</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.09927222555111062</v>
+        <v>0.09980448886708287</v>
       </c>
       <c r="T9">
-        <v>0.7780860356938994</v>
+        <v>0.7858311154844215</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2051,7 +2051,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>22.09648512863705</v>
+        <v>19.33442448755742</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2059,22 +2059,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.09548196975771625</v>
+        <v>0.09543665975289964</v>
       </c>
       <c r="C10">
-        <v>1455.167356935908</v>
+        <v>1442.200380060489</v>
       </c>
       <c r="D10">
-        <v>1044.027356935908</v>
+        <v>1044.980380060489</v>
       </c>
       <c r="E10">
-        <v>-576.24</v>
+        <v>-562.3200000000001</v>
       </c>
       <c r="F10">
-        <v>111.36</v>
+        <v>125.28</v>
       </c>
       <c r="G10">
         <v>522.5</v>
@@ -2095,28 +2095,28 @@
         <v>108.3</v>
       </c>
       <c r="M10">
-        <v>5.601407999999999</v>
+        <v>6.301584</v>
       </c>
       <c r="N10">
-        <v>102.698592</v>
+        <v>101.998416</v>
       </c>
       <c r="O10">
-        <v>9.242873280000001</v>
+        <v>9.179857440000001</v>
       </c>
       <c r="P10">
-        <v>93.45571872000002</v>
+        <v>92.81855856</v>
       </c>
       <c r="Q10">
-        <v>228.65571872</v>
+        <v>228.01855856</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.09980448886708287</v>
+        <v>0.1003484502779117</v>
       </c>
       <c r="T10">
-        <v>0.7858311154844215</v>
+        <v>0.7937464168088013</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2133,7 +2133,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>19.33442448755742</v>
+        <v>17.18615510005104</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2141,22 +2141,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.09543665975289964</v>
+        <v>0.095391349748083</v>
       </c>
       <c r="C11">
-        <v>1442.200380060489</v>
+        <v>1429.235144677591</v>
       </c>
       <c r="D11">
-        <v>1044.980380060489</v>
+        <v>1045.935144677591</v>
       </c>
       <c r="E11">
-        <v>-562.3200000000001</v>
+        <v>-548.4000000000001</v>
       </c>
       <c r="F11">
-        <v>125.28</v>
+        <v>139.2</v>
       </c>
       <c r="G11">
         <v>522.5</v>
@@ -2177,28 +2177,28 @@
         <v>108.3</v>
       </c>
       <c r="M11">
-        <v>6.301584</v>
+        <v>7.001759999999999</v>
       </c>
       <c r="N11">
-        <v>101.998416</v>
+        <v>101.29824</v>
       </c>
       <c r="O11">
-        <v>9.179857440000001</v>
+        <v>9.116841600000001</v>
       </c>
       <c r="P11">
-        <v>92.81855856</v>
+        <v>92.18139840000001</v>
       </c>
       <c r="Q11">
-        <v>228.01855856</v>
+        <v>227.3813984</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1003484502779117</v>
+        <v>0.1009044997200922</v>
       </c>
       <c r="T11">
-        <v>0.7937464168088013</v>
+        <v>0.8018376137181672</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2215,7 +2215,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>17.18615510005104</v>
+        <v>15.46753959004593</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2223,22 +2223,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.095391349748083</v>
+        <v>0.09534603974326637</v>
       </c>
       <c r="C12">
-        <v>1429.235144677591</v>
+        <v>1416.271655565016</v>
       </c>
       <c r="D12">
-        <v>1045.935144677591</v>
+        <v>1046.891655565016</v>
       </c>
       <c r="E12">
-        <v>-548.4</v>
+        <v>-534.48</v>
       </c>
       <c r="F12">
-        <v>139.2</v>
+        <v>153.12</v>
       </c>
       <c r="G12">
         <v>522.5</v>
@@ -2259,28 +2259,28 @@
         <v>108.3</v>
       </c>
       <c r="M12">
-        <v>7.001760000000001</v>
+        <v>7.701936</v>
       </c>
       <c r="N12">
-        <v>101.29824</v>
+        <v>100.598064</v>
       </c>
       <c r="O12">
-        <v>9.116841600000001</v>
+        <v>9.05382576</v>
       </c>
       <c r="P12">
-        <v>92.18139840000001</v>
+        <v>91.54423824000001</v>
       </c>
       <c r="Q12">
-        <v>227.3813984</v>
+        <v>226.74423824</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1009044997200922</v>
+        <v>0.1014730446553555</v>
       </c>
       <c r="T12">
-        <v>0.8018376137181672</v>
+        <v>0.8101106352771817</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2297,7 +2297,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>15.46753959004593</v>
+        <v>14.06139962731448</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2305,22 +2305,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.09534603974326637</v>
+        <v>0.09530072973844976</v>
       </c>
       <c r="C13">
-        <v>1416.271655565016</v>
+        <v>1403.309917518057</v>
       </c>
       <c r="D13">
-        <v>1046.891655565016</v>
+        <v>1047.849917518057</v>
       </c>
       <c r="E13">
-        <v>-534.48</v>
+        <v>-520.5600000000001</v>
       </c>
       <c r="F13">
-        <v>153.12</v>
+        <v>167.04</v>
       </c>
       <c r="G13">
         <v>522.5</v>
@@ -2341,28 +2341,28 @@
         <v>108.3</v>
       </c>
       <c r="M13">
-        <v>7.701936</v>
+        <v>8.402111999999999</v>
       </c>
       <c r="N13">
-        <v>100.598064</v>
+        <v>99.89788800000001</v>
       </c>
       <c r="O13">
-        <v>9.05382576</v>
+        <v>8.99080992</v>
       </c>
       <c r="P13">
-        <v>91.54423824000001</v>
+        <v>90.90707808000001</v>
       </c>
       <c r="Q13">
-        <v>226.74423824</v>
+        <v>226.10707808</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1014730446553555</v>
+        <v>0.1020545110664202</v>
       </c>
       <c r="T13">
-        <v>0.8101106352771817</v>
+        <v>0.8185716800534468</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2379,7 +2379,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>14.06139962731448</v>
+        <v>12.88961632503828</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2387,22 +2387,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.09530072973844976</v>
+        <v>0.09543286973363312</v>
       </c>
       <c r="C14">
-        <v>1403.309917518057</v>
+        <v>1386.600175885208</v>
       </c>
       <c r="D14">
-        <v>1047.849917518057</v>
+        <v>1045.060175885208</v>
       </c>
       <c r="E14">
-        <v>-520.5600000000001</v>
+        <v>-506.64</v>
       </c>
       <c r="F14">
-        <v>167.04</v>
+        <v>180.96</v>
       </c>
       <c r="G14">
         <v>522.5</v>
@@ -2423,45 +2423,45 @@
         <v>108.3</v>
       </c>
       <c r="M14">
-        <v>8.402111999999999</v>
+        <v>9.373728</v>
       </c>
       <c r="N14">
-        <v>99.89788800000001</v>
+        <v>98.92627200000001</v>
       </c>
       <c r="O14">
-        <v>8.99080992</v>
+        <v>8.90336448</v>
       </c>
       <c r="P14">
-        <v>90.90707808000001</v>
+        <v>90.02290752000002</v>
       </c>
       <c r="Q14">
-        <v>226.10707808</v>
+        <v>225.22290752</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1020545110664202</v>
+        <v>0.1026493445214174</v>
       </c>
       <c r="T14">
-        <v>0.8185716800534468</v>
+        <v>0.8272272316061776</v>
       </c>
       <c r="U14">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V14">
         <v>0.09</v>
       </c>
       <c r="W14">
-        <v>0.045773</v>
+        <v>0.047138</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y14">
-        <v>12.88961632503828</v>
+        <v>11.55356758805035</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2469,22 +2469,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.09543286973363312</v>
+        <v>0.09540120972881651</v>
       </c>
       <c r="C15">
-        <v>1386.600175885208</v>
+        <v>1373.347228370078</v>
       </c>
       <c r="D15">
-        <v>1045.060175885208</v>
+        <v>1045.727228370078</v>
       </c>
       <c r="E15">
-        <v>-506.64</v>
+        <v>-492.72</v>
       </c>
       <c r="F15">
-        <v>180.96</v>
+        <v>194.88</v>
       </c>
       <c r="G15">
         <v>522.5</v>
@@ -2505,28 +2505,28 @@
         <v>108.3</v>
       </c>
       <c r="M15">
-        <v>9.373728</v>
+        <v>10.094784</v>
       </c>
       <c r="N15">
-        <v>98.92627200000001</v>
+        <v>98.20521600000001</v>
       </c>
       <c r="O15">
-        <v>8.90336448</v>
+        <v>8.838469440000001</v>
       </c>
       <c r="P15">
-        <v>90.02290752000002</v>
+        <v>89.36674656000001</v>
       </c>
       <c r="Q15">
-        <v>225.22290752</v>
+        <v>224.56674656</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1026493445214174</v>
+        <v>0.1032580113125773</v>
       </c>
       <c r="T15">
-        <v>0.8272272316061776</v>
+        <v>0.8360840750554835</v>
       </c>
       <c r="U15">
         <v>0.0518</v>
@@ -2543,7 +2543,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>11.55356758805035</v>
+        <v>10.72831276033246</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2551,22 +2551,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.09540120972881651</v>
+        <v>0.09536954972399989</v>
       </c>
       <c r="C16">
-        <v>1373.347228370078</v>
+        <v>1360.095132946</v>
       </c>
       <c r="D16">
-        <v>1045.727228370078</v>
+        <v>1046.395132946</v>
       </c>
       <c r="E16">
-        <v>-492.72</v>
+        <v>-478.8</v>
       </c>
       <c r="F16">
-        <v>194.88</v>
+        <v>208.8</v>
       </c>
       <c r="G16">
         <v>522.5</v>
@@ -2587,28 +2587,28 @@
         <v>108.3</v>
       </c>
       <c r="M16">
-        <v>10.094784</v>
+        <v>10.81584</v>
       </c>
       <c r="N16">
-        <v>98.20521600000001</v>
+        <v>97.48416</v>
       </c>
       <c r="O16">
-        <v>8.838469440000001</v>
+        <v>8.773574399999999</v>
       </c>
       <c r="P16">
-        <v>89.36674656000001</v>
+        <v>88.7105856</v>
       </c>
       <c r="Q16">
-        <v>224.56674656</v>
+        <v>223.9105856</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1032580113125773</v>
+        <v>0.103880999675294</v>
       </c>
       <c r="T16">
-        <v>0.8360840750554835</v>
+        <v>0.8451493148212439</v>
       </c>
       <c r="U16">
         <v>0.0518</v>
@@ -2625,7 +2625,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>10.72831276033246</v>
+        <v>10.01309190964363</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2633,22 +2633,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.09536954972399989</v>
+        <v>0.09558540971918324</v>
       </c>
       <c r="C17">
-        <v>1360.095132946</v>
+        <v>1341.638164190864</v>
       </c>
       <c r="D17">
-        <v>1046.395132946</v>
+        <v>1041.858164190864</v>
       </c>
       <c r="E17">
-        <v>-478.8000000000001</v>
+        <v>-464.88</v>
       </c>
       <c r="F17">
-        <v>208.8</v>
+        <v>222.72</v>
       </c>
       <c r="G17">
         <v>522.5</v>
@@ -2669,45 +2669,45 @@
         <v>108.3</v>
       </c>
       <c r="M17">
-        <v>10.81584</v>
+        <v>11.91552</v>
       </c>
       <c r="N17">
-        <v>97.48416000000002</v>
+        <v>96.38448000000001</v>
       </c>
       <c r="O17">
-        <v>8.773574400000001</v>
+        <v>8.6746032</v>
       </c>
       <c r="P17">
-        <v>88.71058560000002</v>
+        <v>87.70987680000002</v>
       </c>
       <c r="Q17">
-        <v>223.9105856</v>
+        <v>222.9098768</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.103880999675294</v>
+        <v>0.1045188210942658</v>
       </c>
       <c r="T17">
-        <v>0.8451493148212439</v>
+        <v>0.8544303936290459</v>
       </c>
       <c r="U17">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V17">
         <v>0.09</v>
       </c>
       <c r="W17">
-        <v>0.047138</v>
+        <v>0.048685</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y17">
-        <v>10.01309190964364</v>
+        <v>9.088986464711571</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2715,22 +2715,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.09558540971918324</v>
+        <v>0.09556921971436663</v>
       </c>
       <c r="C18">
-        <v>1341.638164190864</v>
+        <v>1328.057082277047</v>
       </c>
       <c r="D18">
-        <v>1041.858164190864</v>
+        <v>1042.197082277047</v>
       </c>
       <c r="E18">
-        <v>-464.88</v>
+        <v>-450.96</v>
       </c>
       <c r="F18">
-        <v>222.72</v>
+        <v>236.64</v>
       </c>
       <c r="G18">
         <v>522.5</v>
@@ -2751,28 +2751,28 @@
         <v>108.3</v>
       </c>
       <c r="M18">
-        <v>11.91552</v>
+        <v>12.66024</v>
       </c>
       <c r="N18">
-        <v>96.38448000000001</v>
+        <v>95.63976000000001</v>
       </c>
       <c r="O18">
-        <v>8.6746032</v>
+        <v>8.607578400000001</v>
       </c>
       <c r="P18">
-        <v>87.70987680000002</v>
+        <v>87.0321816</v>
       </c>
       <c r="Q18">
-        <v>222.9098768</v>
+        <v>222.2321816</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1045188210942658</v>
+        <v>0.1051720117040562</v>
       </c>
       <c r="T18">
-        <v>0.8544303936290459</v>
+        <v>0.8639351128900481</v>
       </c>
       <c r="U18">
         <v>0.0535</v>
@@ -2789,7 +2789,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>9.088986464711571</v>
+        <v>8.554340202081477</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2797,22 +2797,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.09556921971436663</v>
+        <v>0.09555302970955</v>
       </c>
       <c r="C19">
-        <v>1328.057082277047</v>
+        <v>1314.47622093615</v>
       </c>
       <c r="D19">
-        <v>1042.197082277047</v>
+        <v>1042.536220936149</v>
       </c>
       <c r="E19">
-        <v>-450.96</v>
+        <v>-437.04</v>
       </c>
       <c r="F19">
-        <v>236.64</v>
+        <v>250.56</v>
       </c>
       <c r="G19">
         <v>522.5</v>
@@ -2833,28 +2833,28 @@
         <v>108.3</v>
       </c>
       <c r="M19">
-        <v>12.66024</v>
+        <v>13.40496</v>
       </c>
       <c r="N19">
-        <v>95.63976000000001</v>
+        <v>94.89504000000001</v>
       </c>
       <c r="O19">
-        <v>8.607578400000001</v>
+        <v>8.540553600000001</v>
       </c>
       <c r="P19">
-        <v>87.0321816</v>
+        <v>86.35448640000001</v>
       </c>
       <c r="Q19">
-        <v>222.2321816</v>
+        <v>221.5544864</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1051720117040562</v>
+        <v>0.1058411337921342</v>
       </c>
       <c r="T19">
-        <v>0.8639351128900481</v>
+        <v>0.8736716545720504</v>
       </c>
       <c r="U19">
         <v>0.0535</v>
@@ -2871,7 +2871,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>8.554340202081477</v>
+        <v>8.079099079743617</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2879,22 +2879,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.09555302970955001</v>
+        <v>0.09553683970473338</v>
       </c>
       <c r="C20">
-        <v>1314.476220936149</v>
+        <v>1300.895580383566</v>
       </c>
       <c r="D20">
-        <v>1042.536220936149</v>
+        <v>1042.875580383566</v>
       </c>
       <c r="E20">
-        <v>-437.04</v>
+        <v>-423.12</v>
       </c>
       <c r="F20">
-        <v>250.56</v>
+        <v>264.48</v>
       </c>
       <c r="G20">
         <v>522.5</v>
@@ -2915,28 +2915,28 @@
         <v>108.3</v>
       </c>
       <c r="M20">
-        <v>13.40496</v>
+        <v>14.14968</v>
       </c>
       <c r="N20">
-        <v>94.89504000000001</v>
+        <v>94.15032000000001</v>
       </c>
       <c r="O20">
-        <v>8.540553600000001</v>
+        <v>8.4735288</v>
       </c>
       <c r="P20">
-        <v>86.35448640000001</v>
+        <v>85.67679120000001</v>
       </c>
       <c r="Q20">
-        <v>221.5544864</v>
+        <v>220.8767912</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1058411337921342</v>
+        <v>0.1065267774132511</v>
       </c>
       <c r="T20">
-        <v>0.8736716545720504</v>
+        <v>0.8836486046906453</v>
       </c>
       <c r="U20">
         <v>0.0535</v>
@@ -2953,7 +2953,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>8.079099079743617</v>
+        <v>7.65388333870448</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2961,22 +2961,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.09553683970473338</v>
+        <v>0.09566624969991677</v>
       </c>
       <c r="C21">
-        <v>1300.895580383566</v>
+        <v>1284.269170243512</v>
       </c>
       <c r="D21">
-        <v>1042.875580383566</v>
+        <v>1040.169170243512</v>
       </c>
       <c r="E21">
-        <v>-423.12</v>
+        <v>-409.2</v>
       </c>
       <c r="F21">
-        <v>264.48</v>
+        <v>278.4</v>
       </c>
       <c r="G21">
         <v>522.5</v>
@@ -2997,45 +2997,45 @@
         <v>108.3</v>
       </c>
       <c r="M21">
-        <v>14.14968</v>
+        <v>15.11712</v>
       </c>
       <c r="N21">
-        <v>94.15032000000001</v>
+        <v>93.18288000000001</v>
       </c>
       <c r="O21">
-        <v>8.4735288</v>
+        <v>8.386459200000001</v>
       </c>
       <c r="P21">
-        <v>85.67679120000001</v>
+        <v>84.79642080000001</v>
       </c>
       <c r="Q21">
-        <v>220.8767912</v>
+        <v>219.9964208</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1065267774132511</v>
+        <v>0.107229562124896</v>
       </c>
       <c r="T21">
-        <v>0.8836486046906453</v>
+        <v>0.8938749785622051</v>
       </c>
       <c r="U21">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V21">
         <v>0.09</v>
       </c>
       <c r="W21">
-        <v>0.048685</v>
+        <v>0.04941300000000001</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y21">
-        <v>7.65388333870448</v>
+        <v>7.164062996126247</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3043,22 +3043,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.09566624969991677</v>
+        <v>0.09565733969510012</v>
       </c>
       <c r="C22">
-        <v>1284.269170243512</v>
+        <v>1270.53505886841</v>
       </c>
       <c r="D22">
-        <v>1040.169170243512</v>
+        <v>1040.35505886841</v>
       </c>
       <c r="E22">
-        <v>-409.2</v>
+        <v>-395.28</v>
       </c>
       <c r="F22">
-        <v>278.4</v>
+        <v>292.3200000000001</v>
       </c>
       <c r="G22">
         <v>522.5</v>
@@ -3079,28 +3079,28 @@
         <v>108.3</v>
       </c>
       <c r="M22">
-        <v>15.11712</v>
+        <v>15.872976</v>
       </c>
       <c r="N22">
-        <v>93.18288000000001</v>
+        <v>92.427024</v>
       </c>
       <c r="O22">
-        <v>8.386459200000001</v>
+        <v>8.31843216</v>
       </c>
       <c r="P22">
-        <v>84.79642080000001</v>
+        <v>84.10859184</v>
       </c>
       <c r="Q22">
-        <v>219.9964208</v>
+        <v>219.30859184</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.107229562124896</v>
+        <v>0.1079501388545571</v>
       </c>
       <c r="T22">
-        <v>0.8938749785622051</v>
+        <v>0.904360247974817</v>
       </c>
       <c r="U22">
         <v>0.0543</v>
@@ -3117,7 +3117,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>7.164062996126247</v>
+        <v>6.822917139167853</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3125,22 +3125,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.09565733969510012</v>
+        <v>0.0956484296902835</v>
       </c>
       <c r="C23">
-        <v>1270.53505886841</v>
+        <v>1256.801013945493</v>
       </c>
       <c r="D23">
-        <v>1040.35505886841</v>
+        <v>1040.541013945493</v>
       </c>
       <c r="E23">
-        <v>-395.28</v>
+        <v>-381.36</v>
       </c>
       <c r="F23">
-        <v>292.32</v>
+        <v>306.24</v>
       </c>
       <c r="G23">
         <v>522.5</v>
@@ -3161,28 +3161,28 @@
         <v>108.3</v>
       </c>
       <c r="M23">
-        <v>15.872976</v>
+        <v>16.628832</v>
       </c>
       <c r="N23">
-        <v>92.42702400000002</v>
+        <v>91.67116800000001</v>
       </c>
       <c r="O23">
-        <v>8.31843216</v>
+        <v>8.25040512</v>
       </c>
       <c r="P23">
-        <v>84.10859184000002</v>
+        <v>83.42076288000001</v>
       </c>
       <c r="Q23">
-        <v>219.30859184</v>
+        <v>218.62076288</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1079501388545571</v>
+        <v>0.1086891919106199</v>
       </c>
       <c r="T23">
-        <v>0.904360247974817</v>
+        <v>0.9151143704492907</v>
       </c>
       <c r="U23">
         <v>0.0543</v>
@@ -3199,7 +3199,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>6.822917139167854</v>
+        <v>6.512784541932952</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3207,22 +3207,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.0956484296902835</v>
+        <v>0.0956395196854669</v>
       </c>
       <c r="C24">
-        <v>1256.801013945493</v>
+        <v>1243.067035510401</v>
       </c>
       <c r="D24">
-        <v>1040.541013945493</v>
+        <v>1040.727035510401</v>
       </c>
       <c r="E24">
-        <v>-381.36</v>
+        <v>-367.44</v>
       </c>
       <c r="F24">
-        <v>306.24</v>
+        <v>320.16</v>
       </c>
       <c r="G24">
         <v>522.5</v>
@@ -3243,28 +3243,28 @@
         <v>108.3</v>
       </c>
       <c r="M24">
-        <v>16.628832</v>
+        <v>17.384688</v>
       </c>
       <c r="N24">
-        <v>91.67116800000001</v>
+        <v>90.91531200000001</v>
       </c>
       <c r="O24">
-        <v>8.25040512</v>
+        <v>8.182378080000001</v>
       </c>
       <c r="P24">
-        <v>83.42076288000001</v>
+        <v>82.73293392000001</v>
       </c>
       <c r="Q24">
-        <v>218.62076288</v>
+        <v>217.93293392</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1086891919106199</v>
+        <v>0.109447441149957</v>
       </c>
       <c r="T24">
-        <v>0.9151143704492907</v>
+        <v>0.9261478207802443</v>
       </c>
       <c r="U24">
         <v>0.0543</v>
@@ -3281,7 +3281,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>6.512784541932952</v>
+        <v>6.229619996631519</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3289,22 +3289,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.0956395196854669</v>
+        <v>0.09584900968065027</v>
       </c>
       <c r="C25">
-        <v>1243.067035510401</v>
+        <v>1224.790867365468</v>
       </c>
       <c r="D25">
-        <v>1040.727035510401</v>
+        <v>1036.370867365468</v>
       </c>
       <c r="E25">
-        <v>-367.44</v>
+        <v>-353.52</v>
       </c>
       <c r="F25">
-        <v>320.16</v>
+        <v>334.08</v>
       </c>
       <c r="G25">
         <v>522.5</v>
@@ -3325,45 +3325,45 @@
         <v>108.3</v>
       </c>
       <c r="M25">
-        <v>17.384688</v>
+        <v>18.474624</v>
       </c>
       <c r="N25">
-        <v>90.91531200000001</v>
+        <v>89.82537600000001</v>
       </c>
       <c r="O25">
-        <v>8.182378080000001</v>
+        <v>8.084283839999999</v>
       </c>
       <c r="P25">
-        <v>82.73293392000001</v>
+        <v>81.74109216000001</v>
       </c>
       <c r="Q25">
-        <v>217.93293392</v>
+        <v>216.94109216</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.109447441149957</v>
+        <v>0.1102256443166451</v>
       </c>
       <c r="T25">
-        <v>0.9261478207802443</v>
+        <v>0.9374716250672758</v>
       </c>
       <c r="U25">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V25">
         <v>0.09</v>
       </c>
       <c r="W25">
-        <v>0.04941300000000001</v>
+        <v>0.05032300000000001</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y25">
-        <v>6.229619996631519</v>
+        <v>5.862094947101494</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3371,22 +3371,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.09584900968065027</v>
+        <v>0.09584919967583364</v>
       </c>
       <c r="C26">
-        <v>1224.790867365468</v>
+        <v>1210.866933127273</v>
       </c>
       <c r="D26">
-        <v>1036.370867365468</v>
+        <v>1036.366933127273</v>
       </c>
       <c r="E26">
-        <v>-353.52</v>
+        <v>-339.6</v>
       </c>
       <c r="F26">
-        <v>334.08</v>
+        <v>348</v>
       </c>
       <c r="G26">
         <v>522.5</v>
@@ -3407,28 +3407,28 @@
         <v>108.3</v>
       </c>
       <c r="M26">
-        <v>18.474624</v>
+        <v>19.2444</v>
       </c>
       <c r="N26">
-        <v>89.82537600000001</v>
+        <v>89.05560000000001</v>
       </c>
       <c r="O26">
-        <v>8.084283839999999</v>
+        <v>8.015004000000001</v>
       </c>
       <c r="P26">
-        <v>81.74109216000001</v>
+        <v>81.04059600000001</v>
       </c>
       <c r="Q26">
-        <v>216.94109216</v>
+        <v>216.240596</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1102256443166451</v>
+        <v>0.1110245995677782</v>
       </c>
       <c r="T26">
-        <v>0.9374716250672755</v>
+        <v>0.9490973974686278</v>
       </c>
       <c r="U26">
         <v>0.0553</v>
@@ -3445,7 +3445,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>5.862094947101495</v>
+        <v>5.627611149217435</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3453,22 +3453,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.09584919967583364</v>
+        <v>0.095849389671017</v>
       </c>
       <c r="C27">
-        <v>1210.866933127273</v>
+        <v>1196.942998918948</v>
       </c>
       <c r="D27">
-        <v>1036.366933127273</v>
+        <v>1036.362998918949</v>
       </c>
       <c r="E27">
-        <v>-339.6</v>
+        <v>-325.68</v>
       </c>
       <c r="F27">
-        <v>348</v>
+        <v>361.92</v>
       </c>
       <c r="G27">
         <v>522.5</v>
@@ -3489,28 +3489,28 @@
         <v>108.3</v>
       </c>
       <c r="M27">
-        <v>19.2444</v>
+        <v>20.014176</v>
       </c>
       <c r="N27">
-        <v>89.05560000000001</v>
+        <v>88.28582400000001</v>
       </c>
       <c r="O27">
-        <v>8.015004000000001</v>
+        <v>7.94572416</v>
       </c>
       <c r="P27">
-        <v>81.04059600000001</v>
+        <v>80.34009984000001</v>
       </c>
       <c r="Q27">
-        <v>216.240596</v>
+        <v>215.54009984</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1110245995677782</v>
+        <v>0.111845148204077</v>
       </c>
       <c r="T27">
-        <v>0.9490973974686278</v>
+        <v>0.9610373799348814</v>
       </c>
       <c r="U27">
         <v>0.0553</v>
@@ -3527,7 +3527,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>5.627611149217435</v>
+        <v>5.411164566555225</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3535,22 +3535,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.095849389671017</v>
+        <v>0.09584957966620038</v>
       </c>
       <c r="C28">
-        <v>1196.942998918948</v>
+        <v>1183.019064740493</v>
       </c>
       <c r="D28">
-        <v>1036.362998918949</v>
+        <v>1036.359064740493</v>
       </c>
       <c r="E28">
-        <v>-325.68</v>
+        <v>-311.76</v>
       </c>
       <c r="F28">
-        <v>361.92</v>
+        <v>375.84</v>
       </c>
       <c r="G28">
         <v>522.5</v>
@@ -3571,28 +3571,28 @@
         <v>108.3</v>
       </c>
       <c r="M28">
-        <v>20.014176</v>
+        <v>20.783952</v>
       </c>
       <c r="N28">
-        <v>88.28582400000001</v>
+        <v>87.51604800000001</v>
       </c>
       <c r="O28">
-        <v>7.94572416</v>
+        <v>7.876444320000001</v>
       </c>
       <c r="P28">
-        <v>80.34009984000001</v>
+        <v>79.63960368000001</v>
       </c>
       <c r="Q28">
-        <v>215.54009984</v>
+        <v>214.83960368</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.111845148204077</v>
+        <v>0.112688177624932</v>
       </c>
       <c r="T28">
-        <v>0.9610373799348814</v>
+        <v>0.9733044852084295</v>
       </c>
       <c r="U28">
         <v>0.0553</v>
@@ -3609,7 +3609,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>5.411164566555225</v>
+        <v>5.210751064090218</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3617,22 +3617,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.09584957966620038</v>
+        <v>0.09584976966138375</v>
       </c>
       <c r="C29">
-        <v>1183.019064740493</v>
+        <v>1169.095130591907</v>
       </c>
       <c r="D29">
-        <v>1036.359064740493</v>
+        <v>1036.355130591907</v>
       </c>
       <c r="E29">
-        <v>-311.76</v>
+        <v>-297.84</v>
       </c>
       <c r="F29">
-        <v>375.84</v>
+        <v>389.76</v>
       </c>
       <c r="G29">
         <v>522.5</v>
@@ -3653,28 +3653,28 @@
         <v>108.3</v>
       </c>
       <c r="M29">
-        <v>20.783952</v>
+        <v>21.553728</v>
       </c>
       <c r="N29">
-        <v>87.51604800000001</v>
+        <v>86.746272</v>
       </c>
       <c r="O29">
-        <v>7.876444320000001</v>
+        <v>7.80716448</v>
       </c>
       <c r="P29">
-        <v>79.63960368000001</v>
+        <v>78.93910752000001</v>
       </c>
       <c r="Q29">
-        <v>214.83960368</v>
+        <v>214.13910752</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.112688177624932</v>
+        <v>0.1135546245296997</v>
       </c>
       <c r="T29">
-        <v>0.9733044852084295</v>
+        <v>0.9859123434062429</v>
       </c>
       <c r="U29">
         <v>0.0553</v>
@@ -3691,7 +3691,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>5.210751064090218</v>
+        <v>5.024652811801281</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3699,22 +3699,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.09584976966138375</v>
+        <v>0.09584995965656715</v>
       </c>
       <c r="C30">
-        <v>1169.095130591907</v>
+        <v>1155.171196473189</v>
       </c>
       <c r="D30">
-        <v>1036.355130591907</v>
+        <v>1036.351196473189</v>
       </c>
       <c r="E30">
-        <v>-297.84</v>
+        <v>-283.92</v>
       </c>
       <c r="F30">
-        <v>389.76</v>
+        <v>403.6800000000001</v>
       </c>
       <c r="G30">
         <v>522.5</v>
@@ -3735,28 +3735,28 @@
         <v>108.3</v>
       </c>
       <c r="M30">
-        <v>21.553728</v>
+        <v>22.323504</v>
       </c>
       <c r="N30">
-        <v>86.746272</v>
+        <v>85.97649600000001</v>
       </c>
       <c r="O30">
-        <v>7.80716448</v>
+        <v>7.737884640000001</v>
       </c>
       <c r="P30">
-        <v>78.93910752000001</v>
+        <v>78.23861136000001</v>
       </c>
       <c r="Q30">
-        <v>214.13910752</v>
+        <v>213.43861136</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1135546245296997</v>
+        <v>0.1144454783895312</v>
       </c>
       <c r="T30">
-        <v>0.9859123434062429</v>
+        <v>0.9988753525392061</v>
       </c>
       <c r="U30">
         <v>0.0553</v>
@@ -3773,7 +3773,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>5.024652811801281</v>
+        <v>4.851388921739168</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3781,22 +3781,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.09584995965656713</v>
+        <v>0.09585014965175052</v>
       </c>
       <c r="C31">
-        <v>1155.17119647319</v>
+        <v>1141.247262384341</v>
       </c>
       <c r="D31">
-        <v>1036.35119647319</v>
+        <v>1036.347262384341</v>
       </c>
       <c r="E31">
-        <v>-283.9200000000001</v>
+        <v>-270.0000000000001</v>
       </c>
       <c r="F31">
-        <v>403.6799999999999</v>
+        <v>417.6</v>
       </c>
       <c r="G31">
         <v>522.5</v>
@@ -3817,28 +3817,28 @@
         <v>108.3</v>
       </c>
       <c r="M31">
-        <v>22.323504</v>
+        <v>23.09328</v>
       </c>
       <c r="N31">
-        <v>85.97649600000001</v>
+        <v>85.20672000000002</v>
       </c>
       <c r="O31">
-        <v>7.737884640000001</v>
+        <v>7.668604800000002</v>
       </c>
       <c r="P31">
-        <v>78.23861136000001</v>
+        <v>77.53811520000002</v>
       </c>
       <c r="Q31">
-        <v>213.43861136</v>
+        <v>212.7381152</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1144454783895312</v>
+        <v>0.1153617852167865</v>
       </c>
       <c r="T31">
-        <v>0.9988753525392059</v>
+        <v>1.012208733361682</v>
       </c>
       <c r="U31">
         <v>0.0553</v>
@@ -3855,7 +3855,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>4.851388921739169</v>
+        <v>4.689675957681196</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3863,22 +3863,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.09585014965175052</v>
+        <v>0.09585033964693389</v>
       </c>
       <c r="C32">
-        <v>1141.247262384341</v>
+        <v>1127.323328325361</v>
       </c>
       <c r="D32">
-        <v>1036.347262384341</v>
+        <v>1036.343328325361</v>
       </c>
       <c r="E32">
-        <v>-270.0000000000001</v>
+        <v>-256.08</v>
       </c>
       <c r="F32">
-        <v>417.6</v>
+        <v>431.52</v>
       </c>
       <c r="G32">
         <v>522.5</v>
@@ -3899,28 +3899,28 @@
         <v>108.3</v>
       </c>
       <c r="M32">
-        <v>23.09328</v>
+        <v>23.863056</v>
       </c>
       <c r="N32">
-        <v>85.20672000000002</v>
+        <v>84.43694400000001</v>
       </c>
       <c r="O32">
-        <v>7.668604800000002</v>
+        <v>7.599324960000001</v>
       </c>
       <c r="P32">
-        <v>77.53811520000002</v>
+        <v>76.83761904000001</v>
       </c>
       <c r="Q32">
-        <v>212.7381152</v>
+        <v>212.03761904</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1153617852167865</v>
+        <v>0.116304651662223</v>
       </c>
       <c r="T32">
-        <v>1.012208733361682</v>
+        <v>1.025928588990607</v>
       </c>
       <c r="U32">
         <v>0.0553</v>
@@ -3937,7 +3937,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>4.689675957681196</v>
+        <v>4.538396088078577</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3945,22 +3945,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.09585033964693389</v>
+        <v>0.09657852964211726</v>
       </c>
       <c r="C33">
-        <v>1127.323328325361</v>
+        <v>1098.541636807699</v>
       </c>
       <c r="D33">
-        <v>1036.343328325361</v>
+        <v>1021.481636807699</v>
       </c>
       <c r="E33">
-        <v>-256.08</v>
+        <v>-242.16</v>
       </c>
       <c r="F33">
-        <v>431.52</v>
+        <v>445.44</v>
       </c>
       <c r="G33">
         <v>522.5</v>
@@ -3981,45 +3981,45 @@
         <v>108.3</v>
       </c>
       <c r="M33">
-        <v>23.863056</v>
+        <v>25.746432</v>
       </c>
       <c r="N33">
-        <v>84.43694400000001</v>
+        <v>82.55356800000001</v>
       </c>
       <c r="O33">
-        <v>7.599324960000001</v>
+        <v>7.429821120000001</v>
       </c>
       <c r="P33">
-        <v>76.83761904000001</v>
+        <v>75.12374688000001</v>
       </c>
       <c r="Q33">
-        <v>212.03761904</v>
+        <v>210.32374688</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.116304651662223</v>
+        <v>0.1172752494737019</v>
       </c>
       <c r="T33">
-        <v>1.025928588990607</v>
+        <v>1.040051969785089</v>
       </c>
       <c r="U33">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V33">
         <v>0.09</v>
       </c>
       <c r="W33">
-        <v>0.05032300000000001</v>
+        <v>0.05259800000000001</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y33">
-        <v>4.538396088078577</v>
+        <v>4.206408095692638</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4027,22 +4027,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.09657852964211726</v>
+        <v>0.09660146963730064</v>
       </c>
       <c r="C34">
-        <v>1098.541636807699</v>
+        <v>1084.160374879736</v>
       </c>
       <c r="D34">
-        <v>1021.481636807699</v>
+        <v>1021.020374879736</v>
       </c>
       <c r="E34">
-        <v>-242.16</v>
+        <v>-228.24</v>
       </c>
       <c r="F34">
-        <v>445.44</v>
+        <v>459.36</v>
       </c>
       <c r="G34">
         <v>522.5</v>
@@ -4063,28 +4063,28 @@
         <v>108.3</v>
       </c>
       <c r="M34">
-        <v>25.746432</v>
+        <v>26.551008</v>
       </c>
       <c r="N34">
-        <v>82.55356800000001</v>
+        <v>81.74899200000002</v>
       </c>
       <c r="O34">
-        <v>7.429821120000001</v>
+        <v>7.357409280000001</v>
       </c>
       <c r="P34">
-        <v>75.12374688000001</v>
+        <v>74.39158272000002</v>
       </c>
       <c r="Q34">
-        <v>210.32374688</v>
+        <v>209.59158272</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1172752494737019</v>
+        <v>0.1182748203541801</v>
       </c>
       <c r="T34">
-        <v>1.040051969785089</v>
+        <v>1.054596944036122</v>
       </c>
       <c r="U34">
         <v>0.0578</v>
@@ -4101,7 +4101,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>4.206408095692638</v>
+        <v>4.078941183701952</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4109,22 +4109,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.09660146963730064</v>
+        <v>0.09770730963248403</v>
       </c>
       <c r="C35">
-        <v>1084.160374879736</v>
+        <v>1048.488425598732</v>
       </c>
       <c r="D35">
-        <v>1021.020374879736</v>
+        <v>999.2684255987322</v>
       </c>
       <c r="E35">
-        <v>-228.24</v>
+        <v>-214.32</v>
       </c>
       <c r="F35">
-        <v>459.36</v>
+        <v>473.28</v>
       </c>
       <c r="G35">
         <v>522.5</v>
@@ -4145,45 +4145,45 @@
         <v>108.3</v>
       </c>
       <c r="M35">
-        <v>26.551008</v>
+        <v>29.012064</v>
       </c>
       <c r="N35">
-        <v>81.74899200000002</v>
+        <v>79.287936</v>
       </c>
       <c r="O35">
-        <v>7.357409280000001</v>
+        <v>7.13591424</v>
       </c>
       <c r="P35">
-        <v>74.39158272000002</v>
+        <v>72.15202176</v>
       </c>
       <c r="Q35">
-        <v>209.59158272</v>
+        <v>207.35202176</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1182748203541801</v>
+        <v>0.1193046812613394</v>
       </c>
       <c r="T35">
-        <v>1.054596944036122</v>
+        <v>1.069582675082641</v>
       </c>
       <c r="U35">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V35">
         <v>0.09</v>
       </c>
       <c r="W35">
-        <v>0.05259800000000001</v>
+        <v>0.055783</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y35">
-        <v>4.078941183701952</v>
+        <v>3.732929859799013</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4191,22 +4191,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.09770730963248403</v>
+        <v>0.09776209962766738</v>
       </c>
       <c r="C36">
-        <v>1048.488425598732</v>
+        <v>1033.514774714381</v>
       </c>
       <c r="D36">
-        <v>999.2684255987322</v>
+        <v>998.2147747143812</v>
       </c>
       <c r="E36">
-        <v>-214.32</v>
+        <v>-200.4</v>
       </c>
       <c r="F36">
-        <v>473.28</v>
+        <v>487.2</v>
       </c>
       <c r="G36">
         <v>522.5</v>
@@ -4227,28 +4227,28 @@
         <v>108.3</v>
       </c>
       <c r="M36">
-        <v>29.012064</v>
+        <v>29.86536</v>
       </c>
       <c r="N36">
-        <v>79.287936</v>
+        <v>78.43464</v>
       </c>
       <c r="O36">
-        <v>7.13591424</v>
+        <v>7.0591176</v>
       </c>
       <c r="P36">
-        <v>72.15202176</v>
+        <v>71.37552240000001</v>
       </c>
       <c r="Q36">
-        <v>207.35202176</v>
+        <v>206.5755224</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1193046812613394</v>
+        <v>0.1203662301964114</v>
       </c>
       <c r="T36">
-        <v>1.069582675082641</v>
+        <v>1.085029505545976</v>
       </c>
       <c r="U36">
         <v>0.0613</v>
@@ -4265,7 +4265,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>3.732929859799013</v>
+        <v>3.626274720947613</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4273,22 +4273,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.09776209962766738</v>
+        <v>0.09781688962285076</v>
       </c>
       <c r="C37">
-        <v>1033.514774714381</v>
+        <v>1018.543343475506</v>
       </c>
       <c r="D37">
-        <v>998.2147747143812</v>
+        <v>997.1633434755061</v>
       </c>
       <c r="E37">
-        <v>-200.4</v>
+        <v>-186.48</v>
       </c>
       <c r="F37">
-        <v>487.2</v>
+        <v>501.1200000000001</v>
       </c>
       <c r="G37">
         <v>522.5</v>
@@ -4309,28 +4309,28 @@
         <v>108.3</v>
       </c>
       <c r="M37">
-        <v>29.86536</v>
+        <v>30.718656</v>
       </c>
       <c r="N37">
-        <v>78.43464</v>
+        <v>77.581344</v>
       </c>
       <c r="O37">
-        <v>7.0591176</v>
+        <v>6.98232096</v>
       </c>
       <c r="P37">
-        <v>71.37552240000001</v>
+        <v>70.59902304000001</v>
       </c>
       <c r="Q37">
-        <v>206.5755224</v>
+        <v>205.79902304</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1203662301964114</v>
+        <v>0.1214609525357043</v>
       </c>
       <c r="T37">
-        <v>1.085029505545976</v>
+        <v>1.10095904946129</v>
       </c>
       <c r="U37">
         <v>0.0613</v>
@@ -4347,7 +4347,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>3.626274720947613</v>
+        <v>3.525544867587957</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4355,22 +4355,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.09781688962285076</v>
+        <v>0.09881443961803414</v>
       </c>
       <c r="C38">
-        <v>1018.543343475506</v>
+        <v>985.8601480961352</v>
       </c>
       <c r="D38">
-        <v>997.1633434755061</v>
+        <v>978.4001480961352</v>
       </c>
       <c r="E38">
-        <v>-186.48</v>
+        <v>-172.5600000000001</v>
       </c>
       <c r="F38">
-        <v>501.12</v>
+        <v>515.04</v>
       </c>
       <c r="G38">
         <v>522.5</v>
@@ -4391,45 +4391,45 @@
         <v>108.3</v>
       </c>
       <c r="M38">
-        <v>30.718656</v>
+        <v>33.014064</v>
       </c>
       <c r="N38">
-        <v>77.58134400000002</v>
+        <v>75.28593600000002</v>
       </c>
       <c r="O38">
-        <v>6.982320960000001</v>
+        <v>6.775734240000002</v>
       </c>
       <c r="P38">
-        <v>70.59902304000002</v>
+        <v>68.51020176000002</v>
       </c>
       <c r="Q38">
-        <v>205.79902304</v>
+        <v>203.71020176</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1214609525357043</v>
+        <v>0.1225904279651336</v>
       </c>
       <c r="T38">
-        <v>1.10095904946129</v>
+        <v>1.11739429318344</v>
       </c>
       <c r="U38">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V38">
         <v>0.09</v>
       </c>
       <c r="W38">
-        <v>0.055783</v>
+        <v>0.05833100000000001</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y38">
-        <v>3.525544867587957</v>
+        <v>3.280420126404311</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4437,22 +4437,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.09881443961803414</v>
+        <v>0.09889470961321753</v>
       </c>
       <c r="C39">
-        <v>985.8601480961352</v>
+        <v>970.4609767107518</v>
       </c>
       <c r="D39">
-        <v>978.4001480961352</v>
+        <v>976.9209767107519</v>
       </c>
       <c r="E39">
-        <v>-172.5600000000001</v>
+        <v>-158.64</v>
       </c>
       <c r="F39">
-        <v>515.04</v>
+        <v>528.96</v>
       </c>
       <c r="G39">
         <v>522.5</v>
@@ -4473,28 +4473,28 @@
         <v>108.3</v>
       </c>
       <c r="M39">
-        <v>33.014064</v>
+        <v>33.906336</v>
       </c>
       <c r="N39">
-        <v>75.28593600000002</v>
+        <v>74.393664</v>
       </c>
       <c r="O39">
-        <v>6.775734240000002</v>
+        <v>6.69542976</v>
       </c>
       <c r="P39">
-        <v>68.51020176000002</v>
+        <v>67.69823424000001</v>
       </c>
       <c r="Q39">
-        <v>203.71020176</v>
+        <v>202.89823424</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1225904279651336</v>
+        <v>0.1237563380858347</v>
       </c>
       <c r="T39">
-        <v>1.11739429318344</v>
+        <v>1.134359706057917</v>
       </c>
       <c r="U39">
         <v>0.0641</v>
@@ -4511,7 +4511,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>3.280420126404311</v>
+        <v>3.194093280972618</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4519,22 +4519,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.09889470961321753</v>
+        <v>0.09897497960840089</v>
       </c>
       <c r="C40">
-        <v>970.4609767107518</v>
+        <v>955.0662710752709</v>
       </c>
       <c r="D40">
-        <v>976.9209767107519</v>
+        <v>975.4462710752709</v>
       </c>
       <c r="E40">
-        <v>-158.64</v>
+        <v>-144.72</v>
       </c>
       <c r="F40">
-        <v>528.96</v>
+        <v>542.88</v>
       </c>
       <c r="G40">
         <v>522.5</v>
@@ -4555,28 +4555,28 @@
         <v>108.3</v>
       </c>
       <c r="M40">
-        <v>33.906336</v>
+        <v>34.798608</v>
       </c>
       <c r="N40">
-        <v>74.393664</v>
+        <v>73.50139200000001</v>
       </c>
       <c r="O40">
-        <v>6.69542976</v>
+        <v>6.615125280000001</v>
       </c>
       <c r="P40">
-        <v>67.69823424000001</v>
+        <v>66.88626672000001</v>
       </c>
       <c r="Q40">
-        <v>202.89823424</v>
+        <v>202.08626672</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1237563380858347</v>
+        <v>0.1249604747678703</v>
       </c>
       <c r="T40">
-        <v>1.134359706057917</v>
+        <v>1.151881361977459</v>
       </c>
       <c r="U40">
         <v>0.0641</v>
@@ -4593,7 +4593,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>3.194093280972618</v>
+        <v>3.112193453255372</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4601,22 +4601,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.09897497960840089</v>
+        <v>0.09905524960358429</v>
       </c>
       <c r="C41">
-        <v>955.0662710752709</v>
+        <v>939.6760109964295</v>
       </c>
       <c r="D41">
-        <v>975.4462710752709</v>
+        <v>973.9760109964296</v>
       </c>
       <c r="E41">
-        <v>-144.72</v>
+        <v>-130.8</v>
       </c>
       <c r="F41">
-        <v>542.88</v>
+        <v>556.8000000000001</v>
       </c>
       <c r="G41">
         <v>522.5</v>
@@ -4637,28 +4637,28 @@
         <v>108.3</v>
       </c>
       <c r="M41">
-        <v>34.798608</v>
+        <v>35.69088000000001</v>
       </c>
       <c r="N41">
-        <v>73.50139200000001</v>
+        <v>72.60912</v>
       </c>
       <c r="O41">
-        <v>6.615125280000001</v>
+        <v>6.5348208</v>
       </c>
       <c r="P41">
-        <v>66.88626672000001</v>
+        <v>66.0742992</v>
       </c>
       <c r="Q41">
-        <v>202.08626672</v>
+        <v>201.2742992</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1249604747678703</v>
+        <v>0.1262047493393071</v>
       </c>
       <c r="T41">
-        <v>1.151881361977459</v>
+        <v>1.169987073094319</v>
       </c>
       <c r="U41">
         <v>0.0641</v>
@@ -4675,7 +4675,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>3.112193453255372</v>
+        <v>3.034388616923987</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4683,22 +4683,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.09905524960358429</v>
+        <v>0.1020456995987677</v>
       </c>
       <c r="C42">
-        <v>939.6760109964295</v>
+        <v>873.9720243419763</v>
       </c>
       <c r="D42">
-        <v>973.9760109964296</v>
+        <v>922.1920243419762</v>
       </c>
       <c r="E42">
-        <v>-130.8</v>
+        <v>-116.88</v>
       </c>
       <c r="F42">
-        <v>556.8000000000001</v>
+        <v>570.72</v>
       </c>
       <c r="G42">
         <v>522.5</v>
@@ -4719,45 +4719,45 @@
         <v>108.3</v>
       </c>
       <c r="M42">
-        <v>35.69088000000001</v>
+        <v>41.03476800000001</v>
       </c>
       <c r="N42">
-        <v>72.60912</v>
+        <v>67.265232</v>
       </c>
       <c r="O42">
-        <v>6.5348208</v>
+        <v>6.05387088</v>
       </c>
       <c r="P42">
-        <v>66.0742992</v>
+        <v>61.21136112</v>
       </c>
       <c r="Q42">
-        <v>201.2742992</v>
+        <v>196.41136112</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1262047493393071</v>
+        <v>0.1274912027097757</v>
       </c>
       <c r="T42">
-        <v>1.169987073094319</v>
+        <v>1.188706537130394</v>
       </c>
       <c r="U42">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V42">
         <v>0.09</v>
       </c>
       <c r="W42">
-        <v>0.05833100000000001</v>
+        <v>0.065429</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y42">
-        <v>3.034388616923987</v>
+        <v>2.639225351536044</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4765,22 +4765,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1020456995987677</v>
+        <v>0.102196949593951</v>
       </c>
       <c r="C43">
-        <v>873.9720243419763</v>
+        <v>857.5788136409699</v>
       </c>
       <c r="D43">
-        <v>922.1920243419762</v>
+        <v>919.7188136409701</v>
       </c>
       <c r="E43">
-        <v>-116.88</v>
+        <v>-102.9599999999999</v>
       </c>
       <c r="F43">
-        <v>570.72</v>
+        <v>584.6400000000001</v>
       </c>
       <c r="G43">
         <v>522.5</v>
@@ -4801,28 +4801,28 @@
         <v>108.3</v>
       </c>
       <c r="M43">
-        <v>41.03476800000001</v>
+        <v>42.03561600000001</v>
       </c>
       <c r="N43">
-        <v>67.265232</v>
+        <v>66.26438400000001</v>
       </c>
       <c r="O43">
-        <v>6.05387088</v>
+        <v>5.96379456</v>
       </c>
       <c r="P43">
-        <v>61.21136112</v>
+        <v>60.30058944000001</v>
       </c>
       <c r="Q43">
-        <v>196.41136112</v>
+        <v>195.50058944</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1274912027097757</v>
+        <v>0.1288220165412949</v>
       </c>
       <c r="T43">
-        <v>1.188706537130394</v>
+        <v>1.208071499926334</v>
       </c>
       <c r="U43">
         <v>0.07190000000000001</v>
@@ -4839,7 +4839,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>2.639225351536044</v>
+        <v>2.576386652689947</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4847,22 +4847,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.102196949593951</v>
+        <v>0.1023481995891344</v>
       </c>
       <c r="C44">
-        <v>857.5788136409698</v>
+        <v>841.1988331792757</v>
       </c>
       <c r="D44">
-        <v>919.7188136409698</v>
+        <v>917.2588331792756</v>
       </c>
       <c r="E44">
-        <v>-102.96</v>
+        <v>-89.04000000000008</v>
       </c>
       <c r="F44">
-        <v>584.64</v>
+        <v>598.5599999999999</v>
       </c>
       <c r="G44">
         <v>522.5</v>
@@ -4883,28 +4883,28 @@
         <v>108.3</v>
       </c>
       <c r="M44">
-        <v>42.035616</v>
+        <v>43.036464</v>
       </c>
       <c r="N44">
-        <v>66.26438400000001</v>
+        <v>65.26353600000002</v>
       </c>
       <c r="O44">
-        <v>5.96379456</v>
+        <v>5.873718240000001</v>
       </c>
       <c r="P44">
-        <v>60.30058944000001</v>
+        <v>59.38981776000001</v>
       </c>
       <c r="Q44">
-        <v>195.50058944</v>
+        <v>194.58981776</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1288220165412949</v>
+        <v>0.1301995255949726</v>
       </c>
       <c r="T44">
-        <v>1.208071499926334</v>
+        <v>1.228115935101079</v>
       </c>
       <c r="U44">
         <v>0.07190000000000001</v>
@@ -4921,7 +4921,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>2.576386652689948</v>
+        <v>2.51647068402274</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4929,22 +4929,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1023481995891344</v>
+        <v>0.1040610095843178</v>
       </c>
       <c r="C45">
-        <v>841.1988331792757</v>
+        <v>800.3124261628309</v>
       </c>
       <c r="D45">
-        <v>917.2588331792756</v>
+        <v>890.2924261628308</v>
       </c>
       <c r="E45">
-        <v>-89.04000000000008</v>
+        <v>-75.12</v>
       </c>
       <c r="F45">
-        <v>598.5599999999999</v>
+        <v>612.48</v>
       </c>
       <c r="G45">
         <v>522.5</v>
@@ -4965,45 +4965,45 @@
         <v>108.3</v>
       </c>
       <c r="M45">
-        <v>43.036464</v>
+        <v>46.42598400000001</v>
       </c>
       <c r="N45">
-        <v>65.26353600000002</v>
+        <v>61.874016</v>
       </c>
       <c r="O45">
-        <v>5.873718240000001</v>
+        <v>5.568661440000001</v>
       </c>
       <c r="P45">
-        <v>59.38981776000001</v>
+        <v>56.30535456</v>
       </c>
       <c r="Q45">
-        <v>194.58981776</v>
+        <v>191.50535456</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1301995255949726</v>
+        <v>0.1316262314005675</v>
       </c>
       <c r="T45">
-        <v>1.228115935101079</v>
+        <v>1.248876242960637</v>
       </c>
       <c r="U45">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V45">
         <v>0.09</v>
       </c>
       <c r="W45">
-        <v>0.065429</v>
+        <v>0.06897800000000001</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y45">
-        <v>2.51647068402274</v>
+        <v>2.332745386721367</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5011,22 +5011,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1040610095843178</v>
+        <v>0.1042477495795012</v>
       </c>
       <c r="C46">
-        <v>800.3124261628309</v>
+        <v>783.5479504632609</v>
       </c>
       <c r="D46">
-        <v>890.2924261628308</v>
+        <v>887.4479504632609</v>
       </c>
       <c r="E46">
-        <v>-75.12</v>
+        <v>-61.20000000000005</v>
       </c>
       <c r="F46">
-        <v>612.48</v>
+        <v>626.4</v>
       </c>
       <c r="G46">
         <v>522.5</v>
@@ -5047,28 +5047,28 @@
         <v>108.3</v>
       </c>
       <c r="M46">
-        <v>46.42598400000001</v>
+        <v>47.48112</v>
       </c>
       <c r="N46">
-        <v>61.874016</v>
+        <v>60.81888000000001</v>
       </c>
       <c r="O46">
-        <v>5.568661440000001</v>
+        <v>5.4736992</v>
       </c>
       <c r="P46">
-        <v>56.30535456</v>
+        <v>55.34518080000001</v>
       </c>
       <c r="Q46">
-        <v>191.50535456</v>
+        <v>190.5451808</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1316262314005675</v>
+        <v>0.1331048174172748</v>
       </c>
       <c r="T46">
-        <v>1.248876242960637</v>
+        <v>1.270391471105996</v>
       </c>
       <c r="U46">
         <v>0.07580000000000001</v>
@@ -5085,7 +5085,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>2.332745386721367</v>
+        <v>2.280906600349781</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5093,22 +5093,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1042477495795012</v>
+        <v>0.1044344895746845</v>
       </c>
       <c r="C47">
-        <v>783.5479504632609</v>
+        <v>766.8015930207879</v>
       </c>
       <c r="D47">
-        <v>887.4479504632609</v>
+        <v>884.6215930207879</v>
       </c>
       <c r="E47">
-        <v>-61.20000000000005</v>
+        <v>-47.27999999999997</v>
       </c>
       <c r="F47">
-        <v>626.4</v>
+        <v>640.3200000000001</v>
       </c>
       <c r="G47">
         <v>522.5</v>
@@ -5129,28 +5129,28 @@
         <v>108.3</v>
       </c>
       <c r="M47">
-        <v>47.48112</v>
+        <v>48.53625600000001</v>
       </c>
       <c r="N47">
-        <v>60.81888000000001</v>
+        <v>59.763744</v>
       </c>
       <c r="O47">
-        <v>5.4736992</v>
+        <v>5.37873696</v>
       </c>
       <c r="P47">
-        <v>55.34518080000001</v>
+        <v>54.38500704</v>
       </c>
       <c r="Q47">
-        <v>190.5451808</v>
+        <v>189.58500704</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1331048174172748</v>
+        <v>0.1346381658790454</v>
       </c>
       <c r="T47">
-        <v>1.270391471105996</v>
+        <v>1.292703559553036</v>
       </c>
       <c r="U47">
         <v>0.07580000000000001</v>
@@ -5167,7 +5167,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>2.280906600349781</v>
+        <v>2.23132167425522</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5175,22 +5175,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1044344895746845</v>
+        <v>0.1046212295698679</v>
       </c>
       <c r="C48">
-        <v>766.8015930207879</v>
+        <v>750.0731812751003</v>
       </c>
       <c r="D48">
-        <v>884.6215930207879</v>
+        <v>881.8131812751003</v>
       </c>
       <c r="E48">
-        <v>-47.27999999999997</v>
+        <v>-33.36000000000001</v>
       </c>
       <c r="F48">
-        <v>640.3200000000001</v>
+        <v>654.24</v>
       </c>
       <c r="G48">
         <v>522.5</v>
@@ -5211,28 +5211,28 @@
         <v>108.3</v>
       </c>
       <c r="M48">
-        <v>48.53625600000001</v>
+        <v>49.59139200000001</v>
       </c>
       <c r="N48">
-        <v>59.763744</v>
+        <v>58.70860800000001</v>
       </c>
       <c r="O48">
-        <v>5.37873696</v>
+        <v>5.28377472</v>
       </c>
       <c r="P48">
-        <v>54.38500704</v>
+        <v>53.42483328</v>
       </c>
       <c r="Q48">
-        <v>189.58500704</v>
+        <v>188.62483328</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1346381658790454</v>
+        <v>0.1362293765469206</v>
       </c>
       <c r="T48">
-        <v>1.292703559553036</v>
+        <v>1.31585761360185</v>
       </c>
       <c r="U48">
         <v>0.07580000000000001</v>
@@ -5249,7 +5249,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>2.23132167425522</v>
+        <v>2.183846745015748</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5257,22 +5257,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1046212295698679</v>
+        <v>0.1048079695650513</v>
       </c>
       <c r="C49">
-        <v>750.0731812751003</v>
+        <v>733.3625448502626</v>
       </c>
       <c r="D49">
-        <v>881.8131812751003</v>
+        <v>879.0225448502626</v>
       </c>
       <c r="E49">
-        <v>-33.36000000000001</v>
+        <v>-19.43999999999994</v>
       </c>
       <c r="F49">
-        <v>654.24</v>
+        <v>668.1600000000001</v>
       </c>
       <c r="G49">
         <v>522.5</v>
@@ -5293,28 +5293,28 @@
         <v>108.3</v>
       </c>
       <c r="M49">
-        <v>49.59139200000001</v>
+        <v>50.64652800000001</v>
       </c>
       <c r="N49">
-        <v>58.70860800000001</v>
+        <v>57.653472</v>
       </c>
       <c r="O49">
-        <v>5.28377472</v>
+        <v>5.18881248</v>
       </c>
       <c r="P49">
-        <v>53.42483328</v>
+        <v>52.46465952</v>
       </c>
       <c r="Q49">
-        <v>188.62483328</v>
+        <v>187.66465952</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1362293765469206</v>
+        <v>0.1378817876250986</v>
       </c>
       <c r="T49">
-        <v>1.31585761360185</v>
+        <v>1.339902208191004</v>
       </c>
       <c r="U49">
         <v>0.07580000000000001</v>
@@ -5331,7 +5331,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>2.183846745015748</v>
+        <v>2.13834993782792</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5339,22 +5339,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1048079695650513</v>
+        <v>0.1049947095602347</v>
       </c>
       <c r="C50">
-        <v>733.3625448502627</v>
+        <v>716.6695155202616</v>
       </c>
       <c r="D50">
-        <v>879.0225448502626</v>
+        <v>876.2495155202616</v>
       </c>
       <c r="E50">
-        <v>-19.44000000000005</v>
+        <v>-5.519999999999982</v>
       </c>
       <c r="F50">
-        <v>668.16</v>
+        <v>682.08</v>
       </c>
       <c r="G50">
         <v>522.5</v>
@@ -5375,28 +5375,28 @@
         <v>108.3</v>
       </c>
       <c r="M50">
-        <v>50.646528</v>
+        <v>51.70166400000001</v>
       </c>
       <c r="N50">
-        <v>57.65347200000001</v>
+        <v>56.598336</v>
       </c>
       <c r="O50">
-        <v>5.18881248</v>
+        <v>5.09385024</v>
       </c>
       <c r="P50">
-        <v>52.46465952</v>
+        <v>51.50448576</v>
       </c>
       <c r="Q50">
-        <v>187.66465952</v>
+        <v>186.70448576</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1378817876250986</v>
+        <v>0.139598999137715</v>
       </c>
       <c r="T50">
-        <v>1.339902208191004</v>
+        <v>1.364889728058164</v>
       </c>
       <c r="U50">
         <v>0.07580000000000001</v>
@@ -5413,7 +5413,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>2.13834993782792</v>
+        <v>2.094710143178371</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5421,22 +5421,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1049947095602347</v>
+        <v>0.105181449555418</v>
       </c>
       <c r="C51">
-        <v>716.6695155202616</v>
+        <v>699.9939271752014</v>
       </c>
       <c r="D51">
-        <v>876.2495155202616</v>
+        <v>873.4939271752015</v>
       </c>
       <c r="E51">
-        <v>-5.519999999999982</v>
+        <v>8.399999999999977</v>
       </c>
       <c r="F51">
-        <v>682.08</v>
+        <v>696</v>
       </c>
       <c r="G51">
         <v>522.5</v>
@@ -5457,28 +5457,28 @@
         <v>108.3</v>
       </c>
       <c r="M51">
-        <v>51.70166400000001</v>
+        <v>52.75680000000001</v>
       </c>
       <c r="N51">
-        <v>56.598336</v>
+        <v>55.54320000000001</v>
       </c>
       <c r="O51">
-        <v>5.09385024</v>
+        <v>4.998888</v>
       </c>
       <c r="P51">
-        <v>51.50448576</v>
+        <v>50.54431200000001</v>
       </c>
       <c r="Q51">
-        <v>186.70448576</v>
+        <v>185.744312</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.139598999137715</v>
+        <v>0.1413848991108361</v>
       </c>
       <c r="T51">
-        <v>1.364889728058164</v>
+        <v>1.39087674872001</v>
       </c>
       <c r="U51">
         <v>0.07580000000000001</v>
@@ -5495,7 +5495,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>2.094710143178371</v>
+        <v>2.052815940314803</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5503,22 +5503,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.105181449555418</v>
+        <v>0.1053681895506014</v>
       </c>
       <c r="C52">
-        <v>699.9939271752014</v>
+        <v>683.3356157881341</v>
       </c>
       <c r="D52">
-        <v>873.4939271752015</v>
+        <v>870.7556157881339</v>
       </c>
       <c r="E52">
-        <v>8.399999999999977</v>
+        <v>22.31999999999994</v>
       </c>
       <c r="F52">
-        <v>696</v>
+        <v>709.92</v>
       </c>
       <c r="G52">
         <v>522.5</v>
@@ -5539,28 +5539,28 @@
         <v>108.3</v>
       </c>
       <c r="M52">
-        <v>52.75680000000001</v>
+        <v>53.811936</v>
       </c>
       <c r="N52">
-        <v>55.54320000000001</v>
+        <v>54.48806400000001</v>
       </c>
       <c r="O52">
-        <v>4.998888</v>
+        <v>4.903925760000001</v>
       </c>
       <c r="P52">
-        <v>50.54431200000001</v>
+        <v>49.58413824000001</v>
       </c>
       <c r="Q52">
-        <v>185.744312</v>
+        <v>184.78413824</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1413848991108361</v>
+        <v>0.143243692960411</v>
       </c>
       <c r="T52">
-        <v>1.39087674872001</v>
+        <v>1.417924464102747</v>
       </c>
       <c r="U52">
         <v>0.07580000000000001</v>
@@ -5577,7 +5577,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>2.052815940314803</v>
+        <v>2.012564647367454</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5585,22 +5585,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1053681895506014</v>
+        <v>0.1122743695457848</v>
       </c>
       <c r="C53">
-        <v>683.3356157881341</v>
+        <v>578.9507485687815</v>
       </c>
       <c r="D53">
-        <v>870.7556157881339</v>
+        <v>780.2907485687816</v>
       </c>
       <c r="E53">
-        <v>22.31999999999994</v>
+        <v>36.24000000000001</v>
       </c>
       <c r="F53">
-        <v>709.92</v>
+        <v>723.84</v>
       </c>
       <c r="G53">
         <v>522.5</v>
@@ -5621,45 +5621,45 @@
         <v>108.3</v>
       </c>
       <c r="M53">
-        <v>53.811936</v>
+        <v>65.1456</v>
       </c>
       <c r="N53">
-        <v>54.48806400000001</v>
+        <v>43.15440000000001</v>
       </c>
       <c r="O53">
-        <v>4.903925760000001</v>
+        <v>3.883896000000001</v>
       </c>
       <c r="P53">
-        <v>49.58413824000001</v>
+        <v>39.27050400000001</v>
       </c>
       <c r="Q53">
-        <v>184.78413824</v>
+        <v>174.470504</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.143243692960411</v>
+        <v>0.1451799365537183</v>
       </c>
       <c r="T53">
-        <v>1.417924464102747</v>
+        <v>1.446099167626432</v>
       </c>
       <c r="U53">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V53">
         <v>0.09</v>
       </c>
       <c r="W53">
-        <v>0.06897800000000001</v>
+        <v>0.0819</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y53">
-        <v>2.012564647367454</v>
+        <v>1.662430002947244</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5667,22 +5667,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1122743695457848</v>
+        <v>0.1125903295409681</v>
       </c>
       <c r="C54">
-        <v>578.9507485687815</v>
+        <v>561.3394857339697</v>
       </c>
       <c r="D54">
-        <v>780.2907485687816</v>
+        <v>776.5994857339696</v>
       </c>
       <c r="E54">
-        <v>36.24000000000001</v>
+        <v>50.15999999999997</v>
       </c>
       <c r="F54">
-        <v>723.84</v>
+        <v>737.76</v>
       </c>
       <c r="G54">
         <v>522.5</v>
@@ -5703,28 +5703,28 @@
         <v>108.3</v>
       </c>
       <c r="M54">
-        <v>65.1456</v>
+        <v>66.3984</v>
       </c>
       <c r="N54">
-        <v>43.15440000000001</v>
+        <v>41.90160000000002</v>
       </c>
       <c r="O54">
-        <v>3.883896000000001</v>
+        <v>3.771144000000001</v>
       </c>
       <c r="P54">
-        <v>39.27050400000001</v>
+        <v>38.13045600000002</v>
       </c>
       <c r="Q54">
-        <v>174.470504</v>
+        <v>173.330456</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1451799365537183</v>
+        <v>0.1471985734914216</v>
       </c>
       <c r="T54">
-        <v>1.446099167626432</v>
+        <v>1.475472794704316</v>
       </c>
       <c r="U54">
         <v>0.09</v>
@@ -5741,7 +5741,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>1.662430002947244</v>
+        <v>1.631063399118051</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5749,22 +5749,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1125903295409681</v>
+        <v>0.1129062895361515</v>
       </c>
       <c r="C55">
-        <v>561.3394857339697</v>
+        <v>543.7629824245482</v>
       </c>
       <c r="D55">
-        <v>776.5994857339696</v>
+        <v>772.9429824245483</v>
       </c>
       <c r="E55">
-        <v>50.15999999999997</v>
+        <v>64.08000000000004</v>
       </c>
       <c r="F55">
-        <v>737.76</v>
+        <v>751.6800000000001</v>
       </c>
       <c r="G55">
         <v>522.5</v>
@@ -5785,28 +5785,28 @@
         <v>108.3</v>
       </c>
       <c r="M55">
-        <v>66.3984</v>
+        <v>67.6512</v>
       </c>
       <c r="N55">
-        <v>41.90160000000002</v>
+        <v>40.64880000000001</v>
       </c>
       <c r="O55">
-        <v>3.771144000000001</v>
+        <v>3.658392000000001</v>
       </c>
       <c r="P55">
-        <v>38.13045600000002</v>
+        <v>36.99040800000001</v>
       </c>
       <c r="Q55">
-        <v>173.330456</v>
+        <v>172.190408</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1471985734914216</v>
+        <v>0.1493049772525033</v>
       </c>
       <c r="T55">
-        <v>1.475472794704316</v>
+        <v>1.506123536002979</v>
       </c>
       <c r="U55">
         <v>0.09</v>
@@ -5823,7 +5823,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>1.631063399118051</v>
+        <v>1.600858521356606</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5831,22 +5831,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1129062895361515</v>
+        <v>0.1132222495313349</v>
       </c>
       <c r="C56">
-        <v>543.7629824245482</v>
+        <v>526.2207499612072</v>
       </c>
       <c r="D56">
-        <v>772.9429824245483</v>
+        <v>769.3207499612071</v>
       </c>
       <c r="E56">
-        <v>64.08000000000004</v>
+        <v>78</v>
       </c>
       <c r="F56">
-        <v>751.6800000000001</v>
+        <v>765.6</v>
       </c>
       <c r="G56">
         <v>522.5</v>
@@ -5867,28 +5867,28 @@
         <v>108.3</v>
       </c>
       <c r="M56">
-        <v>67.6512</v>
+        <v>68.904</v>
       </c>
       <c r="N56">
-        <v>40.64880000000001</v>
+        <v>39.39600000000002</v>
       </c>
       <c r="O56">
-        <v>3.658392000000001</v>
+        <v>3.545640000000001</v>
       </c>
       <c r="P56">
-        <v>36.99040800000001</v>
+        <v>35.85036000000002</v>
       </c>
       <c r="Q56">
-        <v>172.190408</v>
+        <v>171.05036</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1493049772525033</v>
+        <v>0.151504998958522</v>
       </c>
       <c r="T56">
-        <v>1.506123536002979</v>
+        <v>1.53813653247047</v>
       </c>
       <c r="U56">
         <v>0.09</v>
@@ -5905,7 +5905,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>1.600858521356606</v>
+        <v>1.571752002786486</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5913,22 +5913,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1132222495313349</v>
+        <v>0.1135382095265183</v>
       </c>
       <c r="C57">
-        <v>526.2207499612072</v>
+        <v>508.7123087822732</v>
       </c>
       <c r="D57">
-        <v>769.3207499612071</v>
+        <v>765.7323087822732</v>
       </c>
       <c r="E57">
-        <v>78</v>
+        <v>91.92000000000007</v>
       </c>
       <c r="F57">
-        <v>765.6</v>
+        <v>779.5200000000001</v>
       </c>
       <c r="G57">
         <v>522.5</v>
@@ -5949,28 +5949,28 @@
         <v>108.3</v>
       </c>
       <c r="M57">
-        <v>68.904</v>
+        <v>70.1568</v>
       </c>
       <c r="N57">
-        <v>39.39600000000002</v>
+        <v>38.14320000000001</v>
       </c>
       <c r="O57">
-        <v>3.545640000000001</v>
+        <v>3.432888000000001</v>
       </c>
       <c r="P57">
-        <v>35.85036000000002</v>
+        <v>34.71031200000001</v>
       </c>
       <c r="Q57">
-        <v>171.05036</v>
+        <v>169.910312</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.151504998958522</v>
+        <v>0.1538050216511779</v>
       </c>
       <c r="T57">
-        <v>1.53813653247047</v>
+        <v>1.571604665141029</v>
       </c>
       <c r="U57">
         <v>0.09</v>
@@ -5987,7 +5987,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>1.571752002786486</v>
+        <v>1.543685002736727</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -5995,22 +5995,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1135382095265183</v>
+        <v>0.1138541695217016</v>
       </c>
       <c r="C58">
-        <v>508.7123087822732</v>
+        <v>491.2371882320556</v>
       </c>
       <c r="D58">
-        <v>765.7323087822732</v>
+        <v>762.1771882320556</v>
       </c>
       <c r="E58">
-        <v>91.92000000000007</v>
+        <v>105.84</v>
       </c>
       <c r="F58">
-        <v>779.5200000000001</v>
+        <v>793.4400000000001</v>
       </c>
       <c r="G58">
         <v>522.5</v>
@@ -6031,28 +6031,28 @@
         <v>108.3</v>
       </c>
       <c r="M58">
-        <v>70.1568</v>
+        <v>71.4096</v>
       </c>
       <c r="N58">
-        <v>38.14320000000001</v>
+        <v>36.89040000000001</v>
       </c>
       <c r="O58">
-        <v>3.432888000000001</v>
+        <v>3.320136000000001</v>
       </c>
       <c r="P58">
-        <v>34.71031200000001</v>
+        <v>33.57026400000002</v>
       </c>
       <c r="Q58">
-        <v>169.910312</v>
+        <v>168.770264</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1538050216511779</v>
+        <v>0.1562120221434922</v>
       </c>
       <c r="T58">
-        <v>1.571604665141029</v>
+        <v>1.606629455145103</v>
       </c>
       <c r="U58">
         <v>0.09</v>
@@ -6069,7 +6069,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>1.543685002736727</v>
+        <v>1.516602809706258</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6077,22 +6077,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1138541695217016</v>
+        <v>0.1450352441947387</v>
       </c>
       <c r="C59">
-        <v>491.2371882320556</v>
+        <v>237.830662923448</v>
       </c>
       <c r="D59">
-        <v>762.1771882320556</v>
+        <v>522.6906629234481</v>
       </c>
       <c r="E59">
-        <v>105.84</v>
+        <v>119.7600000000001</v>
       </c>
       <c r="F59">
-        <v>793.4400000000001</v>
+        <v>807.3600000000001</v>
       </c>
       <c r="G59">
         <v>522.5</v>
@@ -6113,45 +6113,45 @@
         <v>108.3</v>
       </c>
       <c r="M59">
-        <v>71.4096</v>
+        <v>118.520448</v>
       </c>
       <c r="N59">
-        <v>36.89040000000001</v>
+        <v>-10.22044800000002</v>
       </c>
       <c r="O59">
-        <v>3.320136000000001</v>
+        <v>-0.9198403200000017</v>
       </c>
       <c r="P59">
-        <v>33.57026400000002</v>
+        <v>-9.300607680000017</v>
       </c>
       <c r="Q59">
-        <v>168.770264</v>
+        <v>125.89939232</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1562120221434922</v>
+        <v>0.1592699984932202</v>
       </c>
       <c r="T59">
-        <v>1.606629455145103</v>
+        <v>1.651126737064503</v>
       </c>
       <c r="U59">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V59">
-        <v>0.09</v>
+        <v>0.08223897364950897</v>
       </c>
       <c r="W59">
-        <v>0.0819</v>
+        <v>0.1347273186682521</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y59">
-        <v>1.516602809706258</v>
+        <v>0.9137663738834331</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6159,22 +6159,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1450352441947386</v>
+        <v>0.1460452441947387</v>
       </c>
       <c r="C60">
-        <v>237.8306629234485</v>
+        <v>218.6444024260711</v>
       </c>
       <c r="D60">
-        <v>522.6906629234484</v>
+        <v>517.424402426071</v>
       </c>
       <c r="E60">
-        <v>119.7599999999999</v>
+        <v>133.6799999999999</v>
       </c>
       <c r="F60">
-        <v>807.3599999999999</v>
+        <v>821.28</v>
       </c>
       <c r="G60">
         <v>522.5</v>
@@ -6195,37 +6195,37 @@
         <v>108.3</v>
       </c>
       <c r="M60">
-        <v>118.520448</v>
+        <v>120.563904</v>
       </c>
       <c r="N60">
-        <v>-10.22044799999999</v>
+        <v>-12.263904</v>
       </c>
       <c r="O60">
-        <v>-0.9198403199999992</v>
+        <v>-1.10375136</v>
       </c>
       <c r="P60">
-        <v>-9.300607679999992</v>
+        <v>-11.16015264</v>
       </c>
       <c r="Q60">
-        <v>125.89939232</v>
+        <v>124.03984736</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1592699984932201</v>
+        <v>0.1620375594320791</v>
       </c>
       <c r="T60">
-        <v>1.651126737064502</v>
+        <v>1.691398120895344</v>
       </c>
       <c r="U60">
         <v>0.1468</v>
       </c>
       <c r="V60">
-        <v>0.082238973649509</v>
+        <v>0.08084509274019527</v>
       </c>
       <c r="W60">
-        <v>0.1347273186682521</v>
+        <v>0.1349319403857394</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6233,7 +6233,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.9137663738834333</v>
+        <v>0.898278808224392</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6241,22 +6241,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1460452441947387</v>
+        <v>0.1470552441947387</v>
       </c>
       <c r="C61">
-        <v>218.6444024260711</v>
+        <v>199.5632016348781</v>
       </c>
       <c r="D61">
-        <v>517.424402426071</v>
+        <v>512.263201634878</v>
       </c>
       <c r="E61">
-        <v>133.6799999999999</v>
+        <v>147.5999999999999</v>
       </c>
       <c r="F61">
-        <v>821.28</v>
+        <v>835.1999999999999</v>
       </c>
       <c r="G61">
         <v>522.5</v>
@@ -6277,37 +6277,37 @@
         <v>108.3</v>
       </c>
       <c r="M61">
-        <v>120.563904</v>
+        <v>122.60736</v>
       </c>
       <c r="N61">
-        <v>-12.263904</v>
+        <v>-14.30735999999999</v>
       </c>
       <c r="O61">
-        <v>-1.10375136</v>
+        <v>-1.287662399999999</v>
       </c>
       <c r="P61">
-        <v>-11.16015264</v>
+        <v>-13.01969759999999</v>
       </c>
       <c r="Q61">
-        <v>124.03984736</v>
+        <v>122.1803024</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1620375594320791</v>
+        <v>0.1649434984178811</v>
       </c>
       <c r="T61">
-        <v>1.691398120895344</v>
+        <v>1.733683073917727</v>
       </c>
       <c r="U61">
         <v>0.1468</v>
       </c>
       <c r="V61">
-        <v>0.08084509274019527</v>
+        <v>0.07949767452785869</v>
       </c>
       <c r="W61">
-        <v>0.1349319403857394</v>
+        <v>0.1351297413793104</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6315,7 +6315,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.898278808224392</v>
+        <v>0.8833074947539855</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6323,22 +6323,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1470552441947387</v>
+        <v>0.1480652441947387</v>
       </c>
       <c r="C62">
-        <v>199.5632016348781</v>
+        <v>180.5839477532171</v>
       </c>
       <c r="D62">
-        <v>512.263201634878</v>
+        <v>507.2039477532171</v>
       </c>
       <c r="E62">
-        <v>147.5999999999999</v>
+        <v>161.52</v>
       </c>
       <c r="F62">
-        <v>835.1999999999999</v>
+        <v>849.12</v>
       </c>
       <c r="G62">
         <v>522.5</v>
@@ -6359,37 +6359,37 @@
         <v>108.3</v>
       </c>
       <c r="M62">
-        <v>122.60736</v>
+        <v>124.650816</v>
       </c>
       <c r="N62">
-        <v>-14.30735999999999</v>
+        <v>-16.35081599999999</v>
       </c>
       <c r="O62">
-        <v>-1.287662399999999</v>
+        <v>-1.47157344</v>
       </c>
       <c r="P62">
-        <v>-13.01969759999999</v>
+        <v>-14.87924255999999</v>
       </c>
       <c r="Q62">
-        <v>122.1803024</v>
+        <v>120.32075744</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1649434984178811</v>
+        <v>0.1679984599157755</v>
       </c>
       <c r="T62">
-        <v>1.733683073917727</v>
+        <v>1.778136486069464</v>
       </c>
       <c r="U62">
         <v>0.1468</v>
       </c>
       <c r="V62">
-        <v>0.07949767452785869</v>
+        <v>0.07819443396182821</v>
       </c>
       <c r="W62">
-        <v>0.1351297413793104</v>
+        <v>0.1353210570944036</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6397,7 +6397,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.8833074947539855</v>
+        <v>0.8688270440203135</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6405,22 +6405,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1480652441947387</v>
+        <v>0.1490752441947387</v>
       </c>
       <c r="C63">
-        <v>180.5839477532171</v>
+        <v>161.7036497531969</v>
       </c>
       <c r="D63">
-        <v>507.2039477532171</v>
+        <v>502.243649753197</v>
       </c>
       <c r="E63">
-        <v>161.52</v>
+        <v>175.4399999999999</v>
       </c>
       <c r="F63">
-        <v>849.12</v>
+        <v>863.04</v>
       </c>
       <c r="G63">
         <v>522.5</v>
@@ -6441,37 +6441,37 @@
         <v>108.3</v>
       </c>
       <c r="M63">
-        <v>124.650816</v>
+        <v>126.694272</v>
       </c>
       <c r="N63">
-        <v>-16.35081599999999</v>
+        <v>-18.394272</v>
       </c>
       <c r="O63">
-        <v>-1.47157344</v>
+        <v>-1.65548448</v>
       </c>
       <c r="P63">
-        <v>-14.87924255999999</v>
+        <v>-16.73878752</v>
       </c>
       <c r="Q63">
-        <v>120.32075744</v>
+        <v>118.46121248</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1679984599157755</v>
+        <v>0.1712142088609275</v>
       </c>
       <c r="T63">
-        <v>1.778136486069464</v>
+        <v>1.824929551492345</v>
       </c>
       <c r="U63">
         <v>0.1468</v>
       </c>
       <c r="V63">
-        <v>0.07819443396182821</v>
+        <v>0.07693323341405679</v>
       </c>
       <c r="W63">
-        <v>0.1353210570944036</v>
+        <v>0.1355062013348165</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6479,7 +6479,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.8688270440203135</v>
+        <v>0.854813704600631</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6487,22 +6487,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1490752441947387</v>
+        <v>0.1500852441947387</v>
       </c>
       <c r="C64">
-        <v>161.7036497531969</v>
+        <v>142.9194324790495</v>
       </c>
       <c r="D64">
-        <v>502.243649753197</v>
+        <v>497.3794324790496</v>
       </c>
       <c r="E64">
-        <v>175.4399999999999</v>
+        <v>189.36</v>
       </c>
       <c r="F64">
-        <v>863.04</v>
+        <v>876.96</v>
       </c>
       <c r="G64">
         <v>522.5</v>
@@ -6523,37 +6523,37 @@
         <v>108.3</v>
       </c>
       <c r="M64">
-        <v>126.694272</v>
+        <v>128.737728</v>
       </c>
       <c r="N64">
-        <v>-18.394272</v>
+        <v>-20.43772799999999</v>
       </c>
       <c r="O64">
-        <v>-1.65548448</v>
+        <v>-1.839395519999999</v>
       </c>
       <c r="P64">
-        <v>-16.73878752</v>
+        <v>-18.59833247999999</v>
       </c>
       <c r="Q64">
-        <v>118.46121248</v>
+        <v>116.60166752</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1712142088609275</v>
+        <v>0.174603782073385</v>
       </c>
       <c r="T64">
-        <v>1.824929551492345</v>
+        <v>1.874251971802948</v>
       </c>
       <c r="U64">
         <v>0.1468</v>
       </c>
       <c r="V64">
-        <v>0.07693323341405679</v>
+        <v>0.07571207097891304</v>
       </c>
       <c r="W64">
-        <v>0.1355062013348165</v>
+        <v>0.1356854679802956</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6561,7 +6561,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.854813704600631</v>
+        <v>0.8412452330990338</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6569,22 +6569,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1500852441947387</v>
+        <v>0.1510952441947387</v>
       </c>
       <c r="C65">
-        <v>142.9194324790495</v>
+        <v>124.228531089859</v>
       </c>
       <c r="D65">
-        <v>497.3794324790496</v>
+        <v>492.608531089859</v>
       </c>
       <c r="E65">
-        <v>189.36</v>
+        <v>203.28</v>
       </c>
       <c r="F65">
-        <v>876.96</v>
+        <v>890.88</v>
       </c>
       <c r="G65">
         <v>522.5</v>
@@ -6605,37 +6605,37 @@
         <v>108.3</v>
       </c>
       <c r="M65">
-        <v>128.737728</v>
+        <v>130.781184</v>
       </c>
       <c r="N65">
-        <v>-20.43772799999999</v>
+        <v>-22.48118400000001</v>
       </c>
       <c r="O65">
-        <v>-1.839395519999999</v>
+        <v>-2.023306560000001</v>
       </c>
       <c r="P65">
-        <v>-18.59833247999999</v>
+        <v>-20.45787744000001</v>
       </c>
       <c r="Q65">
-        <v>116.60166752</v>
+        <v>114.74212256</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.174603782073385</v>
+        <v>0.1781816649087568</v>
       </c>
       <c r="T65">
-        <v>1.874251971802948</v>
+        <v>1.926314526575253</v>
       </c>
       <c r="U65">
         <v>0.1468</v>
       </c>
       <c r="V65">
-        <v>0.07571207097891304</v>
+        <v>0.07452906986986751</v>
       </c>
       <c r="W65">
-        <v>0.1356854679802956</v>
+        <v>0.1358591325431035</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6643,7 +6643,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.8412452330990338</v>
+        <v>0.8281007763318613</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6651,22 +6651,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1510952441947387</v>
+        <v>0.1521052441947387</v>
       </c>
       <c r="C66">
-        <v>124.228531089859</v>
+        <v>105.6282858190863</v>
       </c>
       <c r="D66">
-        <v>492.608531089859</v>
+        <v>487.9282858190863</v>
       </c>
       <c r="E66">
-        <v>203.28</v>
+        <v>217.2</v>
       </c>
       <c r="F66">
-        <v>890.88</v>
+        <v>904.8000000000001</v>
       </c>
       <c r="G66">
         <v>522.5</v>
@@ -6687,37 +6687,37 @@
         <v>108.3</v>
       </c>
       <c r="M66">
-        <v>130.781184</v>
+        <v>132.82464</v>
       </c>
       <c r="N66">
-        <v>-22.48118400000001</v>
+        <v>-24.52464000000001</v>
       </c>
       <c r="O66">
-        <v>-2.023306560000001</v>
+        <v>-2.2072176</v>
       </c>
       <c r="P66">
-        <v>-20.45787744000001</v>
+        <v>-22.31742240000001</v>
       </c>
       <c r="Q66">
-        <v>114.74212256</v>
+        <v>112.8825776</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1781816649087568</v>
+        <v>0.1819639981918642</v>
       </c>
       <c r="T66">
-        <v>1.926314526575253</v>
+        <v>1.981352084477403</v>
       </c>
       <c r="U66">
         <v>0.1468</v>
       </c>
       <c r="V66">
-        <v>0.07452906986986751</v>
+        <v>0.07338246879494648</v>
       </c>
       <c r="W66">
-        <v>0.1358591325431035</v>
+        <v>0.1360274535809019</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6725,7 +6725,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.8281007763318613</v>
+        <v>0.8153607643882942</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6733,22 +6733,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1521052441947387</v>
+        <v>0.1531152441947387</v>
       </c>
       <c r="C67">
-        <v>105.6282858190863</v>
+        <v>87.11613703001944</v>
       </c>
       <c r="D67">
-        <v>487.9282858190863</v>
+        <v>483.3361370300195</v>
       </c>
       <c r="E67">
-        <v>217.2</v>
+        <v>231.12</v>
       </c>
       <c r="F67">
-        <v>904.8000000000001</v>
+        <v>918.72</v>
       </c>
       <c r="G67">
         <v>522.5</v>
@@ -6769,37 +6769,37 @@
         <v>108.3</v>
       </c>
       <c r="M67">
-        <v>132.82464</v>
+        <v>134.868096</v>
       </c>
       <c r="N67">
-        <v>-24.52464000000001</v>
+        <v>-26.568096</v>
       </c>
       <c r="O67">
-        <v>-2.2072176</v>
+        <v>-2.39112864</v>
       </c>
       <c r="P67">
-        <v>-22.31742240000001</v>
+        <v>-24.17696736</v>
       </c>
       <c r="Q67">
-        <v>112.8825776</v>
+        <v>111.02303264</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1819639981918642</v>
+        <v>0.1859688216680954</v>
       </c>
       <c r="T67">
-        <v>1.981352084477403</v>
+        <v>2.039627145785562</v>
       </c>
       <c r="U67">
         <v>0.1468</v>
       </c>
       <c r="V67">
-        <v>0.07338246879494648</v>
+        <v>0.07227061320714426</v>
       </c>
       <c r="W67">
-        <v>0.1360274535809019</v>
+        <v>0.1361906739811913</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6807,7 +6807,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.8153607643882942</v>
+        <v>0.8030068134127141</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6815,22 +6815,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1531152441947387</v>
+        <v>0.1909471800671054</v>
       </c>
       <c r="C68">
-        <v>87.11613703001944</v>
+        <v>-52.78317398699971</v>
       </c>
       <c r="D68">
-        <v>483.3361370300195</v>
+        <v>357.3568260130004</v>
       </c>
       <c r="E68">
-        <v>231.12</v>
+        <v>245.0400000000001</v>
       </c>
       <c r="F68">
-        <v>918.72</v>
+        <v>932.6400000000001</v>
       </c>
       <c r="G68">
         <v>522.5</v>
@@ -6851,45 +6851,45 @@
         <v>108.3</v>
       </c>
       <c r="M68">
-        <v>134.868096</v>
+        <v>187.274112</v>
       </c>
       <c r="N68">
-        <v>-26.568096</v>
+        <v>-78.97411200000002</v>
       </c>
       <c r="O68">
-        <v>-2.39112864</v>
+        <v>-7.107670080000002</v>
       </c>
       <c r="P68">
-        <v>-24.17696736</v>
+        <v>-71.86644192000001</v>
       </c>
       <c r="Q68">
-        <v>111.02303264</v>
+        <v>63.33355807999997</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1859688216680954</v>
+        <v>0.1921616219379368</v>
       </c>
       <c r="T68">
-        <v>2.039627145785562</v>
+        <v>2.129739935409386</v>
       </c>
       <c r="U68">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V68">
-        <v>0.07227061320714426</v>
+        <v>0.05204670253622668</v>
       </c>
       <c r="W68">
-        <v>0.1361906739811913</v>
+        <v>0.1903490221307257</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y68">
-        <v>0.8030068134127141</v>
+        <v>0.5782966948469631</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6897,22 +6897,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1909471800671054</v>
+        <v>0.1924971800671053</v>
       </c>
       <c r="C69">
-        <v>-52.78317398699971</v>
+        <v>-70.47900035303303</v>
       </c>
       <c r="D69">
-        <v>357.3568260130004</v>
+        <v>353.580999646967</v>
       </c>
       <c r="E69">
-        <v>245.0400000000001</v>
+        <v>258.96</v>
       </c>
       <c r="F69">
-        <v>932.6400000000001</v>
+        <v>946.5600000000001</v>
       </c>
       <c r="G69">
         <v>522.5</v>
@@ -6933,37 +6933,37 @@
         <v>108.3</v>
       </c>
       <c r="M69">
-        <v>187.274112</v>
+        <v>190.069248</v>
       </c>
       <c r="N69">
-        <v>-78.97411200000002</v>
+        <v>-81.769248</v>
       </c>
       <c r="O69">
-        <v>-7.107670080000002</v>
+        <v>-7.35923232</v>
       </c>
       <c r="P69">
-        <v>-71.86644192000001</v>
+        <v>-74.41001568</v>
       </c>
       <c r="Q69">
-        <v>63.33355807999997</v>
+        <v>60.78998431999999</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1921616219379368</v>
+        <v>0.1967354226234973</v>
       </c>
       <c r="T69">
-        <v>2.129739935409386</v>
+        <v>2.19629430839093</v>
       </c>
       <c r="U69">
         <v>0.2008</v>
       </c>
       <c r="V69">
-        <v>0.05204670253622668</v>
+        <v>0.05128130985187041</v>
       </c>
       <c r="W69">
-        <v>0.1903490221307257</v>
+        <v>0.1905027129817444</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6971,7 +6971,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.5782966948469631</v>
+        <v>0.5697923316874489</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6979,22 +6979,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1924971800671053</v>
+        <v>0.1940471800671053</v>
       </c>
       <c r="C70">
-        <v>-70.47900035303303</v>
+        <v>-88.09587033197454</v>
       </c>
       <c r="D70">
-        <v>353.580999646967</v>
+        <v>349.8841296680256</v>
       </c>
       <c r="E70">
-        <v>258.96</v>
+        <v>272.8800000000001</v>
       </c>
       <c r="F70">
-        <v>946.5600000000001</v>
+        <v>960.4800000000001</v>
       </c>
       <c r="G70">
         <v>522.5</v>
@@ -7015,37 +7015,37 @@
         <v>108.3</v>
       </c>
       <c r="M70">
-        <v>190.069248</v>
+        <v>192.864384</v>
       </c>
       <c r="N70">
-        <v>-81.769248</v>
+        <v>-84.56438400000002</v>
       </c>
       <c r="O70">
-        <v>-7.35923232</v>
+        <v>-7.610794560000001</v>
       </c>
       <c r="P70">
-        <v>-74.41001568</v>
+        <v>-76.95358944000002</v>
       </c>
       <c r="Q70">
-        <v>60.78998431999999</v>
+        <v>58.24641055999997</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1967354226234973</v>
+        <v>0.2016043072242553</v>
       </c>
       <c r="T70">
-        <v>2.19629430839093</v>
+        <v>2.267142511887411</v>
       </c>
       <c r="U70">
         <v>0.2008</v>
       </c>
       <c r="V70">
-        <v>0.05128130985187041</v>
+        <v>0.05053810246271286</v>
       </c>
       <c r="W70">
-        <v>0.1905027129817444</v>
+        <v>0.1906519490254873</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7053,7 +7053,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.5697923316874489</v>
+        <v>0.5615344718079207</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7061,22 +7061,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1940471800671053</v>
+        <v>0.1955971800671054</v>
       </c>
       <c r="C71">
-        <v>-88.09587033197454</v>
+        <v>-105.6362348858499</v>
       </c>
       <c r="D71">
-        <v>349.8841296680256</v>
+        <v>346.2637651141501</v>
       </c>
       <c r="E71">
-        <v>272.8800000000001</v>
+        <v>286.8000000000001</v>
       </c>
       <c r="F71">
-        <v>960.4800000000001</v>
+        <v>974.4000000000001</v>
       </c>
       <c r="G71">
         <v>522.5</v>
@@ -7097,37 +7097,37 @@
         <v>108.3</v>
       </c>
       <c r="M71">
-        <v>192.864384</v>
+        <v>195.65952</v>
       </c>
       <c r="N71">
-        <v>-84.56438400000002</v>
+        <v>-87.35952</v>
       </c>
       <c r="O71">
-        <v>-7.610794560000001</v>
+        <v>-7.8623568</v>
       </c>
       <c r="P71">
-        <v>-76.95358944000002</v>
+        <v>-79.4971632</v>
       </c>
       <c r="Q71">
-        <v>58.24641055999997</v>
+        <v>55.70283679999999</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.2016043072242553</v>
+        <v>0.2067977841317304</v>
       </c>
       <c r="T71">
-        <v>2.267142511887411</v>
+        <v>2.342713928950325</v>
       </c>
       <c r="U71">
         <v>0.2008</v>
       </c>
       <c r="V71">
-        <v>0.05053810246271286</v>
+        <v>0.04981612957038839</v>
       </c>
       <c r="W71">
-        <v>0.1906519490254873</v>
+        <v>0.190796921182266</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7135,7 +7135,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.5615344718079207</v>
+        <v>0.5535125507820933</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7143,22 +7143,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1955971800671054</v>
+        <v>0.1971471800671054</v>
       </c>
       <c r="C72">
-        <v>-105.6362348858499</v>
+        <v>-123.1024445720096</v>
       </c>
       <c r="D72">
-        <v>346.2637651141501</v>
+        <v>342.7175554279904</v>
       </c>
       <c r="E72">
-        <v>286.8000000000001</v>
+        <v>300.72</v>
       </c>
       <c r="F72">
-        <v>974.4000000000001</v>
+        <v>988.3200000000001</v>
       </c>
       <c r="G72">
         <v>522.5</v>
@@ -7179,37 +7179,37 @@
         <v>108.3</v>
       </c>
       <c r="M72">
-        <v>195.65952</v>
+        <v>198.454656</v>
       </c>
       <c r="N72">
-        <v>-87.35952</v>
+        <v>-90.15465600000002</v>
       </c>
       <c r="O72">
-        <v>-7.8623568</v>
+        <v>-8.113919040000001</v>
       </c>
       <c r="P72">
-        <v>-79.4971632</v>
+        <v>-82.04073696000002</v>
       </c>
       <c r="Q72">
-        <v>55.70283679999999</v>
+        <v>53.15926303999997</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.2067977841317304</v>
+        <v>0.2123494318604108</v>
       </c>
       <c r="T72">
-        <v>2.342713928950325</v>
+        <v>2.423497167879647</v>
       </c>
       <c r="U72">
         <v>0.2008</v>
       </c>
       <c r="V72">
-        <v>0.04981612957038839</v>
+        <v>0.04911449394263644</v>
       </c>
       <c r="W72">
-        <v>0.190796921182266</v>
+        <v>0.1909378096163186</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7217,7 +7217,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.5535125507820933</v>
+        <v>0.5457165993626272</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7225,22 +7225,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1971471800671053</v>
+        <v>0.1986971800671054</v>
       </c>
       <c r="C73">
-        <v>-123.1024445720095</v>
+        <v>-140.496754632406</v>
       </c>
       <c r="D73">
-        <v>342.7175554279904</v>
+        <v>339.243245367594</v>
       </c>
       <c r="E73">
-        <v>300.7199999999999</v>
+        <v>314.64</v>
       </c>
       <c r="F73">
-        <v>988.3199999999999</v>
+        <v>1002.24</v>
       </c>
       <c r="G73">
         <v>522.5</v>
@@ -7261,37 +7261,37 @@
         <v>108.3</v>
       </c>
       <c r="M73">
-        <v>198.454656</v>
+        <v>201.249792</v>
       </c>
       <c r="N73">
-        <v>-90.15465599999999</v>
+        <v>-92.949792</v>
       </c>
       <c r="O73">
-        <v>-8.113919039999999</v>
+        <v>-8.365481279999999</v>
       </c>
       <c r="P73">
-        <v>-82.04073695999999</v>
+        <v>-84.58431072</v>
       </c>
       <c r="Q73">
-        <v>53.15926304</v>
+        <v>50.61568927999998</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.2123494318604108</v>
+        <v>0.2182976258554254</v>
       </c>
       <c r="T73">
-        <v>2.423497167879646</v>
+        <v>2.510050638161062</v>
       </c>
       <c r="U73">
         <v>0.2008</v>
       </c>
       <c r="V73">
-        <v>0.04911449394263646</v>
+        <v>0.04843234819343317</v>
       </c>
       <c r="W73">
-        <v>0.1909378096163186</v>
+        <v>0.1910747844827586</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7299,7 +7299,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.5457165993626272</v>
+        <v>0.5381372021492574</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7307,22 +7307,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1986971800671054</v>
+        <v>0.2002471800671053</v>
       </c>
       <c r="C74">
-        <v>-140.496754632406</v>
+        <v>-157.8213297764215</v>
       </c>
       <c r="D74">
-        <v>339.243245367594</v>
+        <v>335.8386702235784</v>
       </c>
       <c r="E74">
-        <v>314.64</v>
+        <v>328.5599999999999</v>
       </c>
       <c r="F74">
-        <v>1002.24</v>
+        <v>1016.16</v>
       </c>
       <c r="G74">
         <v>522.5</v>
@@ -7343,37 +7343,37 @@
         <v>108.3</v>
       </c>
       <c r="M74">
-        <v>201.249792</v>
+        <v>204.044928</v>
       </c>
       <c r="N74">
-        <v>-92.949792</v>
+        <v>-95.74492799999999</v>
       </c>
       <c r="O74">
-        <v>-8.365481279999999</v>
+        <v>-8.617043519999999</v>
       </c>
       <c r="P74">
-        <v>-84.58431072</v>
+        <v>-87.12788447999999</v>
       </c>
       <c r="Q74">
-        <v>50.61568927999998</v>
+        <v>48.07211552</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.2182976258554254</v>
+        <v>0.2246864268130337</v>
       </c>
       <c r="T74">
-        <v>2.510050638161062</v>
+        <v>2.603015476611471</v>
       </c>
       <c r="U74">
         <v>0.2008</v>
       </c>
       <c r="V74">
-        <v>0.04843234819343317</v>
+        <v>0.04776889136886558</v>
       </c>
       <c r="W74">
-        <v>0.1910747844827586</v>
+        <v>0.1912080066131318</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7381,7 +7381,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.5381372021492574</v>
+        <v>0.5307654596540621</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7389,22 +7389,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.2002471800671053</v>
+        <v>0.2017971800671053</v>
       </c>
       <c r="C75">
-        <v>-157.8213297764215</v>
+        <v>-175.0782486785621</v>
       </c>
       <c r="D75">
-        <v>335.8386702235784</v>
+        <v>332.5017513214378</v>
       </c>
       <c r="E75">
-        <v>328.5599999999999</v>
+        <v>342.4799999999999</v>
       </c>
       <c r="F75">
-        <v>1016.16</v>
+        <v>1030.08</v>
       </c>
       <c r="G75">
         <v>522.5</v>
@@ -7425,37 +7425,37 @@
         <v>108.3</v>
       </c>
       <c r="M75">
-        <v>204.044928</v>
+        <v>206.840064</v>
       </c>
       <c r="N75">
-        <v>-95.74492799999999</v>
+        <v>-98.54006399999997</v>
       </c>
       <c r="O75">
-        <v>-8.617043519999999</v>
+        <v>-8.868605759999998</v>
       </c>
       <c r="P75">
-        <v>-87.12788447999999</v>
+        <v>-89.67145823999998</v>
       </c>
       <c r="Q75">
-        <v>48.07211552</v>
+        <v>45.52854176000001</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.2246864268130337</v>
+        <v>0.2315666739981504</v>
       </c>
       <c r="T75">
-        <v>2.603015476611471</v>
+        <v>2.703131456481143</v>
       </c>
       <c r="U75">
         <v>0.2008</v>
       </c>
       <c r="V75">
-        <v>0.04776889136886558</v>
+        <v>0.04712336580982687</v>
       </c>
       <c r="W75">
-        <v>0.1912080066131318</v>
+        <v>0.1913376281453868</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7463,7 +7463,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.5307654596540621</v>
+        <v>0.5235929534425208</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7471,22 +7471,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.2017971800671053</v>
+        <v>0.2033471800671053</v>
       </c>
       <c r="C76">
-        <v>-175.0782486785621</v>
+        <v>-192.2695082106509</v>
       </c>
       <c r="D76">
-        <v>332.5017513214378</v>
+        <v>329.2304917893491</v>
       </c>
       <c r="E76">
-        <v>342.4799999999999</v>
+        <v>356.4</v>
       </c>
       <c r="F76">
-        <v>1030.08</v>
+        <v>1044</v>
       </c>
       <c r="G76">
         <v>522.5</v>
@@ -7507,37 +7507,37 @@
         <v>108.3</v>
       </c>
       <c r="M76">
-        <v>206.840064</v>
+        <v>209.6352</v>
       </c>
       <c r="N76">
-        <v>-98.54006399999997</v>
+        <v>-101.3352</v>
       </c>
       <c r="O76">
-        <v>-8.868605759999998</v>
+        <v>-9.120167999999998</v>
       </c>
       <c r="P76">
-        <v>-89.67145823999998</v>
+        <v>-92.21503199999999</v>
       </c>
       <c r="Q76">
-        <v>45.52854176000001</v>
+        <v>42.98496799999999</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2315666739981504</v>
+        <v>0.2389973409580765</v>
       </c>
       <c r="T76">
-        <v>2.703131456481143</v>
+        <v>2.811256714740389</v>
       </c>
       <c r="U76">
         <v>0.2008</v>
       </c>
       <c r="V76">
-        <v>0.04712336580982687</v>
+        <v>0.04649505426569583</v>
       </c>
       <c r="W76">
-        <v>0.1913376281453868</v>
+        <v>0.1914637931034483</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7545,7 +7545,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.5235929534425208</v>
+        <v>0.5166117140632871</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7553,22 +7553,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.2033471800671053</v>
+        <v>0.2048971800671054</v>
       </c>
       <c r="C77">
-        <v>-192.2695082106509</v>
+        <v>-209.3970274266312</v>
       </c>
       <c r="D77">
-        <v>329.2304917893491</v>
+        <v>326.0229725733689</v>
       </c>
       <c r="E77">
-        <v>356.4</v>
+        <v>370.3200000000001</v>
       </c>
       <c r="F77">
-        <v>1044</v>
+        <v>1057.92</v>
       </c>
       <c r="G77">
         <v>522.5</v>
@@ -7589,37 +7589,37 @@
         <v>108.3</v>
       </c>
       <c r="M77">
-        <v>209.6352</v>
+        <v>212.430336</v>
       </c>
       <c r="N77">
-        <v>-101.3352</v>
+        <v>-104.130336</v>
       </c>
       <c r="O77">
-        <v>-9.120167999999998</v>
+        <v>-9.37173024</v>
       </c>
       <c r="P77">
-        <v>-92.21503199999999</v>
+        <v>-94.75860575999999</v>
       </c>
       <c r="Q77">
-        <v>42.98496799999999</v>
+        <v>40.44139423999999</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2389973409580765</v>
+        <v>0.2470472301646631</v>
       </c>
       <c r="T77">
-        <v>2.811256714740389</v>
+        <v>2.928392411187906</v>
       </c>
       <c r="U77">
         <v>0.2008</v>
       </c>
       <c r="V77">
-        <v>0.04649505426569583</v>
+        <v>0.04588327723588405</v>
       </c>
       <c r="W77">
-        <v>0.1914637931034483</v>
+        <v>0.1915866379310345</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7627,7 +7627,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.5166117140632871</v>
+        <v>0.5098141915098229</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7635,22 +7635,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2048971800671054</v>
+        <v>0.2064471800671053</v>
       </c>
       <c r="C78">
-        <v>-209.3970274266312</v>
+        <v>-226.4626513166838</v>
       </c>
       <c r="D78">
-        <v>326.0229725733689</v>
+        <v>322.877348683316</v>
       </c>
       <c r="E78">
-        <v>370.3200000000001</v>
+        <v>384.2399999999999</v>
       </c>
       <c r="F78">
-        <v>1057.92</v>
+        <v>1071.84</v>
       </c>
       <c r="G78">
         <v>522.5</v>
@@ -7671,37 +7671,37 @@
         <v>108.3</v>
       </c>
       <c r="M78">
-        <v>212.430336</v>
+        <v>215.225472</v>
       </c>
       <c r="N78">
-        <v>-104.130336</v>
+        <v>-106.925472</v>
       </c>
       <c r="O78">
-        <v>-9.37173024</v>
+        <v>-9.623292479999998</v>
       </c>
       <c r="P78">
-        <v>-94.75860575999999</v>
+        <v>-97.30217951999998</v>
       </c>
       <c r="Q78">
-        <v>40.44139423999999</v>
+        <v>37.89782048000001</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2470472301646631</v>
+        <v>0.2557971097370396</v>
       </c>
       <c r="T78">
-        <v>2.928392411187906</v>
+        <v>3.055713820369988</v>
       </c>
       <c r="U78">
         <v>0.2008</v>
       </c>
       <c r="V78">
-        <v>0.04588327723588405</v>
+        <v>0.04528739051853491</v>
       </c>
       <c r="W78">
-        <v>0.1915866379310345</v>
+        <v>0.1917062919838782</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7709,7 +7709,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.5098141915098229</v>
+        <v>0.5031932279837212</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7717,22 +7717,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2064471800671053</v>
+        <v>0.2355562089453307</v>
       </c>
       <c r="C79">
-        <v>-226.4626513166838</v>
+        <v>-289.9127621846519</v>
       </c>
       <c r="D79">
-        <v>322.877348683316</v>
+        <v>273.3472378153481</v>
       </c>
       <c r="E79">
-        <v>384.2399999999999</v>
+        <v>398.16</v>
       </c>
       <c r="F79">
-        <v>1071.84</v>
+        <v>1085.76</v>
       </c>
       <c r="G79">
         <v>522.5</v>
@@ -7753,45 +7753,45 @@
         <v>108.3</v>
       </c>
       <c r="M79">
-        <v>215.225472</v>
+        <v>256.022208</v>
       </c>
       <c r="N79">
-        <v>-106.925472</v>
+        <v>-147.722208</v>
       </c>
       <c r="O79">
-        <v>-9.623292479999998</v>
+        <v>-13.29499872</v>
       </c>
       <c r="P79">
-        <v>-97.30217951999998</v>
+        <v>-134.42720928</v>
       </c>
       <c r="Q79">
-        <v>37.89782048000001</v>
+        <v>0.7727907199999606</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2557971097370396</v>
+        <v>0.2665198368988388</v>
       </c>
       <c r="T79">
-        <v>3.055713820369988</v>
+        <v>3.211742565819847</v>
       </c>
       <c r="U79">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.04528739051853491</v>
+        <v>0.03807091609802849</v>
       </c>
       <c r="W79">
-        <v>0.1917062919838782</v>
+        <v>0.2268228779840849</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y79">
-        <v>0.5031932279837212</v>
+        <v>0.4230101788669832</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7799,22 +7799,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2355562089453307</v>
+        <v>0.2374562089453308</v>
       </c>
       <c r="C80">
-        <v>-289.9127621846519</v>
+        <v>-306.5426130927293</v>
       </c>
       <c r="D80">
-        <v>273.3472378153481</v>
+        <v>270.6373869072708</v>
       </c>
       <c r="E80">
-        <v>398.16</v>
+        <v>412.08</v>
       </c>
       <c r="F80">
-        <v>1085.76</v>
+        <v>1099.68</v>
       </c>
       <c r="G80">
         <v>522.5</v>
@@ -7835,37 +7835,37 @@
         <v>108.3</v>
       </c>
       <c r="M80">
-        <v>256.022208</v>
+        <v>259.304544</v>
       </c>
       <c r="N80">
-        <v>-147.722208</v>
+        <v>-151.004544</v>
       </c>
       <c r="O80">
-        <v>-13.29499872</v>
+        <v>-13.59040896</v>
       </c>
       <c r="P80">
-        <v>-134.42720928</v>
+        <v>-137.41413504</v>
       </c>
       <c r="Q80">
-        <v>0.7727907199999606</v>
+        <v>-2.214135040000031</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2665198368988388</v>
+        <v>0.2770303053225931</v>
       </c>
       <c r="T80">
-        <v>3.211742565819847</v>
+        <v>3.364682688001744</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.03807091609802849</v>
+        <v>0.0375890057676737</v>
       </c>
       <c r="W80">
-        <v>0.2268228779840849</v>
+        <v>0.2269365124399826</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7873,7 +7873,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.4230101788669832</v>
+        <v>0.417655619640819</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7881,22 +7881,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2374562089453308</v>
+        <v>0.2393562089453308</v>
       </c>
       <c r="C81">
-        <v>-306.5426130927293</v>
+        <v>-323.119262744661</v>
       </c>
       <c r="D81">
-        <v>270.6373869072708</v>
+        <v>267.9807372553391</v>
       </c>
       <c r="E81">
-        <v>412.08</v>
+        <v>426.0000000000001</v>
       </c>
       <c r="F81">
-        <v>1099.68</v>
+        <v>1113.6</v>
       </c>
       <c r="G81">
         <v>522.5</v>
@@ -7917,37 +7917,37 @@
         <v>108.3</v>
       </c>
       <c r="M81">
-        <v>259.304544</v>
+        <v>262.5868800000001</v>
       </c>
       <c r="N81">
-        <v>-151.004544</v>
+        <v>-154.2868800000001</v>
       </c>
       <c r="O81">
-        <v>-13.59040896</v>
+        <v>-13.8858192</v>
       </c>
       <c r="P81">
-        <v>-137.41413504</v>
+        <v>-140.4010608</v>
       </c>
       <c r="Q81">
-        <v>-2.214135040000031</v>
+        <v>-5.20106080000005</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2770303053225931</v>
+        <v>0.2885918205887227</v>
       </c>
       <c r="T81">
-        <v>3.364682688001744</v>
+        <v>3.532916822401832</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.0375890057676737</v>
+        <v>0.03711914319557778</v>
       </c>
       <c r="W81">
-        <v>0.2269365124399826</v>
+        <v>0.2270473060344828</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7955,7 +7955,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.417655619640819</v>
+        <v>0.4124349243953086</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7963,22 +7963,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2393562089453308</v>
+        <v>0.2412562089453308</v>
       </c>
       <c r="C82">
-        <v>-323.119262744661</v>
+        <v>-339.6442626243402</v>
       </c>
       <c r="D82">
-        <v>267.9807372553391</v>
+        <v>265.3757373756598</v>
       </c>
       <c r="E82">
-        <v>426.0000000000001</v>
+        <v>439.92</v>
       </c>
       <c r="F82">
-        <v>1113.6</v>
+        <v>1127.52</v>
       </c>
       <c r="G82">
         <v>522.5</v>
@@ -7999,37 +7999,37 @@
         <v>108.3</v>
       </c>
       <c r="M82">
-        <v>262.5868800000001</v>
+        <v>265.869216</v>
       </c>
       <c r="N82">
-        <v>-154.2868800000001</v>
+        <v>-157.569216</v>
       </c>
       <c r="O82">
-        <v>-13.8858192</v>
+        <v>-14.18122944</v>
       </c>
       <c r="P82">
-        <v>-140.4010608</v>
+        <v>-143.38798656</v>
       </c>
       <c r="Q82">
-        <v>-5.20106080000005</v>
+        <v>-8.187986559999985</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2885918205887227</v>
+        <v>0.3013703374618134</v>
       </c>
       <c r="T82">
-        <v>3.532916822401832</v>
+        <v>3.718859813054559</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.03711914319557778</v>
+        <v>0.03666088216847189</v>
       </c>
       <c r="W82">
-        <v>0.2270473060344828</v>
+        <v>0.2271553639846743</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8037,7 +8037,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.4124349243953086</v>
+        <v>0.4073431352052432</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8045,22 +8045,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2412562089453308</v>
+        <v>0.2431562089453308</v>
       </c>
       <c r="C83">
-        <v>-339.6442626243402</v>
+        <v>-356.1191044694904</v>
       </c>
       <c r="D83">
-        <v>265.3757373756598</v>
+        <v>262.8208955305097</v>
       </c>
       <c r="E83">
-        <v>439.92</v>
+        <v>453.84</v>
       </c>
       <c r="F83">
-        <v>1127.52</v>
+        <v>1141.44</v>
       </c>
       <c r="G83">
         <v>522.5</v>
@@ -8081,37 +8081,37 @@
         <v>108.3</v>
       </c>
       <c r="M83">
-        <v>265.869216</v>
+        <v>269.151552</v>
       </c>
       <c r="N83">
-        <v>-157.569216</v>
+        <v>-160.851552</v>
       </c>
       <c r="O83">
-        <v>-14.18122944</v>
+        <v>-14.47663968</v>
       </c>
       <c r="P83">
-        <v>-143.38798656</v>
+        <v>-146.37491232</v>
       </c>
       <c r="Q83">
-        <v>-8.187986559999985</v>
+        <v>-11.17491232000003</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.3013703374618134</v>
+        <v>0.3155686895430253</v>
       </c>
       <c r="T83">
-        <v>3.718859813054559</v>
+        <v>3.925463136002036</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.03666088216847189</v>
+        <v>0.03621379823958808</v>
       </c>
       <c r="W83">
-        <v>0.2271553639846743</v>
+        <v>0.2272607863751052</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8119,7 +8119,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.4073431352052432</v>
+        <v>0.4023755359954231</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8127,22 +8127,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2431562089453308</v>
+        <v>0.2450562089453308</v>
       </c>
       <c r="C84">
-        <v>-356.1191044694904</v>
+        <v>-372.5452231202019</v>
       </c>
       <c r="D84">
-        <v>262.8208955305097</v>
+        <v>260.3147768797982</v>
       </c>
       <c r="E84">
-        <v>453.84</v>
+        <v>467.7600000000001</v>
       </c>
       <c r="F84">
-        <v>1141.44</v>
+        <v>1155.36</v>
       </c>
       <c r="G84">
         <v>522.5</v>
@@ -8163,37 +8163,37 @@
         <v>108.3</v>
       </c>
       <c r="M84">
-        <v>269.151552</v>
+        <v>272.433888</v>
       </c>
       <c r="N84">
-        <v>-160.851552</v>
+        <v>-164.133888</v>
       </c>
       <c r="O84">
-        <v>-14.47663968</v>
+        <v>-14.77204992</v>
       </c>
       <c r="P84">
-        <v>-146.37491232</v>
+        <v>-149.36183808</v>
       </c>
       <c r="Q84">
-        <v>-11.17491232000003</v>
+        <v>-14.16183808000002</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.3155686895430253</v>
+        <v>0.3314374359867327</v>
       </c>
       <c r="T84">
-        <v>3.925463136002036</v>
+        <v>4.15637273223745</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.03621379823958808</v>
+        <v>0.03577748741742437</v>
       </c>
       <c r="W84">
-        <v>0.2272607863751052</v>
+        <v>0.2273636684669713</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8201,7 +8201,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.4023755359954231</v>
+        <v>0.3975276379713819</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8209,22 +8209,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2450562089453308</v>
+        <v>0.2469562089453308</v>
       </c>
       <c r="C85">
-        <v>-372.5452231202019</v>
+        <v>-388.9239992060352</v>
       </c>
       <c r="D85">
-        <v>260.3147768797982</v>
+        <v>257.856000793965</v>
       </c>
       <c r="E85">
-        <v>467.7600000000001</v>
+        <v>481.6800000000002</v>
       </c>
       <c r="F85">
-        <v>1155.36</v>
+        <v>1169.28</v>
       </c>
       <c r="G85">
         <v>522.5</v>
@@ -8245,37 +8245,37 @@
         <v>108.3</v>
       </c>
       <c r="M85">
-        <v>272.433888</v>
+        <v>275.7162240000001</v>
       </c>
       <c r="N85">
-        <v>-164.133888</v>
+        <v>-167.4162240000001</v>
       </c>
       <c r="O85">
-        <v>-14.77204992</v>
+        <v>-15.06746016</v>
       </c>
       <c r="P85">
-        <v>-149.36183808</v>
+        <v>-152.3487638400001</v>
       </c>
       <c r="Q85">
-        <v>-14.16183808000002</v>
+        <v>-17.14876384000007</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.3314374359867327</v>
+        <v>0.3492897757359036</v>
       </c>
       <c r="T85">
-        <v>4.15637273223745</v>
+        <v>4.416146028002292</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.03577748741742437</v>
+        <v>0.03535156494816931</v>
       </c>
       <c r="W85">
-        <v>0.2273636684669713</v>
+        <v>0.2274641009852217</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8283,7 +8283,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.3975276379713819</v>
+        <v>0.3927951660907701</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8291,22 +8291,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2469562089453308</v>
+        <v>0.2488562089453307</v>
       </c>
       <c r="C86">
-        <v>-388.923999206035</v>
+        <v>-405.2567616822636</v>
       </c>
       <c r="D86">
-        <v>257.856000793965</v>
+        <v>255.4432383177365</v>
       </c>
       <c r="E86">
-        <v>481.6799999999999</v>
+        <v>495.6</v>
       </c>
       <c r="F86">
-        <v>1169.28</v>
+        <v>1183.2</v>
       </c>
       <c r="G86">
         <v>522.5</v>
@@ -8327,37 +8327,37 @@
         <v>108.3</v>
       </c>
       <c r="M86">
-        <v>275.716224</v>
+        <v>278.99856</v>
       </c>
       <c r="N86">
-        <v>-167.416224</v>
+        <v>-170.69856</v>
       </c>
       <c r="O86">
-        <v>-15.06746016</v>
+        <v>-15.3628704</v>
       </c>
       <c r="P86">
-        <v>-152.34876384</v>
+        <v>-155.3356896</v>
       </c>
       <c r="Q86">
-        <v>-17.14876384000002</v>
+        <v>-20.13568960000001</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.3492897757359034</v>
+        <v>0.3695224274516302</v>
       </c>
       <c r="T86">
-        <v>4.416146028002288</v>
+        <v>4.71055576320244</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.03535156494816932</v>
+        <v>0.03493566418407321</v>
       </c>
       <c r="W86">
-        <v>0.2274641009852217</v>
+        <v>0.2275621703853955</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8365,7 +8365,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.3927951660907703</v>
+        <v>0.3881740464897023</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8373,22 +8373,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2488562089453307</v>
+        <v>0.2507562089453307</v>
       </c>
       <c r="C87">
-        <v>-405.2567616822636</v>
+        <v>-421.5447902250492</v>
       </c>
       <c r="D87">
-        <v>255.4432383177365</v>
+        <v>253.0752097749508</v>
       </c>
       <c r="E87">
-        <v>495.6</v>
+        <v>509.5199999999999</v>
       </c>
       <c r="F87">
-        <v>1183.2</v>
+        <v>1197.12</v>
       </c>
       <c r="G87">
         <v>522.5</v>
@@ -8409,37 +8409,37 @@
         <v>108.3</v>
       </c>
       <c r="M87">
-        <v>278.99856</v>
+        <v>282.280896</v>
       </c>
       <c r="N87">
-        <v>-170.69856</v>
+        <v>-173.980896</v>
       </c>
       <c r="O87">
-        <v>-15.3628704</v>
+        <v>-15.65828064</v>
       </c>
       <c r="P87">
-        <v>-155.3356896</v>
+        <v>-158.32261536</v>
       </c>
       <c r="Q87">
-        <v>-20.13568960000001</v>
+        <v>-23.12261536</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.3695224274516302</v>
+        <v>0.3926454579838896</v>
       </c>
       <c r="T87">
-        <v>4.71055576320244</v>
+        <v>5.047024032002615</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.03493566418407321</v>
+        <v>0.03452943553077004</v>
       </c>
       <c r="W87">
-        <v>0.2275621703853955</v>
+        <v>0.2276579591018444</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8447,7 +8447,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.3881740464897023</v>
+        <v>0.3836603947863337</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8455,22 +8455,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2507562089453307</v>
+        <v>0.2526562089453308</v>
       </c>
       <c r="C88">
-        <v>-421.5447902250492</v>
+        <v>-437.789317494615</v>
       </c>
       <c r="D88">
-        <v>253.0752097749508</v>
+        <v>250.7506825053849</v>
       </c>
       <c r="E88">
-        <v>509.5199999999999</v>
+        <v>523.4399999999999</v>
       </c>
       <c r="F88">
-        <v>1197.12</v>
+        <v>1211.04</v>
       </c>
       <c r="G88">
         <v>522.5</v>
@@ -8491,37 +8491,37 @@
         <v>108.3</v>
       </c>
       <c r="M88">
-        <v>282.280896</v>
+        <v>285.563232</v>
       </c>
       <c r="N88">
-        <v>-173.980896</v>
+        <v>-177.263232</v>
       </c>
       <c r="O88">
-        <v>-15.65828064</v>
+        <v>-15.95369088</v>
       </c>
       <c r="P88">
-        <v>-158.32261536</v>
+        <v>-161.30954112</v>
       </c>
       <c r="Q88">
-        <v>-23.12261536</v>
+        <v>-26.10954112000002</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.3926454579838896</v>
+        <v>0.4193258778288041</v>
       </c>
       <c r="T88">
-        <v>5.047024032002615</v>
+        <v>5.43525664984897</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.03452943553077004</v>
+        <v>0.03413254546719796</v>
       </c>
       <c r="W88">
-        <v>0.2276579591018444</v>
+        <v>0.2277515457788347</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8529,7 +8529,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.3836603947863337</v>
+        <v>0.3792505051910885</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8537,22 +8537,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2526562089453308</v>
+        <v>0.2545562089453308</v>
       </c>
       <c r="C89">
-        <v>-437.789317494615</v>
+        <v>-453.991531274829</v>
       </c>
       <c r="D89">
-        <v>250.7506825053849</v>
+        <v>248.4684687251711</v>
       </c>
       <c r="E89">
-        <v>523.4399999999999</v>
+        <v>537.36</v>
       </c>
       <c r="F89">
-        <v>1211.04</v>
+        <v>1224.96</v>
       </c>
       <c r="G89">
         <v>522.5</v>
@@ -8573,37 +8573,37 @@
         <v>108.3</v>
       </c>
       <c r="M89">
-        <v>285.563232</v>
+        <v>288.845568</v>
       </c>
       <c r="N89">
-        <v>-177.263232</v>
+        <v>-180.545568</v>
       </c>
       <c r="O89">
-        <v>-15.95369088</v>
+        <v>-16.24910112</v>
       </c>
       <c r="P89">
-        <v>-161.30954112</v>
+        <v>-164.29646688</v>
       </c>
       <c r="Q89">
-        <v>-26.10954112000002</v>
+        <v>-29.09646688000001</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.4193258778288041</v>
+        <v>0.4504530343145379</v>
       </c>
       <c r="T89">
-        <v>5.43525664984897</v>
+        <v>5.888194704003052</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.03413254546719796</v>
+        <v>0.03374467563234344</v>
       </c>
       <c r="W89">
-        <v>0.2277515457788347</v>
+        <v>0.2278430054858934</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8611,7 +8611,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.3792505051910885</v>
+        <v>0.3749408403593716</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8619,22 +8619,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2545562089453308</v>
+        <v>0.2564562089453307</v>
       </c>
       <c r="C90">
-        <v>-453.991531274829</v>
+        <v>-470.1525764970011</v>
       </c>
       <c r="D90">
-        <v>248.4684687251711</v>
+        <v>246.2274235029991</v>
       </c>
       <c r="E90">
-        <v>537.36</v>
+        <v>551.2800000000001</v>
       </c>
       <c r="F90">
-        <v>1224.96</v>
+        <v>1238.88</v>
       </c>
       <c r="G90">
         <v>522.5</v>
@@ -8655,37 +8655,37 @@
         <v>108.3</v>
       </c>
       <c r="M90">
-        <v>288.845568</v>
+        <v>292.1279040000001</v>
       </c>
       <c r="N90">
-        <v>-180.545568</v>
+        <v>-183.827904</v>
       </c>
       <c r="O90">
-        <v>-16.24910112</v>
+        <v>-16.54451136</v>
       </c>
       <c r="P90">
-        <v>-164.29646688</v>
+        <v>-167.28339264</v>
       </c>
       <c r="Q90">
-        <v>-29.09646688000001</v>
+        <v>-32.08339264000006</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.4504530343145379</v>
+        <v>0.4872396737976777</v>
       </c>
       <c r="T90">
-        <v>5.888194704003052</v>
+        <v>6.423485131639693</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.03374467563234344</v>
+        <v>0.03336552197355306</v>
       </c>
       <c r="W90">
-        <v>0.2278430054858934</v>
+        <v>0.2279324099186362</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8693,7 +8693,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.3749408403593716</v>
+        <v>0.3707280219283673</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8701,22 +8701,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2564562089453307</v>
+        <v>0.2583562089453307</v>
       </c>
       <c r="C91">
-        <v>-470.1525764970011</v>
+        <v>-486.2735571551384</v>
       </c>
       <c r="D91">
-        <v>246.2274235029991</v>
+        <v>244.0264428448615</v>
       </c>
       <c r="E91">
-        <v>551.2800000000001</v>
+        <v>565.1999999999999</v>
       </c>
       <c r="F91">
-        <v>1238.88</v>
+        <v>1252.8</v>
       </c>
       <c r="G91">
         <v>522.5</v>
@@ -8737,37 +8737,37 @@
         <v>108.3</v>
       </c>
       <c r="M91">
-        <v>292.1279040000001</v>
+        <v>295.41024</v>
       </c>
       <c r="N91">
-        <v>-183.827904</v>
+        <v>-187.11024</v>
       </c>
       <c r="O91">
-        <v>-16.54451136</v>
+        <v>-16.8399216</v>
       </c>
       <c r="P91">
-        <v>-167.28339264</v>
+        <v>-170.2703184</v>
       </c>
       <c r="Q91">
-        <v>-32.08339264000006</v>
+        <v>-35.07031839999999</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.4872396737976777</v>
+        <v>0.5313836411774455</v>
       </c>
       <c r="T91">
-        <v>6.423485131639693</v>
+        <v>7.065833644803663</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.03336552197355306</v>
+        <v>0.0329947939516247</v>
       </c>
       <c r="W91">
-        <v>0.2279324099186362</v>
+        <v>0.2280198275862069</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8775,7 +8775,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.3707280219283673</v>
+        <v>0.3666088216847189</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8783,22 +8783,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2583562089453307</v>
+        <v>0.2602562089453307</v>
       </c>
       <c r="C92">
-        <v>-486.2735571551384</v>
+        <v>-502.3555381193894</v>
       </c>
       <c r="D92">
-        <v>244.0264428448615</v>
+        <v>241.8644618806106</v>
       </c>
       <c r="E92">
-        <v>565.1999999999999</v>
+        <v>579.12</v>
       </c>
       <c r="F92">
-        <v>1252.8</v>
+        <v>1266.72</v>
       </c>
       <c r="G92">
         <v>522.5</v>
@@ -8819,37 +8819,37 @@
         <v>108.3</v>
       </c>
       <c r="M92">
-        <v>295.41024</v>
+        <v>298.692576</v>
       </c>
       <c r="N92">
-        <v>-187.11024</v>
+        <v>-190.392576</v>
       </c>
       <c r="O92">
-        <v>-16.8399216</v>
+        <v>-17.13533184</v>
       </c>
       <c r="P92">
-        <v>-170.2703184</v>
+        <v>-173.25724416</v>
       </c>
       <c r="Q92">
-        <v>-35.07031839999999</v>
+        <v>-38.05724416000004</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.5313836411774455</v>
+        <v>0.5853373790860505</v>
       </c>
       <c r="T92">
-        <v>7.065833644803663</v>
+        <v>7.850926272004071</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.0329947939516247</v>
+        <v>0.03263221379831014</v>
       </c>
       <c r="W92">
-        <v>0.2280198275862069</v>
+        <v>0.2281053239863585</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8857,7 +8857,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.3666088216847189</v>
+        <v>0.3625801533145571</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8865,22 +8865,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2602562089453307</v>
+        <v>0.2621562089453308</v>
       </c>
       <c r="C93">
-        <v>-502.3555381193894</v>
+        <v>-518.3995468539357</v>
       </c>
       <c r="D93">
-        <v>241.8644618806106</v>
+        <v>239.7404531460644</v>
       </c>
       <c r="E93">
-        <v>579.12</v>
+        <v>593.0400000000001</v>
       </c>
       <c r="F93">
-        <v>1266.72</v>
+        <v>1280.64</v>
       </c>
       <c r="G93">
         <v>522.5</v>
@@ -8901,37 +8901,37 @@
         <v>108.3</v>
       </c>
       <c r="M93">
-        <v>298.692576</v>
+        <v>301.974912</v>
       </c>
       <c r="N93">
-        <v>-190.392576</v>
+        <v>-193.674912</v>
       </c>
       <c r="O93">
-        <v>-17.13533184</v>
+        <v>-17.43074208</v>
       </c>
       <c r="P93">
-        <v>-173.25724416</v>
+        <v>-176.24416992</v>
       </c>
       <c r="Q93">
-        <v>-38.05724416000004</v>
+        <v>-41.04416992000003</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.5853373790860505</v>
+        <v>0.652779551471807</v>
       </c>
       <c r="T93">
-        <v>7.850926272004071</v>
+        <v>8.832292056004581</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.03263221379831014</v>
+        <v>0.03227751582224155</v>
       </c>
       <c r="W93">
-        <v>0.2281053239863585</v>
+        <v>0.2281889617691154</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8939,7 +8939,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.3625801533145571</v>
+        <v>0.3586390646915728</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8947,22 +8947,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2621562089453308</v>
+        <v>0.2640562089453308</v>
       </c>
       <c r="C94">
-        <v>-518.3995468539357</v>
+        <v>-534.4065750451548</v>
       </c>
       <c r="D94">
-        <v>239.7404531460644</v>
+        <v>237.6534249548453</v>
       </c>
       <c r="E94">
-        <v>593.0400000000001</v>
+        <v>606.9600000000002</v>
       </c>
       <c r="F94">
-        <v>1280.64</v>
+        <v>1294.56</v>
       </c>
       <c r="G94">
         <v>522.5</v>
@@ -8983,37 +8983,37 @@
         <v>108.3</v>
       </c>
       <c r="M94">
-        <v>301.974912</v>
+        <v>305.2572480000001</v>
       </c>
       <c r="N94">
-        <v>-193.674912</v>
+        <v>-196.957248</v>
       </c>
       <c r="O94">
-        <v>-17.43074208</v>
+        <v>-17.72615232</v>
       </c>
       <c r="P94">
-        <v>-176.24416992</v>
+        <v>-179.23109568</v>
       </c>
       <c r="Q94">
-        <v>-41.04416992000003</v>
+        <v>-44.03109568000005</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.652779551471807</v>
+        <v>0.7394909159677796</v>
       </c>
       <c r="T94">
-        <v>8.832292056004581</v>
+        <v>10.09404806400524</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.03227751582224155</v>
+        <v>0.0319304457596368</v>
       </c>
       <c r="W94">
-        <v>0.2281889617691154</v>
+        <v>0.2282708008898777</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9021,7 +9021,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.3586390646915728</v>
+        <v>0.3547827306626311</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9029,22 +9029,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2640562089453308</v>
+        <v>0.2659562089453308</v>
       </c>
       <c r="C95">
-        <v>-534.4065750451548</v>
+        <v>-550.3775801454757</v>
       </c>
       <c r="D95">
-        <v>237.6534249548453</v>
+        <v>235.6024198545243</v>
       </c>
       <c r="E95">
-        <v>606.9600000000002</v>
+        <v>620.88</v>
       </c>
       <c r="F95">
-        <v>1294.56</v>
+        <v>1308.48</v>
       </c>
       <c r="G95">
         <v>522.5</v>
@@ -9065,37 +9065,37 @@
         <v>108.3</v>
       </c>
       <c r="M95">
-        <v>305.2572480000001</v>
+        <v>308.539584</v>
       </c>
       <c r="N95">
-        <v>-196.957248</v>
+        <v>-200.239584</v>
       </c>
       <c r="O95">
-        <v>-17.72615232</v>
+        <v>-18.02156256</v>
       </c>
       <c r="P95">
-        <v>-179.23109568</v>
+        <v>-182.21802144</v>
       </c>
       <c r="Q95">
-        <v>-44.03109568000005</v>
+        <v>-47.01802143999998</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.7394909159677796</v>
+        <v>0.8551060686290765</v>
       </c>
       <c r="T95">
-        <v>10.09404806400524</v>
+        <v>11.77638940800611</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.0319304457596368</v>
+        <v>0.03159076016644918</v>
       </c>
       <c r="W95">
-        <v>0.2282708008898777</v>
+        <v>0.2283508987527513</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9103,7 +9103,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.3547827306626311</v>
+        <v>0.3510084462938798</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9111,22 +9111,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2659562089453308</v>
+        <v>0.2678562089453308</v>
       </c>
       <c r="C96">
-        <v>-550.3775801454757</v>
+        <v>-566.3134868379736</v>
       </c>
       <c r="D96">
-        <v>235.6024198545243</v>
+        <v>233.5865131620264</v>
       </c>
       <c r="E96">
-        <v>620.88</v>
+        <v>634.8000000000001</v>
       </c>
       <c r="F96">
-        <v>1308.48</v>
+        <v>1322.4</v>
       </c>
       <c r="G96">
         <v>522.5</v>
@@ -9147,37 +9147,37 @@
         <v>108.3</v>
       </c>
       <c r="M96">
-        <v>308.539584</v>
+        <v>311.82192</v>
       </c>
       <c r="N96">
-        <v>-200.239584</v>
+        <v>-203.52192</v>
       </c>
       <c r="O96">
-        <v>-18.02156256</v>
+        <v>-18.3169728</v>
       </c>
       <c r="P96">
-        <v>-182.21802144</v>
+        <v>-185.2049472</v>
       </c>
       <c r="Q96">
-        <v>-47.01802143999998</v>
+        <v>-50.00494720000003</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.8551060686290765</v>
+        <v>1.016967282354892</v>
       </c>
       <c r="T96">
-        <v>11.77638940800611</v>
+        <v>14.13166728960734</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.03159076016644918</v>
+        <v>0.0312582258489076</v>
       </c>
       <c r="W96">
-        <v>0.2283508987527513</v>
+        <v>0.2284293103448276</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9185,7 +9185,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.3510084462938798</v>
+        <v>0.3473136205434179</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9193,22 +9193,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2678562089453308</v>
+        <v>0.2697562089453308</v>
       </c>
       <c r="C97">
-        <v>-566.3134868379736</v>
+        <v>-582.2151884264132</v>
       </c>
       <c r="D97">
-        <v>233.5865131620264</v>
+        <v>231.604811573587</v>
       </c>
       <c r="E97">
-        <v>634.8000000000001</v>
+        <v>648.7200000000001</v>
       </c>
       <c r="F97">
-        <v>1322.4</v>
+        <v>1336.32</v>
       </c>
       <c r="G97">
         <v>522.5</v>
@@ -9229,37 +9229,37 @@
         <v>108.3</v>
       </c>
       <c r="M97">
-        <v>311.82192</v>
+        <v>315.1042560000001</v>
       </c>
       <c r="N97">
-        <v>-203.52192</v>
+        <v>-206.8042560000001</v>
       </c>
       <c r="O97">
-        <v>-18.3169728</v>
+        <v>-18.61238304</v>
       </c>
       <c r="P97">
-        <v>-185.2049472</v>
+        <v>-188.1918729600001</v>
       </c>
       <c r="Q97">
-        <v>-50.00494720000003</v>
+        <v>-52.99187296000008</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.016967282354892</v>
+        <v>1.259759102943616</v>
       </c>
       <c r="T97">
-        <v>14.13166728960734</v>
+        <v>17.66458411200919</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.0312582258489076</v>
+        <v>0.03093261932964815</v>
       </c>
       <c r="W97">
-        <v>0.2284293103448276</v>
+        <v>0.228506088362069</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9267,7 +9267,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.3473136205434179</v>
+        <v>0.3436957703294239</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9275,22 +9275,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2697562089453308</v>
+        <v>0.2716562089453308</v>
       </c>
       <c r="C98">
-        <v>-582.215188426413</v>
+        <v>-598.0835481551302</v>
       </c>
       <c r="D98">
-        <v>231.604811573587</v>
+        <v>229.6564518448698</v>
       </c>
       <c r="E98">
-        <v>648.7199999999999</v>
+        <v>662.64</v>
       </c>
       <c r="F98">
-        <v>1336.32</v>
+        <v>1350.24</v>
       </c>
       <c r="G98">
         <v>522.5</v>
@@ -9311,37 +9311,37 @@
         <v>108.3</v>
       </c>
       <c r="M98">
-        <v>315.104256</v>
+        <v>318.386592</v>
       </c>
       <c r="N98">
-        <v>-206.804256</v>
+        <v>-210.086592</v>
       </c>
       <c r="O98">
-        <v>-18.61238304</v>
+        <v>-18.90779328</v>
       </c>
       <c r="P98">
-        <v>-188.19187296</v>
+        <v>-191.17879872</v>
       </c>
       <c r="Q98">
-        <v>-52.99187296000002</v>
+        <v>-55.97879872000001</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.259759102943612</v>
+        <v>1.66441213725815</v>
       </c>
       <c r="T98">
-        <v>17.66458411200914</v>
+        <v>23.55277881601219</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.03093261932964815</v>
+        <v>0.03061372634686828</v>
       </c>
       <c r="W98">
-        <v>0.228506088362069</v>
+        <v>0.2285812833274085</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9349,7 +9349,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.3436957703294239</v>
+        <v>0.340152514965203</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9357,22 +9357,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2716562089453308</v>
+        <v>0.2735562089453308</v>
       </c>
       <c r="C99">
-        <v>-598.0835481551302</v>
+        <v>-613.9194004628494</v>
       </c>
       <c r="D99">
-        <v>229.6564518448698</v>
+        <v>227.7405995371508</v>
       </c>
       <c r="E99">
-        <v>662.64</v>
+        <v>676.5600000000001</v>
       </c>
       <c r="F99">
-        <v>1350.24</v>
+        <v>1364.16</v>
       </c>
       <c r="G99">
         <v>522.5</v>
@@ -9393,37 +9393,37 @@
         <v>108.3</v>
       </c>
       <c r="M99">
-        <v>318.386592</v>
+        <v>321.6689280000001</v>
       </c>
       <c r="N99">
-        <v>-210.086592</v>
+        <v>-213.368928</v>
       </c>
       <c r="O99">
-        <v>-18.90779328</v>
+        <v>-19.20320352</v>
       </c>
       <c r="P99">
-        <v>-191.17879872</v>
+        <v>-194.1657244800001</v>
       </c>
       <c r="Q99">
-        <v>-55.97879872000001</v>
+        <v>-58.96572448000006</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.66441213725815</v>
+        <v>2.473718205887224</v>
       </c>
       <c r="T99">
-        <v>23.55277881601219</v>
+        <v>35.32916822401828</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.03061372634686828</v>
+        <v>0.03030134138414513</v>
       </c>
       <c r="W99">
-        <v>0.2285812833274085</v>
+        <v>0.2286549437016186</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9431,7 +9431,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.340152514965203</v>
+        <v>0.3366815709349459</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9439,22 +9439,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2735562089453308</v>
+        <v>0.2754562089453307</v>
       </c>
       <c r="C100">
-        <v>-613.9194004628494</v>
+        <v>-629.7235521742605</v>
       </c>
       <c r="D100">
-        <v>227.7405995371508</v>
+        <v>225.8564478257395</v>
       </c>
       <c r="E100">
-        <v>676.5600000000001</v>
+        <v>690.4799999999999</v>
       </c>
       <c r="F100">
-        <v>1364.16</v>
+        <v>1378.08</v>
       </c>
       <c r="G100">
         <v>522.5</v>
@@ -9475,37 +9475,37 @@
         <v>108.3</v>
       </c>
       <c r="M100">
-        <v>321.6689280000001</v>
+        <v>324.951264</v>
       </c>
       <c r="N100">
-        <v>-213.368928</v>
+        <v>-216.651264</v>
       </c>
       <c r="O100">
-        <v>-19.20320352</v>
+        <v>-19.49861376</v>
       </c>
       <c r="P100">
-        <v>-194.1657244800001</v>
+        <v>-197.15265024</v>
       </c>
       <c r="Q100">
-        <v>-58.96572448000006</v>
+        <v>-61.95265023999997</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.473718205887224</v>
+        <v>4.901636411774449</v>
       </c>
       <c r="T100">
-        <v>35.32916822401828</v>
+        <v>70.65833644803655</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.03030134138414513</v>
+        <v>0.02999526722874973</v>
       </c>
       <c r="W100">
-        <v>0.2286549437016186</v>
+        <v>0.2287271159874608</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9513,91 +9513,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.3366815709349459</v>
+        <v>0.3332807469861081</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2754562089453307</v>
-      </c>
-      <c r="C101">
-        <v>-629.7235521742605</v>
-      </c>
-      <c r="D101">
-        <v>225.8564478257395</v>
-      </c>
-      <c r="E101">
-        <v>690.4799999999999</v>
-      </c>
-      <c r="F101">
-        <v>1378.08</v>
-      </c>
-      <c r="G101">
-        <v>522.5</v>
-      </c>
-      <c r="H101">
-        <v>704.4</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>243.5</v>
-      </c>
-      <c r="K101">
-        <v>135.2</v>
-      </c>
-      <c r="L101">
-        <v>108.3</v>
-      </c>
-      <c r="M101">
-        <v>324.951264</v>
-      </c>
-      <c r="N101">
-        <v>-216.651264</v>
-      </c>
-      <c r="O101">
-        <v>-19.49861376</v>
-      </c>
-      <c r="P101">
-        <v>-197.15265024</v>
-      </c>
-      <c r="Q101">
-        <v>-61.95265023999997</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>4.901636411774449</v>
-      </c>
-      <c r="T101">
-        <v>70.65833644803655</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.02999526722874973</v>
-      </c>
-      <c r="W101">
-        <v>0.2287271159874608</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.3332807469861081</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
